--- a/Duwalcoe_Fact_Find_Template.xlsx
+++ b/Duwalcoe_Fact_Find_Template.xlsx
@@ -223,84 +223,77 @@
     <definedName name="FF_W_res_choice">Will!$C$76</definedName>
     <definedName name="FF_K_Rs">Will!$B$77:$D$77</definedName>
     <definedName name="FF_T_Rs">Will!$B$79:$D$83</definedName>
-    <definedName name="FF_W_sa_rf">Will!$C$86</definedName>
-    <definedName name="FF_W_sa_lp">Will!$C$87</definedName>
-    <definedName name="FF_W_sa_lp_notes">Will!$C$88</definedName>
-    <definedName name="FF_W_sa_prop_list">Will!$C$89</definedName>
-    <definedName name="FF_W_sa_prop">Will!$C$90</definedName>
-    <definedName name="FF_W_sa_biz">Will!$C$91</definedName>
-    <definedName name="FF_W_sa_biz_detail">Will!$C$92</definedName>
-    <definedName name="FF_W_sa_off">Will!$C$93</definedName>
-    <definedName name="FF_W_sa_off_detail">Will!$C$94</definedName>
-    <definedName name="FF_W_sa_fire">Will!$C$95</definedName>
-    <definedName name="FF_W_sa_fire_num">Will!$C$96</definedName>
-    <definedName name="FF_W_sa_fire_licensed">Will!$C$97</definedName>
-    <definedName name="FF_W_lw">Will!$C$100</definedName>
-    <definedName name="FF_W_lw_date">Will!$C$101</definedName>
-    <definedName name="FF_W_organ">Will!$C$102</definedName>
-    <definedName name="FF_W_cl_organ_reg">Will!$C$103</definedName>
-    <definedName name="FF_W_fw">Will!$C$106</definedName>
-    <definedName name="FF_W_fw_location">Will!$C$107</definedName>
-    <definedName name="FF_W_fw_requests">Will!$C$108</definedName>
-    <definedName name="FF_W_fw_cover">Will!$C$109</definedName>
-    <definedName name="FF_W_fw_cover_provider">Will!$C$110</definedName>
-    <definedName name="FF_W_fw_cover_policy">Will!$C$111</definedName>
-    <definedName name="FF_W_fw_cost">Will!$C$112</definedName>
-    <definedName name="FF_W_da_letter">Will!$C$115</definedName>
-    <definedName name="FF_W_da_letter_with">Will!$C$116</definedName>
-    <definedName name="FF_W_da_social">Will!$C$117</definedName>
-    <definedName name="FF_W_da_crypto">Will!$C$118</definedName>
-    <definedName name="FF_W_da_crypto_loc">Will!$C$119</definedName>
-    <definedName name="FF_W_pet_na">Will!$C$122</definedName>
-    <definedName name="FF_W_pet_carer">Will!$C$123</definedName>
-    <definedName name="FF_W_pet_bequest">Will!$C$124</definedName>
-    <definedName name="FF_W_lo">Will!$C$127</definedName>
-    <definedName name="FF_W_add_notes">Will!$C$130</definedName>
-    <definedName name="FF_W_ex_p_name">Will!$C$133</definedName>
-    <definedName name="FF_W_ex_p_id">Will!$C$134</definedName>
-    <definedName name="FF_W_ex_p_rel">Will!$C$135</definedName>
-    <definedName name="FF_W_ex_p_contact">Will!$C$136</definedName>
-    <definedName name="FF_W_ex_p_address">Will!$C$137</definedName>
-    <definedName name="FF_W_ex_a_name">Will!$C$138</definedName>
-    <definedName name="FF_W_ex_a_id">Will!$C$139</definedName>
-    <definedName name="FF_W_ex_a_rel">Will!$C$140</definedName>
-    <definedName name="FF_W_ex_a_contact">Will!$C$141</definedName>
-    <definedName name="FF_W_ex_security">Will!$C$142</definedName>
-    <definedName name="FF_W_ex_fee">Will!$C$143</definedName>
-    <definedName name="FF_W_ex_fee_rate">Will!$C$144</definedName>
-    <definedName name="FF_W_ex_assume">Will!$C$145</definedName>
-    <definedName name="FF_W_ex_notes">Will!$C$146</definedName>
-    <definedName name="FF_W_cl_lang">Will!$C$149</definedName>
-    <definedName name="FF_W_cl_lang_other">Will!$C$150</definedName>
-    <definedName name="FF_W_cl_wt">Will!$C$151</definedName>
-    <definedName name="FF_W_cl_wt_sp_inc">Will!$C$152</definedName>
-    <definedName name="FF_W_cl_wt_kids_cap">Will!$C$153</definedName>
-    <definedName name="FF_W_cl_wt_cap1_name">Will!$C$154</definedName>
-    <definedName name="FF_W_cl_wt_cap1_rel">Will!$C$155</definedName>
-    <definedName name="FF_W_cl_wt_cap2_name">Will!$C$156</definedName>
-    <definedName name="FF_W_cl_wt_cap2_rel">Will!$C$157</definedName>
-    <definedName name="FF_W_cl_wt_cap3_name">Will!$C$158</definedName>
-    <definedName name="FF_W_cl_wt_cap3_rel">Will!$C$159</definedName>
-    <definedName name="FF_W_cl_pt_ben">Will!$C$160</definedName>
-    <definedName name="FF_W_cl_pt_rel">Will!$C$161</definedName>
-    <definedName name="FF_W_cl_nok_name">Will!$C$162</definedName>
-    <definedName name="FF_W_cl_nok_rel">Will!$C$163</definedName>
-    <definedName name="FF_W_cl_nok_cell">Will!$C$164</definedName>
-    <definedName name="FF_W_cl_nok_email">Will!$C$165</definedName>
-    <definedName name="FF_W_cl_ct1_name">Will!$C$166</definedName>
-    <definedName name="FF_W_cl_ct1_id">Will!$C$167</definedName>
-    <definedName name="FF_W_cl_ct1_rel">Will!$C$168</definedName>
-    <definedName name="FF_W_cl_ct2_name">Will!$C$169</definedName>
-    <definedName name="FF_W_cl_ct2_id">Will!$C$170</definedName>
-    <definedName name="FF_W_cl_ct2_rel">Will!$C$171</definedName>
-    <definedName name="FF_W_cl_exec">Will!$C$172</definedName>
-    <definedName name="FF_W_cl_ce1_name">Will!$C$173</definedName>
-    <definedName name="FF_W_cl_ce1_id">Will!$C$174</definedName>
-    <definedName name="FF_W_cl_ce1_rel">Will!$C$175</definedName>
-    <definedName name="FF_W_cl_ce2_name">Will!$C$176</definedName>
-    <definedName name="FF_W_cl_ce2_id">Will!$C$177</definedName>
-    <definedName name="FF_W_cl_ce2_rel">Will!$C$178</definedName>
-    <definedName name="FF_W_cl_collect">Will!$C$179</definedName>
+    <definedName name="FF_W_sa_off">Will!$C$87</definedName>
+    <definedName name="FF_W_sa_off_detail">Will!$C$88</definedName>
+    <definedName name="FF_W_sa_fire">Will!$C$89</definedName>
+    <definedName name="FF_W_sa_fire_num">Will!$C$90</definedName>
+    <definedName name="FF_W_sa_fire_licensed">Will!$C$91</definedName>
+    <definedName name="FF_W_lw">Will!$C$94</definedName>
+    <definedName name="FF_W_lw_date">Will!$C$95</definedName>
+    <definedName name="FF_W_organ">Will!$C$96</definedName>
+    <definedName name="FF_W_cl_organ_reg">Will!$C$97</definedName>
+    <definedName name="FF_W_fw">Will!$C$100</definedName>
+    <definedName name="FF_W_fw_location">Will!$C$101</definedName>
+    <definedName name="FF_W_fw_requests">Will!$C$102</definedName>
+    <definedName name="FF_W_fw_cover">Will!$C$103</definedName>
+    <definedName name="FF_W_fw_cover_provider">Will!$C$104</definedName>
+    <definedName name="FF_W_fw_cover_policy">Will!$C$105</definedName>
+    <definedName name="FF_W_fw_cost">Will!$C$106</definedName>
+    <definedName name="FF_W_da_letter">Will!$C$109</definedName>
+    <definedName name="FF_W_da_letter_with">Will!$C$110</definedName>
+    <definedName name="FF_W_da_social">Will!$C$111</definedName>
+    <definedName name="FF_W_da_crypto">Will!$C$112</definedName>
+    <definedName name="FF_W_da_crypto_loc">Will!$C$113</definedName>
+    <definedName name="FF_W_pet_na">Will!$C$116</definedName>
+    <definedName name="FF_W_pet_carer">Will!$C$117</definedName>
+    <definedName name="FF_W_pet_bequest">Will!$C$118</definedName>
+    <definedName name="FF_W_lo">Will!$C$121</definedName>
+    <definedName name="FF_W_add_notes">Will!$C$124</definedName>
+    <definedName name="FF_W_ex_p_name">Will!$C$127</definedName>
+    <definedName name="FF_W_ex_p_id">Will!$C$128</definedName>
+    <definedName name="FF_W_ex_p_rel">Will!$C$129</definedName>
+    <definedName name="FF_W_ex_p_contact">Will!$C$130</definedName>
+    <definedName name="FF_W_ex_p_address">Will!$C$131</definedName>
+    <definedName name="FF_W_ex_a_name">Will!$C$132</definedName>
+    <definedName name="FF_W_ex_a_id">Will!$C$133</definedName>
+    <definedName name="FF_W_ex_a_rel">Will!$C$134</definedName>
+    <definedName name="FF_W_ex_a_contact">Will!$C$135</definedName>
+    <definedName name="FF_W_ex_security">Will!$C$136</definedName>
+    <definedName name="FF_W_ex_fee">Will!$C$137</definedName>
+    <definedName name="FF_W_ex_fee_rate">Will!$C$138</definedName>
+    <definedName name="FF_W_ex_assume">Will!$C$139</definedName>
+    <definedName name="FF_W_ex_notes">Will!$C$140</definedName>
+    <definedName name="FF_W_cl_lang">Will!$C$143</definedName>
+    <definedName name="FF_W_cl_lang_other">Will!$C$144</definedName>
+    <definedName name="FF_W_cl_wt">Will!$C$145</definedName>
+    <definedName name="FF_W_cl_wt_sp_inc">Will!$C$146</definedName>
+    <definedName name="FF_W_cl_wt_kids_cap">Will!$C$147</definedName>
+    <definedName name="FF_W_cl_wt_cap1_name">Will!$C$148</definedName>
+    <definedName name="FF_W_cl_wt_cap1_rel">Will!$C$149</definedName>
+    <definedName name="FF_W_cl_wt_cap2_name">Will!$C$150</definedName>
+    <definedName name="FF_W_cl_wt_cap2_rel">Will!$C$151</definedName>
+    <definedName name="FF_W_cl_wt_cap3_name">Will!$C$152</definedName>
+    <definedName name="FF_W_cl_wt_cap3_rel">Will!$C$153</definedName>
+    <definedName name="FF_W_cl_pt_ben">Will!$C$154</definedName>
+    <definedName name="FF_W_cl_pt_rel">Will!$C$155</definedName>
+    <definedName name="FF_W_cl_nok_name">Will!$C$156</definedName>
+    <definedName name="FF_W_cl_nok_rel">Will!$C$157</definedName>
+    <definedName name="FF_W_cl_nok_cell">Will!$C$158</definedName>
+    <definedName name="FF_W_cl_nok_email">Will!$C$159</definedName>
+    <definedName name="FF_W_cl_ct1_name">Will!$C$160</definedName>
+    <definedName name="FF_W_cl_ct1_id">Will!$C$161</definedName>
+    <definedName name="FF_W_cl_ct1_rel">Will!$C$162</definedName>
+    <definedName name="FF_W_cl_ct2_name">Will!$C$163</definedName>
+    <definedName name="FF_W_cl_ct2_id">Will!$C$164</definedName>
+    <definedName name="FF_W_cl_ct2_rel">Will!$C$165</definedName>
+    <definedName name="FF_W_cl_exec">Will!$C$166</definedName>
+    <definedName name="FF_W_cl_ce1_name">Will!$C$167</definedName>
+    <definedName name="FF_W_cl_ce1_id">Will!$C$168</definedName>
+    <definedName name="FF_W_cl_ce1_rel">Will!$C$169</definedName>
+    <definedName name="FF_W_cl_ce2_name">Will!$C$170</definedName>
+    <definedName name="FF_W_cl_ce2_id">Will!$C$171</definedName>
+    <definedName name="FF_W_cl_ce2_rel">Will!$C$172</definedName>
+    <definedName name="FF_W_cl_collect">Will!$C$173</definedName>
     <definedName name="FF_M_Breaks">Lists!$Z$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Start here'!$A1:$F22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Start here'!$1:$2</definedName>
@@ -314,7 +307,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Companies and trusts'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Needs'!$A1:$J24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Needs'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Will'!$A1:$E180</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Will'!$A1:$E174</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Will'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$2</definedName>
@@ -324,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="544">
   <si>
     <t>Duwalcoe Financial Consultants CC</t>
   </si>
@@ -1169,25 +1162,7 @@
     <t>9. Special assets</t>
   </si>
   <si>
-    <t>Retirement funds (s.37C)</t>
-  </si>
-  <si>
-    <t>Life insurance policies</t>
-  </si>
-  <si>
-    <t>Notes on policies</t>
-  </si>
-  <si>
-    <t>Fixed property: address and holding structure (own name, trust or company)</t>
-  </si>
-  <si>
-    <t>Fixed property instruction</t>
-  </si>
-  <si>
-    <t>Business interests</t>
-  </si>
-  <si>
-    <t>Business notes for the attorney (entity, % held, to whom)</t>
+    <t>Your property and business interests, and who each one passes to, are taken from the Assets and debts and the Companies and trusts sheets. Life policies and retirement funds, with their beneficiaries, are on your policy schedule.</t>
   </si>
   <si>
     <t>Offshore assets</t>
@@ -1571,18 +1546,6 @@
     <t>w_res_choice</t>
   </si>
   <si>
-    <t>w_sa_rf</t>
-  </si>
-  <si>
-    <t>w_sa_lp</t>
-  </si>
-  <si>
-    <t>w_sa_prop</t>
-  </si>
-  <si>
-    <t>w_sa_biz</t>
-  </si>
-  <si>
     <t>w_sa_off</t>
   </si>
   <si>
@@ -1679,18 +1642,6 @@
     <t>Entire residue to my spouse / life partner</t>
   </si>
   <si>
-    <t>I have reviewed my fund beneficiary nominations</t>
-  </si>
-  <si>
-    <t>All life policies have current beneficiary nominations</t>
-  </si>
-  <si>
-    <t>Property to pass to surviving spouse (s.4(q) deduction)</t>
-  </si>
-  <si>
-    <t>Not applicable</t>
-  </si>
-  <si>
     <t>Yes — I wish a living will to be drafted</t>
   </si>
   <si>
@@ -1769,7 +1720,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0</t>
+    <t>1.1</t>
   </si>
   <si>
     <t>Trustees may pay capital sooner for education, medical, first home, etc.</t>
@@ -1778,18 +1729,6 @@
     <t>Entire residue to my children equally, per stirpes</t>
   </si>
   <si>
-    <t>I wish to update my fund nominations (attorney / adviser to assist)</t>
-  </si>
-  <si>
-    <t>Some policies pay into my estate (no nominated beneficiary)</t>
-  </si>
-  <si>
-    <t>Property to be sold and proceeds form part of residue</t>
-  </si>
-  <si>
-    <t>I am a shareholder / member (detail below)</t>
-  </si>
-  <si>
     <t>I hold assets offshore (a separate offshore will may be recommended)</t>
   </si>
   <si>
@@ -1871,12 +1810,6 @@
     <t>Entire residue to my children equally, per capita</t>
   </si>
   <si>
-    <t>Specific property to a specific beneficiary (detail in section 7)</t>
-  </si>
-  <si>
-    <t>A buy-and-sell agreement is in place</t>
-  </si>
-  <si>
     <t>I already have a living will (date below)</t>
   </si>
   <si>
@@ -1934,9 +1867,6 @@
     <t>Split as follows (table below)</t>
   </si>
   <si>
-    <t>No buy-and-sell — business interest to pass to (below)</t>
-  </si>
-  <si>
     <t>Dr.</t>
   </si>
   <si>
@@ -2003,7 +1933,7 @@
     <t>Breaks</t>
   </si>
   <si>
-    <t>[["Assets and debts",53],["Companies and trusts",51],["Companies and trusts",96],["Companies and trusts",141]]</t>
+    <t>[["Assets and debts",53],["Companies and trusts",51],["Companies and trusts",96],["Companies and trusts",141],["Will",63]]</t>
   </si>
   <si>
     <t>Adv.</t>
@@ -2627,72 +2557,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AV34"/>
+  <dimension ref="A1:AR34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" t="s">
+        <v>387</v>
+      </c>
+      <c r="D1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E1" t="s">
+        <v>389</v>
+      </c>
+      <c r="F1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G1" t="s">
         <v>391</v>
       </c>
-      <c r="B1" t="s">
+      <c r="H1" t="s">
         <v>392</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
         <v>393</v>
       </c>
-      <c r="D1" t="s">
+      <c r="J1" t="s">
         <v>394</v>
       </c>
-      <c r="E1" t="s">
+      <c r="K1" t="s">
         <v>395</v>
       </c>
-      <c r="F1" t="s">
+      <c r="L1" t="s">
         <v>396</v>
-      </c>
-      <c r="G1" t="s">
-        <v>397</v>
-      </c>
-      <c r="H1" t="s">
-        <v>398</v>
-      </c>
-      <c r="I1" t="s">
-        <v>399</v>
-      </c>
-      <c r="J1" t="s">
-        <v>400</v>
-      </c>
-      <c r="K1" t="s">
-        <v>401</v>
-      </c>
-      <c r="L1" t="s">
-        <v>402</v>
       </c>
       <c r="M1" t="s">
         <v>152</v>
       </c>
       <c r="N1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="O1" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="P1" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="Q1" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="R1" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="S1" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="T1" t="s">
         <v>110</v>
       </c>
       <c r="U1" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="V1" t="s">
         <v>208</v>
@@ -2701,82 +2631,70 @@
         <v>209</v>
       </c>
       <c r="X1" t="s">
+        <v>404</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>405</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>406</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>407</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>408</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>409</v>
+      </c>
+      <c r="AD1" t="s">
         <v>410</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AE1" t="s">
         <v>411</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AF1" t="s">
         <v>412</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AG1" t="s">
         <v>413</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AH1" t="s">
         <v>414</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AI1" t="s">
         <v>415</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AJ1" t="s">
         <v>416</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AK1" t="s">
         <v>417</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AL1" t="s">
         <v>418</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AM1" t="s">
         <v>419</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AN1" t="s">
         <v>420</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AO1" t="s">
         <v>421</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AP1" t="s">
         <v>422</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AQ1" t="s">
         <v>423</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AR1" t="s">
         <v>424</v>
       </c>
-      <c r="AM1" t="s">
-        <v>425</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>426</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>427</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>428</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>429</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>430</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>431</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>432</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>433</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A2">
         <f>IF('Client and family'!$C$11&lt;&gt;"",'Client and family'!$C$11,IF('Client and family'!$C$10&lt;&gt;"",LEFT(TRIM('Client and family'!$C$10),FIND(" ",TRIM('Client and family'!$C$10)&amp;" ")-1),"Client"))</f>
       </c>
@@ -2787,25 +2705,25 @@
         <f>IF('Assets and debts'!$B$12="",""," "&amp;'Assets and debts'!$B$12)</f>
       </c>
       <c r="D2" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="E2" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="F2" t="s">
         <v>77</v>
       </c>
       <c r="G2" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="H2" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="I2" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="J2" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="K2" t="s">
         <v>76</v>
@@ -2814,28 +2732,28 @@
         <v>87</v>
       </c>
       <c r="M2" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="N2" t="s">
         <v>147</v>
       </c>
       <c r="O2" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="P2" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="Q2" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="R2" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="S2" t="s">
         <v>193</v>
       </c>
       <c r="T2" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="U2" t="s">
         <v>128</v>
@@ -2850,79 +2768,67 @@
         <v>128</v>
       </c>
       <c r="Y2" t="s">
+        <v>437</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>438</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>439</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>440</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>435</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>435</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>441</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>442</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>443</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>444</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>445</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>446</v>
+      </c>
+      <c r="AK2" t="s">
         <v>447</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AL2" t="s">
         <v>448</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AM2" t="s">
         <v>449</v>
       </c>
-      <c r="AB2" t="s">
-        <v>450</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>451</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>452</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>453</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>454</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>445</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>445</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>455</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>456</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>457</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>458</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>459</v>
-      </c>
       <c r="AN2" t="s">
-        <v>460</v>
+        <v>77</v>
       </c>
       <c r="AO2" t="s">
-        <v>461</v>
+        <v>77</v>
       </c>
       <c r="AP2" t="s">
-        <v>462</v>
+        <v>77</v>
       </c>
       <c r="AQ2" t="s">
-        <v>463</v>
+        <v>77</v>
       </c>
       <c r="AR2" t="s">
         <v>77</v>
       </c>
-      <c r="AS2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AV2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>IF('Client and family'!$D$10&lt;&gt;"",LEFT(TRIM('Client and family'!$D$10),FIND(" ",TRIM('Client and family'!$D$10)&amp;" ")-1),"Spouse")</f>
       </c>
@@ -2933,52 +2839,52 @@
         <f>IF('Assets and debts'!$B$13="",""," "&amp;'Assets and debts'!$B$13)</f>
       </c>
       <c r="D3" t="s">
-        <v>464</v>
+        <v>450</v>
       </c>
       <c r="E3" t="s">
-        <v>465</v>
+        <v>451</v>
       </c>
       <c r="F3" t="s">
         <v>129</v>
       </c>
       <c r="G3" t="s">
-        <v>466</v>
+        <v>452</v>
       </c>
       <c r="H3" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="I3" t="s">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="J3" t="s">
-        <v>469</v>
+        <v>455</v>
       </c>
       <c r="K3" t="s">
-        <v>470</v>
+        <v>456</v>
       </c>
       <c r="L3" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="M3" t="s">
         <v>164</v>
       </c>
       <c r="N3" t="s">
-        <v>472</v>
+        <v>458</v>
       </c>
       <c r="O3" t="s">
-        <v>473</v>
+        <v>459</v>
       </c>
       <c r="P3" t="s">
-        <v>474</v>
+        <v>460</v>
       </c>
       <c r="Q3" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="R3" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
       <c r="S3" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="T3" t="s">
         <v>149</v>
@@ -2987,88 +2893,76 @@
         <v>148</v>
       </c>
       <c r="V3" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="W3" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="X3" t="s">
         <v>148</v>
       </c>
       <c r="Y3" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="Z3" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="AA3" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="AB3" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="AC3" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="AD3" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="AE3" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="AF3" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="AG3" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="AH3" t="s">
-        <v>489</v>
+        <v>435</v>
       </c>
       <c r="AI3" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="AJ3" t="s">
-        <v>491</v>
+        <v>129</v>
       </c>
       <c r="AK3" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="AL3" t="s">
-        <v>445</v>
+        <v>477</v>
       </c>
       <c r="AM3" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="AN3" t="s">
         <v>129</v>
       </c>
       <c r="AO3" t="s">
-        <v>494</v>
+        <v>129</v>
       </c>
       <c r="AP3" t="s">
-        <v>495</v>
+        <v>129</v>
       </c>
       <c r="AQ3" t="s">
-        <v>496</v>
+        <v>129</v>
       </c>
       <c r="AR3" t="s">
         <v>129</v>
       </c>
-      <c r="AS3" t="s">
-        <v>129</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>129</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>129</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>127</v>
       </c>
@@ -3079,43 +2973,43 @@
         <f>IF('Assets and debts'!$B$14="",""," "&amp;'Assets and debts'!$B$14)</f>
       </c>
       <c r="D4" t="s">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="H4" t="s">
-        <v>498</v>
+        <v>480</v>
       </c>
       <c r="I4" t="s">
-        <v>499</v>
+        <v>481</v>
       </c>
       <c r="J4" t="s">
-        <v>500</v>
+        <v>482</v>
       </c>
       <c r="K4" t="s">
-        <v>501</v>
+        <v>483</v>
       </c>
       <c r="L4" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="M4" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="N4" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="O4" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="P4" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="Q4" t="s">
-        <v>507</v>
+        <v>489</v>
       </c>
       <c r="R4" t="s">
-        <v>508</v>
+        <v>490</v>
       </c>
       <c r="S4" t="s">
-        <v>509</v>
+        <v>491</v>
       </c>
       <c r="T4" t="s">
         <v>194</v>
@@ -3124,46 +3018,40 @@
         <v>122</v>
       </c>
       <c r="V4" t="s">
-        <v>510</v>
+        <v>492</v>
       </c>
       <c r="X4" t="s">
         <v>122</v>
       </c>
       <c r="Y4" t="s">
-        <v>511</v>
+        <v>493</v>
       </c>
       <c r="Z4" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="AA4" t="s">
-        <v>513</v>
+        <v>495</v>
       </c>
       <c r="AB4" t="s">
-        <v>514</v>
+        <v>496</v>
       </c>
       <c r="AE4" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="AF4" t="s">
-        <v>516</v>
+        <v>498</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>499</v>
       </c>
       <c r="AI4" t="s">
-        <v>517</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>518</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="s">
-        <v>520</v>
-      </c>
-      <c r="AQ4" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="5" spans="2:32" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B5">
         <f>IF('Client and family'!$B$40="","",'Client and family'!$B$40)</f>
       </c>
@@ -3171,52 +3059,49 @@
         <f>IF('Assets and debts'!$B$15="",""," "&amp;'Assets and debts'!$B$15)</f>
       </c>
       <c r="D5" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="H5" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="I5" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="J5" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="K5" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="L5" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="M5" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="N5" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="O5" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="Q5" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="S5" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="T5" t="s">
         <v>130</v>
       </c>
       <c r="V5" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="Y5" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="AB5" t="s">
-        <v>535</v>
-      </c>
-      <c r="AF5" t="s">
-        <v>536</v>
+        <v>515</v>
       </c>
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.25">
@@ -3227,34 +3112,34 @@
         <f>IF('Assets and debts'!$B$16="",""," "&amp;'Assets and debts'!$B$16)</f>
       </c>
       <c r="D6" t="s">
-        <v>537</v>
+        <v>516</v>
       </c>
       <c r="H6" t="s">
-        <v>538</v>
+        <v>517</v>
       </c>
       <c r="I6" t="s">
-        <v>539</v>
+        <v>518</v>
       </c>
       <c r="J6" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="K6" t="s">
-        <v>540</v>
+        <v>519</v>
       </c>
       <c r="L6" t="s">
-        <v>541</v>
+        <v>520</v>
       </c>
       <c r="M6" t="s">
-        <v>542</v>
+        <v>521</v>
       </c>
       <c r="N6" t="s">
-        <v>543</v>
+        <v>522</v>
       </c>
       <c r="O6" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
       <c r="V6" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.25">
@@ -3265,34 +3150,34 @@
         <f>IF('Assets and debts'!$B$17="",""," "&amp;'Assets and debts'!$B$17)</f>
       </c>
       <c r="D7" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
       <c r="H7" t="s">
-        <v>546</v>
+        <v>525</v>
       </c>
       <c r="I7" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="K7" t="s">
-        <v>547</v>
+        <v>526</v>
       </c>
       <c r="L7" t="s">
-        <v>548</v>
+        <v>527</v>
       </c>
       <c r="M7" t="s">
-        <v>549</v>
+        <v>528</v>
       </c>
       <c r="N7" t="s">
-        <v>550</v>
+        <v>529</v>
       </c>
       <c r="O7" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="Y7" t="s">
-        <v>551</v>
+        <v>530</v>
       </c>
       <c r="Z7" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.25">
@@ -3303,28 +3188,28 @@
         <f>IF('Assets and debts'!$B$18="",""," "&amp;'Assets and debts'!$B$18)</f>
       </c>
       <c r="D8" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="H8" t="s">
-        <v>553</v>
+        <v>532</v>
       </c>
       <c r="K8" t="s">
-        <v>554</v>
+        <v>533</v>
       </c>
       <c r="L8" t="s">
-        <v>555</v>
+        <v>534</v>
       </c>
       <c r="M8" t="s">
-        <v>556</v>
+        <v>535</v>
       </c>
       <c r="N8" t="s">
-        <v>557</v>
+        <v>536</v>
       </c>
       <c r="Y8" t="s">
-        <v>558</v>
+        <v>537</v>
       </c>
       <c r="Z8" t="s">
-        <v>559</v>
+        <v>538</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -3335,22 +3220,22 @@
         <f>IF('Assets and debts'!$B$19="",""," "&amp;'Assets and debts'!$B$19)</f>
       </c>
       <c r="D9" t="s">
-        <v>560</v>
+        <v>539</v>
       </c>
       <c r="H9" t="s">
-        <v>561</v>
+        <v>540</v>
       </c>
       <c r="K9" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="L9" t="s">
-        <v>562</v>
+        <v>541</v>
       </c>
       <c r="M9" t="s">
-        <v>563</v>
+        <v>542</v>
       </c>
       <c r="N9" t="s">
-        <v>564</v>
+        <v>543</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -3361,13 +3246,13 @@
         <f>IF('Assets and debts'!$B$26="",""," "&amp;'Assets and debts'!$B$26)</f>
       </c>
       <c r="L10" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="M10" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="N10" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="3:3" x14ac:dyDescent="0.25">
@@ -8007,7 +7892,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:E179"/>
+  <dimension ref="B1:E173"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -8600,12 +8485,12 @@
       <c r="E85" s="5"/>
     </row>
     <row r="86" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="C86" s="11"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
+      <c r="C86" s="28"/>
+      <c r="D86" s="28"/>
+      <c r="E86" s="28"/>
     </row>
     <row r="87" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B87" s="7" t="s">
@@ -8623,7 +8508,7 @@
       <c r="D88" s="11"/>
       <c r="E88" s="11"/>
     </row>
-    <row r="89" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="89" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B89" s="7" t="s">
         <v>284</v>
       </c>
@@ -8631,7 +8516,7 @@
       <c r="D89" s="11"/>
       <c r="E89" s="11"/>
     </row>
-    <row r="90" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B90" s="7" t="s">
         <v>285</v>
       </c>
@@ -8639,7 +8524,7 @@
       <c r="D90" s="11"/>
       <c r="E90" s="11"/>
     </row>
-    <row r="91" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B91" s="7" t="s">
         <v>286</v>
       </c>
@@ -8647,41 +8532,33 @@
       <c r="D91" s="11"/>
       <c r="E91" s="11"/>
     </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B92" s="7" t="s">
+    <row r="93" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-    </row>
-    <row r="93" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="7" t="s">
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B94" s="7" t="s">
         <v>288</v>
-      </c>
-      <c r="C93" s="11"/>
-      <c r="D93" s="11"/>
-      <c r="E93" s="11"/>
-    </row>
-    <row r="94" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B94" s="7" t="s">
-        <v>289</v>
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
       <c r="E94" s="11"/>
     </row>
-    <row r="95" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B95" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
       <c r="E95" s="11"/>
     </row>
-    <row r="96" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="96" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B96" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
@@ -8689,15 +8566,15 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B97" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
+        <v>291</v>
+      </c>
+      <c r="C97" s="14"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="14"/>
     </row>
     <row r="99" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B99" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -8705,23 +8582,23 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B100" s="7" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
       <c r="E100" s="11"/>
     </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="101" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B101" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
       <c r="E101" s="11"/>
     </row>
-    <row r="102" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="102" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B102" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
@@ -8729,19 +8606,27 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B103" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B104" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C103" s="14"/>
-      <c r="D103" s="14"/>
-      <c r="E103" s="14"/>
-    </row>
-    <row r="105" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B105" s="4" t="s">
+      <c r="C104" s="11"/>
+      <c r="D104" s="11"/>
+      <c r="E104" s="11"/>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B105" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="C105" s="5"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
+      <c r="C105" s="15"/>
+      <c r="D105" s="15"/>
+      <c r="E105" s="15"/>
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B106" s="7" t="s">
@@ -8751,33 +8636,25 @@
       <c r="D106" s="11"/>
       <c r="E106" s="11"/>
     </row>
-    <row r="107" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B107" s="7" t="s">
+    <row r="108" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B108" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="C107" s="11"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="11"/>
-    </row>
-    <row r="108" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B108" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="C108" s="11"/>
-      <c r="D108" s="11"/>
-      <c r="E108" s="11"/>
+      <c r="C108" s="5"/>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B109" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="C109" s="11"/>
-      <c r="D109" s="11"/>
-      <c r="E109" s="11"/>
+        <v>301</v>
+      </c>
+      <c r="C109" s="14"/>
+      <c r="D109" s="14"/>
+      <c r="E109" s="14"/>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B110" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11"/>
@@ -8785,47 +8662,47 @@
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B111" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="C111" s="15"/>
-      <c r="D111" s="15"/>
-      <c r="E111" s="15"/>
+        <v>303</v>
+      </c>
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B112" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="C112" s="14"/>
+      <c r="D112" s="14"/>
+      <c r="E112" s="14"/>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B113" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C112" s="11"/>
-      <c r="D112" s="11"/>
-      <c r="E112" s="11"/>
-    </row>
-    <row r="114" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B114" s="4" t="s">
+      <c r="C113" s="11"/>
+      <c r="D113" s="11"/>
+      <c r="E113" s="11"/>
+    </row>
+    <row r="115" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B115" s="4" t="s">
         <v>306</v>
       </c>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B115" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="C115" s="14"/>
-      <c r="D115" s="14"/>
-      <c r="E115" s="14"/>
+      <c r="C115" s="5"/>
+      <c r="D115" s="5"/>
+      <c r="E115" s="5"/>
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B116" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
+        <v>307</v>
+      </c>
+      <c r="C116" s="14"/>
+      <c r="D116" s="14"/>
+      <c r="E116" s="14"/>
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B117" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C117" s="11"/>
       <c r="D117" s="11"/>
@@ -8833,47 +8710,39 @@
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B118" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C118" s="11"/>
+      <c r="D118" s="11"/>
+      <c r="E118" s="11"/>
+    </row>
+    <row r="120" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B120" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="C118" s="14"/>
-      <c r="D118" s="14"/>
-      <c r="E118" s="14"/>
-    </row>
-    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B119" s="7" t="s">
+      <c r="C120" s="5"/>
+      <c r="D120" s="5"/>
+      <c r="E120" s="5"/>
+    </row>
+    <row r="121" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B121" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
-    </row>
-    <row r="121" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B121" s="4" t="s">
+      <c r="C121" s="11"/>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
+    </row>
+    <row r="123" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B123" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="C121" s="5"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-    </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="7" t="s">
+      <c r="C123" s="5"/>
+      <c r="D123" s="5"/>
+      <c r="E123" s="5"/>
+    </row>
+    <row r="124" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B124" s="7" t="s">
         <v>313</v>
-      </c>
-      <c r="C122" s="14"/>
-      <c r="D122" s="14"/>
-      <c r="E122" s="14"/>
-    </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B123" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="C123" s="11"/>
-      <c r="D123" s="11"/>
-      <c r="E123" s="11"/>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="7" t="s">
-        <v>315</v>
       </c>
       <c r="C124" s="11"/>
       <c r="D124" s="11"/>
@@ -8881,75 +8750,91 @@
     </row>
     <row r="126" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
       <c r="E126" s="5"/>
     </row>
-    <row r="127" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B127" s="7" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C127" s="11"/>
       <c r="D127" s="11"/>
       <c r="E127" s="11"/>
     </row>
-    <row r="129" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B129" s="4" t="s">
+    <row r="128" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B128" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="C128" s="15"/>
+      <c r="D128" s="15"/>
+      <c r="E128" s="15"/>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B129" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C129" s="11"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B130" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
-    </row>
-    <row r="130" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B130" s="7" t="s">
+      <c r="C130" s="15"/>
+      <c r="D130" s="15"/>
+      <c r="E130" s="15"/>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B131" s="7" t="s">
         <v>319</v>
       </c>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="11"/>
-    </row>
-    <row r="132" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B132" s="4" t="s">
+      <c r="C131" s="11"/>
+      <c r="D131" s="11"/>
+      <c r="E131" s="11"/>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B132" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C132" s="5"/>
-      <c r="D132" s="5"/>
-      <c r="E132" s="5"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B133" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="11"/>
+      <c r="C133" s="15"/>
+      <c r="D133" s="15"/>
+      <c r="E133" s="15"/>
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B134" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="C134" s="15"/>
-      <c r="D134" s="15"/>
-      <c r="E134" s="15"/>
+      <c r="C134" s="11"/>
+      <c r="D134" s="11"/>
+      <c r="E134" s="11"/>
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B135" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="C135" s="11"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="11"/>
-    </row>
-    <row r="136" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C135" s="15"/>
+      <c r="D135" s="15"/>
+      <c r="E135" s="15"/>
+    </row>
+    <row r="136" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B136" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="C136" s="15"/>
-      <c r="D136" s="15"/>
-      <c r="E136" s="15"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B137" s="7" t="s">
@@ -8971,11 +8856,11 @@
       <c r="B139" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C139" s="15"/>
-      <c r="D139" s="15"/>
-      <c r="E139" s="15"/>
-    </row>
-    <row r="140" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C139" s="14"/>
+      <c r="D139" s="14"/>
+      <c r="E139" s="14"/>
+    </row>
+    <row r="140" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B140" s="7" t="s">
         <v>328</v>
       </c>
@@ -8983,25 +8868,17 @@
       <c r="D140" s="11"/>
       <c r="E140" s="11"/>
     </row>
-    <row r="141" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B141" s="7" t="s">
+    <row r="142" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B142" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="C141" s="15"/>
-      <c r="D141" s="15"/>
-      <c r="E141" s="15"/>
-    </row>
-    <row r="142" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B142" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="C142" s="11"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
+      <c r="C142" s="5"/>
+      <c r="D142" s="5"/>
+      <c r="E142" s="5"/>
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B143" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C143" s="11"/>
       <c r="D143" s="11"/>
@@ -9009,7 +8886,7 @@
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B144" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C144" s="11"/>
       <c r="D144" s="11"/>
@@ -9017,27 +8894,35 @@
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B145" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11"/>
+      <c r="E145" s="11"/>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B146" s="7" t="s">
         <v>333</v>
-      </c>
-      <c r="C145" s="14"/>
-      <c r="D145" s="14"/>
-      <c r="E145" s="14"/>
-    </row>
-    <row r="146" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B146" s="7" t="s">
-        <v>334</v>
       </c>
       <c r="C146" s="11"/>
       <c r="D146" s="11"/>
       <c r="E146" s="11"/>
     </row>
-    <row r="148" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="4" t="s">
+    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B147" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C147" s="11"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B148" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="C148" s="5"/>
-      <c r="D148" s="5"/>
-      <c r="E148" s="5"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B149" s="7" t="s">
@@ -9115,9 +9000,9 @@
       <c r="B158" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="C158" s="11"/>
-      <c r="D158" s="11"/>
-      <c r="E158" s="11"/>
+      <c r="C158" s="15"/>
+      <c r="D158" s="15"/>
+      <c r="E158" s="15"/>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B159" s="7" t="s">
@@ -9139,9 +9024,9 @@
       <c r="B161" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="C161" s="11"/>
-      <c r="D161" s="11"/>
-      <c r="E161" s="11"/>
+      <c r="C161" s="15"/>
+      <c r="D161" s="15"/>
+      <c r="E161" s="15"/>
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B162" s="7" t="s">
@@ -9187,17 +9072,17 @@
       <c r="B167" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="C167" s="15"/>
-      <c r="D167" s="15"/>
-      <c r="E167" s="15"/>
+      <c r="C167" s="11"/>
+      <c r="D167" s="11"/>
+      <c r="E167" s="11"/>
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B168" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="C168" s="11"/>
-      <c r="D168" s="11"/>
-      <c r="E168" s="11"/>
+      <c r="C168" s="15"/>
+      <c r="D168" s="15"/>
+      <c r="E168" s="15"/>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B169" s="7" t="s">
@@ -9211,17 +9096,17 @@
       <c r="B170" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="C170" s="15"/>
-      <c r="D170" s="15"/>
-      <c r="E170" s="15"/>
+      <c r="C170" s="11"/>
+      <c r="D170" s="11"/>
+      <c r="E170" s="11"/>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B171" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="C171" s="11"/>
-      <c r="D171" s="11"/>
-      <c r="E171" s="11"/>
+      <c r="C171" s="15"/>
+      <c r="D171" s="15"/>
+      <c r="E171" s="15"/>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B172" s="7" t="s">
@@ -9239,57 +9124,9 @@
       <c r="D173" s="11"/>
       <c r="E173" s="11"/>
     </row>
-    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B174" s="7" t="s">
-        <v>361</v>
-      </c>
-      <c r="C174" s="15"/>
-      <c r="D174" s="15"/>
-      <c r="E174" s="15"/>
-    </row>
-    <row r="175" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B175" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="C175" s="11"/>
-      <c r="D175" s="11"/>
-      <c r="E175" s="11"/>
-    </row>
-    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B176" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="C176" s="11"/>
-      <c r="D176" s="11"/>
-      <c r="E176" s="11"/>
-    </row>
-    <row r="177" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B177" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="C177" s="15"/>
-      <c r="D177" s="15"/>
-      <c r="E177" s="15"/>
-    </row>
-    <row r="178" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B178" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="C178" s="11"/>
-      <c r="D178" s="11"/>
-      <c r="E178" s="11"/>
-    </row>
-    <row r="179" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B179" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="C179" s="11"/>
-      <c r="D179" s="11"/>
-      <c r="E179" s="11"/>
-    </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
-  <mergeCells count="127">
+  <mergeCells count="121">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="B5:E5"/>
@@ -9339,14 +9176,12 @@
     <mergeCell ref="C62:E62"/>
     <mergeCell ref="C63:E63"/>
     <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="B86:E86"/>
     <mergeCell ref="C87:E87"/>
     <mergeCell ref="C88:E88"/>
     <mergeCell ref="C89:E89"/>
     <mergeCell ref="C90:E90"/>
     <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C93:E93"/>
     <mergeCell ref="C94:E94"/>
     <mergeCell ref="C95:E95"/>
     <mergeCell ref="C96:E96"/>
@@ -9355,23 +9190,25 @@
     <mergeCell ref="C101:E101"/>
     <mergeCell ref="C102:E102"/>
     <mergeCell ref="C103:E103"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="C105:E105"/>
     <mergeCell ref="C106:E106"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="C108:E108"/>
     <mergeCell ref="C109:E109"/>
     <mergeCell ref="C110:E110"/>
     <mergeCell ref="C111:E111"/>
     <mergeCell ref="C112:E112"/>
-    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="C113:E113"/>
     <mergeCell ref="C116:E116"/>
     <mergeCell ref="C117:E117"/>
     <mergeCell ref="C118:E118"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C121:E121"/>
     <mergeCell ref="C124:E124"/>
     <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="C129:E129"/>
     <mergeCell ref="C130:E130"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="C132:E132"/>
     <mergeCell ref="C133:E133"/>
     <mergeCell ref="C134:E134"/>
     <mergeCell ref="C135:E135"/>
@@ -9380,12 +9217,12 @@
     <mergeCell ref="C138:E138"/>
     <mergeCell ref="C139:E139"/>
     <mergeCell ref="C140:E140"/>
-    <mergeCell ref="C141:E141"/>
-    <mergeCell ref="C142:E142"/>
     <mergeCell ref="C143:E143"/>
     <mergeCell ref="C144:E144"/>
     <mergeCell ref="C145:E145"/>
     <mergeCell ref="C146:E146"/>
+    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="C148:E148"/>
     <mergeCell ref="C149:E149"/>
     <mergeCell ref="C150:E150"/>
     <mergeCell ref="C151:E151"/>
@@ -9411,14 +9248,8 @@
     <mergeCell ref="C171:E171"/>
     <mergeCell ref="C172:E172"/>
     <mergeCell ref="C173:E173"/>
-    <mergeCell ref="C174:E174"/>
-    <mergeCell ref="C175:E175"/>
-    <mergeCell ref="C176:E176"/>
-    <mergeCell ref="C177:E177"/>
-    <mergeCell ref="C178:E178"/>
-    <mergeCell ref="C179:E179"/>
   </mergeCells>
-  <dataValidations count="37">
+  <dataValidations count="33">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Item or amount" prompt="Pick one of your assets from the list, or type an item or an amount." sqref="B68:B73">
       <formula1>'Lists'!$C$2:$C$34</formula1>
     </dataValidation>
@@ -9426,61 +9257,52 @@
       <formula1>'Lists'!$B$2:$B$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C100">
+      <formula1>'Lists'!$AG$2:$AG$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C103">
+      <formula1>'Lists'!$AH$2:$AH$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C109">
+      <formula1>'Lists'!$F$2:$F$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C111">
       <formula1>'Lists'!$AI$2:$AI$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C102">
-      <formula1>'Lists'!$AJ$2:$AJ$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C103">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C112">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C106">
-      <formula1>'Lists'!$AK$2:$AK$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C109">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C116">
+      <formula1>'Lists'!$F$2:$F$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C121">
+      <formula1>'Lists'!$AJ$2:$AJ$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C136">
+      <formula1>'Lists'!$AK$2:$AK$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C137">
       <formula1>'Lists'!$AL$2:$AL$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C115">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C139">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C117">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C143">
       <formula1>'Lists'!$AM$2:$AM$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C118">
-      <formula1>'Lists'!$F$2:$F$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C122">
-      <formula1>'Lists'!$F$2:$F$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C127">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C145">
       <formula1>'Lists'!$AN$2:$AN$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C142">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C146">
       <formula1>'Lists'!$AO$2:$AO$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C143">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C147">
       <formula1>'Lists'!$AP$2:$AP$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C145">
-      <formula1>'Lists'!$F$2:$F$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C149">
-      <formula1>'Lists'!$AQ$2:$AQ$4</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C151">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C166">
+      <formula1>'Lists'!$AQ$2:$AQ$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C173">
       <formula1>'Lists'!$AR$2:$AR$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C152">
-      <formula1>'Lists'!$AS$2:$AS$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C153">
-      <formula1>'Lists'!$AT$2:$AT$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C172">
-      <formula1>'Lists'!$AU$2:$AU$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C179">
-      <formula1>'Lists'!$AV$2:$AV$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C34">
       <formula1>'Lists'!$Y$2:$Y$4</formula1>
@@ -9510,23 +9332,20 @@
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C86">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C87">
       <formula1>'Lists'!$AC$2:$AC$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C87">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C89">
       <formula1>'Lists'!$AD$2:$AD$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C90">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C94">
       <formula1>'Lists'!$AE$2:$AE$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C91">
-      <formula1>'Lists'!$AF$2:$AF$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C93">
-      <formula1>'Lists'!$AG$2:$AG$3</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C95">
-      <formula1>'Lists'!$AH$2:$AH$3</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C96">
+      <formula1>'Lists'!$AF$2:$AF$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C97">
+      <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Name" prompt="Pick a family member from the list, or type any name." sqref="D79:D83">
       <formula1>'Lists'!$B$2:$B$10</formula1>
@@ -9538,6 +9357,9 @@
   <headerFooter>
     <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Fact find&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="63" max="16838" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -9575,12 +9397,12 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -9589,7 +9411,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="32" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="C6" s="33">
         <f>IF('Start here'!$C$19="","Not yet given",'Start here'!$C$19)</f>
@@ -9609,17 +9431,17 @@
         <v>127</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="27" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
       <c r="C10" s="24">
         <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$2)</f>
@@ -9636,7 +9458,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="C11" s="24">
         <f>N('Companies and trusts'!$C$49)+N('Companies and trusts'!$C$94)+N('Companies and trusts'!$C$139)+N('Companies and trusts'!$C$184)</f>
@@ -9653,7 +9475,7 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
       <c r="C12" s="24">
         <f>IF('Companies and trusts'!$C$22="Credit",N('Companies and trusts'!$C$23),0)+IF('Companies and trusts'!$C$68="Credit",N('Companies and trusts'!$C$69),0)+IF('Companies and trusts'!$C$113="Credit",N('Companies and trusts'!$C$114),0)+IF('Companies and trusts'!$C$158="Credit",N('Companies and trusts'!$C$159),0)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
@@ -9670,7 +9492,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="C13" s="24">
         <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
@@ -9687,7 +9509,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C14" s="24">
         <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$2)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
@@ -9704,7 +9526,7 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="35" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
       <c r="C15" s="23">
         <f>C10+C11+C12+C13+C14</f>
@@ -9721,12 +9543,12 @@
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="27" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="C18" s="24">
         <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$2)</f>
@@ -9743,7 +9565,7 @@
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>380</v>
+        <v>374</v>
       </c>
       <c r="C19" s="24">
         <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$2)</f>
@@ -9760,7 +9582,7 @@
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="C20" s="24">
         <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,'Lists'!$A$2)</f>
@@ -9777,7 +9599,7 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="C21" s="24">
         <f>IF('Companies and trusts'!$C$22="Debit",N('Companies and trusts'!$C$23),0)+IF('Companies and trusts'!$C$68="Debit",N('Companies and trusts'!$C$69),0)+IF('Companies and trusts'!$C$113="Debit",N('Companies and trusts'!$C$114),0)+IF('Companies and trusts'!$C$158="Debit",N('Companies and trusts'!$C$159),0)</f>
@@ -9794,7 +9616,7 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="35" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C22" s="23">
         <f>C18+C19+C20+C21</f>
@@ -9811,7 +9633,7 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="36" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="C24" s="37">
         <f>C15-C22</f>
@@ -9828,12 +9650,12 @@
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="27" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="F27" s="24">
         <f>SUMIFS('Companies and trusts'!$D$34:$D$43,'Companies and trusts'!$C$34:$C$43,"Property")+SUMIFS('Companies and trusts'!$D$79:$D$88,'Companies and trusts'!$C$79:$C$88,"Property")+SUMIFS('Companies and trusts'!$D$124:$D$133,'Companies and trusts'!$C$124:$C$133,"Property")+SUMIFS('Companies and trusts'!$D$169:$D$178,'Companies and trusts'!$C$169:$C$178,"Property")</f>
@@ -9841,7 +9663,7 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="F28" s="24">
         <f>SUMIFS('Companies and trusts'!$D$34:$D$43,'Companies and trusts'!$C$34:$C$43,"Bond")+SUMIFS('Companies and trusts'!$D$79:$D$88,'Companies and trusts'!$C$79:$C$88,"Bond")+SUMIFS('Companies and trusts'!$D$124:$D$133,'Companies and trusts'!$C$124:$C$133,"Bond")+SUMIFS('Companies and trusts'!$D$169:$D$178,'Companies and trusts'!$C$169:$C$178,"Bond")+SUMIFS('Companies and trusts'!$D$34:$D$43,'Companies and trusts'!$C$34:$C$43,"Other debt")+SUMIFS('Companies and trusts'!$D$79:$D$88,'Companies and trusts'!$C$79:$C$88,"Other debt")+SUMIFS('Companies and trusts'!$D$124:$D$133,'Companies and trusts'!$C$124:$C$133,"Other debt")+SUMIFS('Companies and trusts'!$D$169:$D$178,'Companies and trusts'!$C$169:$C$178,"Other debt")</f>
@@ -9849,12 +9671,12 @@
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" s="27" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="F31" s="19">
         <f>COUNTIF('Assets and debts'!$P$12:$P$19,"Estimate")+COUNTIF('Assets and debts'!$J$26:$J$31,"Estimate")+COUNTIF('Assets and debts'!$J$38:$J$52,"Estimate")+COUNTIF('Assets and debts'!$I$59:$I$70,"Estimate")+COUNTIF('Companies and trusts'!$C$14,"Estimate")+COUNTIF('Companies and trusts'!$C$60,"Estimate")+COUNTIF('Companies and trusts'!$C$105,"Estimate")+COUNTIF('Companies and trusts'!$C$150,"Estimate")+COUNTIF('Companies and trusts'!$F$34:$F$43,"Estimate")+COUNTIF('Companies and trusts'!$F$79:$F$88,"Estimate")+COUNTIF('Companies and trusts'!$F$124:$F$133,"Estimate")+COUNTIF('Companies and trusts'!$F$169:$F$178,"Estimate")</f>
@@ -9862,7 +9684,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="F32" s="19">
         <f>SUMPRODUCT(('Assets and debts'!$D$12:$D$19&gt;0)*('Assets and debts'!$F$12:$F$19=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Shares / Unit Trusts")*('Assets and debts'!$F$38:$F$52=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Business Interest")*('Assets and debts'!$F$38:$F$52=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Crypto")*('Assets and debts'!$F$38:$F$52=""))+IF(AND(N('Companies and trusts'!$C$21)&gt;0,'Companies and trusts'!$C$24=""),1,0)+IF(AND(N('Companies and trusts'!$D$21)&gt;0,'Companies and trusts'!$D$24=""),1,0)+IF(AND(N('Companies and trusts'!$C$67)&gt;0,'Companies and trusts'!$C$70=""),1,0)+IF(AND(N('Companies and trusts'!$D$67)&gt;0,'Companies and trusts'!$D$70=""),1,0)+IF(AND(N('Companies and trusts'!$C$112)&gt;0,'Companies and trusts'!$C$115=""),1,0)+IF(AND(N('Companies and trusts'!$D$112)&gt;0,'Companies and trusts'!$D$115=""),1,0)+IF(AND(N('Companies and trusts'!$C$157)&gt;0,'Companies and trusts'!$C$160=""),1,0)+IF(AND(N('Companies and trusts'!$D$157)&gt;0,'Companies and trusts'!$D$160=""),1,0)+SUMPRODUCT(('Companies and trusts'!$D$34:$D$43&gt;0)*('Companies and trusts'!$C$34:$C$43="Property")*('Companies and trusts'!$E$34:$E$43=""))+SUMPRODUCT(('Companies and trusts'!$D$79:$D$88&gt;0)*('Companies and trusts'!$C$79:$C$88="Property")*('Companies and trusts'!$E$79:$E$88=""))+SUMPRODUCT(('Companies and trusts'!$D$124:$D$133&gt;0)*('Companies and trusts'!$C$124:$C$133="Property")*('Companies and trusts'!$E$124:$E$133=""))+SUMPRODUCT(('Companies and trusts'!$D$169:$D$178&gt;0)*('Companies and trusts'!$C$169:$C$178="Property")*('Companies and trusts'!$E$169:$E$178=""))</f>

--- a/Duwalcoe_Fact_Find_Template.xlsx
+++ b/Duwalcoe_Fact_Find_Template.xlsx
@@ -5,49 +5,52 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="2" name="Start here" state="visible" r:id="rId4"/>
-    <sheet sheetId="3" name="Client and family" state="visible" r:id="rId5"/>
-    <sheet sheetId="4" name="Income and expenses" state="visible" r:id="rId6"/>
-    <sheet sheetId="5" name="Assets and debts" state="visible" r:id="rId7"/>
-    <sheet sheetId="6" name="Companies and trusts" state="visible" r:id="rId8"/>
-    <sheet sheetId="7" name="Needs" state="visible" r:id="rId9"/>
-    <sheet sheetId="8" name="Will" state="visible" r:id="rId10"/>
-    <sheet sheetId="9" name="Summary" state="visible" r:id="rId11"/>
-    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId12"/>
+    <sheet sheetId="3" name="Meeting notes" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="Client and family" state="visible" r:id="rId6"/>
+    <sheet sheetId="5" name="Income and expenses" state="visible" r:id="rId7"/>
+    <sheet sheetId="6" name="Assets and debts" state="visible" r:id="rId8"/>
+    <sheet sheetId="7" name="Companies and trusts" state="visible" r:id="rId9"/>
+    <sheet sheetId="8" name="Needs" state="visible" r:id="rId10"/>
+    <sheet sheetId="9" name="Will" state="visible" r:id="rId11"/>
+    <sheet sheetId="10" name="Summary" state="visible" r:id="rId12"/>
+    <sheet sheetId="1" name="Lists" state="veryHidden" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="FF_C_Title">'Client and family'!$C$9</definedName>
-    <definedName name="FF_C_Name">'Client and family'!$C$10</definedName>
-    <definedName name="FF_S_SpouseName">'Client and family'!$D$10</definedName>
-    <definedName name="FF_C_CallingName">'Client and family'!$C$11</definedName>
-    <definedName name="FF_C_IDNumber">'Client and family'!$C$12</definedName>
-    <definedName name="FF_S_SpouseIDNumber">'Client and family'!$D$12</definedName>
-    <definedName name="FF_C_DOB">'Client and family'!$C$14</definedName>
-    <definedName name="FF_S_SpouseDOB">'Client and family'!$D$14</definedName>
-    <definedName name="FF_C_Gender">'Client and family'!$C$15</definedName>
-    <definedName name="FF_C_Smoker">'Client and family'!$C$16</definedName>
-    <definedName name="FF_C_Cell">'Client and family'!$C$17</definedName>
-    <definedName name="FF_S_SpouseCell">'Client and family'!$D$17</definedName>
-    <definedName name="FF_C_Email">'Client and family'!$C$18</definedName>
-    <definedName name="FF_S_SpouseEmail">'Client and family'!$D$18</definedName>
-    <definedName name="FF_C_TelHome">'Client and family'!$C$19</definedName>
-    <definedName name="FF_C_TelWork">'Client and family'!$C$20</definedName>
-    <definedName name="FF_C_Address">'Client and family'!$C$21</definedName>
-    <definedName name="FF_C_POBox">'Client and family'!$C$22</definedName>
-    <definedName name="FF_C_Occupation">'Client and family'!$C$23</definedName>
-    <definedName name="FF_S_SpouseOccupation">'Client and family'!$D$23</definedName>
-    <definedName name="FF_C_Employer">'Client and family'!$C$24</definedName>
-    <definedName name="FF_C_Income">'Client and family'!$C$25</definedName>
-    <definedName name="FF_S_SpouseIncome">'Client and family'!$D$25</definedName>
-    <definedName name="FF_S_SpouseWorks">'Client and family'!$D$26</definedName>
-    <definedName name="FF_C_TaxNo">'Client and family'!$C$27</definedName>
-    <definedName name="FF_C_Education">'Client and family'!$C$28</definedName>
-    <definedName name="FF_C_Qualification">'Client and family'!$C$29</definedName>
-    <definedName name="FF_C_MaritalStatus">'Client and family'!$C$30</definedName>
-    <definedName name="FF_C_Anniversary">'Client and family'!$C$31</definedName>
-    <definedName name="FF_C_IsLead">'Client and family'!$C$32</definedName>
-    <definedName name="FF_K_kids">'Client and family'!$B$36:$Z$36</definedName>
-    <definedName name="FF_T_kids">'Client and family'!$B$38:$Z$45</definedName>
-    <definedName name="FF_W_dep_notes">'Client and family'!$C$49</definedName>
+    <definedName name="FF_C_FirstNames">'Client and family'!$C$10</definedName>
+    <definedName name="FF_S_SpouseFirstNames">'Client and family'!$D$10</definedName>
+    <definedName name="FF_C_Surname">'Client and family'!$C$11</definedName>
+    <definedName name="FF_S_SpouseSurname">'Client and family'!$D$11</definedName>
+    <definedName name="FF_C_CallingName">'Client and family'!$C$12</definedName>
+    <definedName name="FF_C_IDNumber">'Client and family'!$C$13</definedName>
+    <definedName name="FF_S_SpouseIDNumber">'Client and family'!$D$13</definedName>
+    <definedName name="FF_C_DOB">'Client and family'!$C$16</definedName>
+    <definedName name="FF_S_SpouseDOB">'Client and family'!$D$16</definedName>
+    <definedName name="FF_C_Gender">'Client and family'!$C$17</definedName>
+    <definedName name="FF_C_Smoker">'Client and family'!$C$18</definedName>
+    <definedName name="FF_C_Cell">'Client and family'!$C$19</definedName>
+    <definedName name="FF_S_SpouseCell">'Client and family'!$D$19</definedName>
+    <definedName name="FF_C_Email">'Client and family'!$C$20</definedName>
+    <definedName name="FF_S_SpouseEmail">'Client and family'!$D$20</definedName>
+    <definedName name="FF_C_TelHome">'Client and family'!$C$21</definedName>
+    <definedName name="FF_C_TelWork">'Client and family'!$C$22</definedName>
+    <definedName name="FF_C_Address">'Client and family'!$C$23</definedName>
+    <definedName name="FF_C_POBox">'Client and family'!$C$24</definedName>
+    <definedName name="FF_C_Occupation">'Client and family'!$C$25</definedName>
+    <definedName name="FF_S_SpouseOccupation">'Client and family'!$D$25</definedName>
+    <definedName name="FF_C_Employer">'Client and family'!$C$26</definedName>
+    <definedName name="FF_C_Income">'Client and family'!$C$27</definedName>
+    <definedName name="FF_S_SpouseIncome">'Client and family'!$D$27</definedName>
+    <definedName name="FF_S_SpouseWorks">'Client and family'!$D$28</definedName>
+    <definedName name="FF_C_TaxNo">'Client and family'!$C$29</definedName>
+    <definedName name="FF_C_Education">'Client and family'!$C$30</definedName>
+    <definedName name="FF_C_Qualification">'Client and family'!$C$31</definedName>
+    <definedName name="FF_C_MaritalStatus">'Client and family'!$C$32</definedName>
+    <definedName name="FF_C_Anniversary">'Client and family'!$C$33</definedName>
+    <definedName name="FF_C_IsLead">'Client and family'!$C$34</definedName>
+    <definedName name="FF_K_kids">'Client and family'!$B$38:$Z$38</definedName>
+    <definedName name="FF_T_kids">'Client and family'!$B$40:$Z$47</definedName>
+    <definedName name="FF_W_dep_notes">'Client and family'!$C$51</definedName>
     <definedName name="FF_M_ClientID">Lists!$Z$1</definedName>
     <definedName name="FF_M_ClientName">Lists!$Z$2</definedName>
     <definedName name="FF_M_Version">Lists!$Z$3</definedName>
@@ -57,6 +60,8 @@
     <definedName name="FF_G_ValDate">'Start here'!$C$19</definedName>
     <definedName name="FF_G_CompletedBy">'Start here'!$C$20</definedName>
     <definedName name="FF_G_DateCompleted">'Start here'!$C$21</definedName>
+    <definedName name="FF_K_notes">'Meeting notes'!$B$7:$Z$7</definedName>
+    <definedName name="FF_T_notes">'Meeting notes'!$B$9:$Z$44</definedName>
     <definedName name="FF_K_income">'Income and expenses'!$B$8:$Z$8</definedName>
     <definedName name="FF_T_income">'Income and expenses'!$B$11:$Z$20</definedName>
     <definedName name="FF_K_expense">'Income and expenses'!$B$25:$Z$25</definedName>
@@ -297,27 +302,29 @@
     <definedName name="FF_M_Breaks">Lists!$Z$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Start here'!$A1:$F22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Start here'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Client and family'!$A1:$G50</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Client and family'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Income and expenses'!$A1:$H49</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Income and expenses'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Assets and debts'!$A1:$Q72</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Assets and debts'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Companies and trusts'!$A1:$G188</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Companies and trusts'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Needs'!$A1:$J24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Needs'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Will'!$A1:$E174</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Will'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Summary'!$A1:$F35</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Summary'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Meeting notes'!$A1:$C44</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Meeting notes'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Client and family'!$A1:$G52</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Client and family'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Income and expenses'!$A1:$H49</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Income and expenses'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Assets and debts'!$A1:$Q72</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Assets and debts'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Companies and trusts'!$A1:$G188</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Companies and trusts'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Needs'!$A1:$J24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Needs'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Will'!$A1:$E174</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Will'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'Summary'!$A1:$F35</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="8">'Summary'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="557">
   <si>
     <t>Duwalcoe Financial Consultants CC</t>
   </si>
@@ -367,6 +374,27 @@
     <t>Date completed</t>
   </si>
   <si>
+    <t>Meeting notes</t>
+  </si>
+  <si>
+    <t>Type a note and press Enter to go to the next line. Tidy them into the other sheets afterwards, or leave them here: they are added to the client's notes in the CRM.</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>topic</t>
+  </si>
+  <si>
+    <t>_id</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Topic (optional)</t>
+  </si>
+  <si>
     <t>Client and family</t>
   </si>
   <si>
@@ -382,99 +410,105 @@
     <t>Title</t>
   </si>
   <si>
+    <t>First names</t>
+  </si>
+  <si>
+    <t>Surname</t>
+  </si>
+  <si>
+    <t>Calling name (what we call you)</t>
+  </si>
+  <si>
+    <t>SA ID number</t>
+  </si>
+  <si>
+    <t>ID number check</t>
+  </si>
+  <si>
+    <t>Date of birth (worked out from a valid ID, or as typed below)</t>
+  </si>
+  <si>
+    <t>Date of birth (only if no valid SA ID number)</t>
+  </si>
+  <si>
+    <t>Gender (only if no valid SA ID number)</t>
+  </si>
+  <si>
+    <t>Smoker</t>
+  </si>
+  <si>
+    <t>Cell</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Home telephone</t>
+  </si>
+  <si>
+    <t>Work telephone</t>
+  </si>
+  <si>
+    <t>Physical address</t>
+  </si>
+  <si>
+    <t>Postal address</t>
+  </si>
+  <si>
+    <t>Occupation</t>
+  </si>
+  <si>
+    <t>Employer</t>
+  </si>
+  <si>
+    <t>Gross income a month (R): salary and business income from the Income sheet</t>
+  </si>
+  <si>
+    <t>Working?</t>
+  </si>
+  <si>
+    <t>Tax number</t>
+  </si>
+  <si>
+    <t>Highest education</t>
+  </si>
+  <si>
+    <t>Qualification</t>
+  </si>
+  <si>
+    <t>Marital status and regime</t>
+  </si>
+  <si>
+    <t>Wedding anniversary</t>
+  </si>
+  <si>
+    <t>Lead or client</t>
+  </si>
+  <si>
+    <t>2. Children and other family members</t>
+  </si>
+  <si>
+    <t>Your children first, then anyone else in the family. Your spouse goes above, not here.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>IDNumber</t>
+  </si>
+  <si>
+    <t>DOB</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Dependent</t>
+  </si>
+  <si>
     <t>Full names</t>
   </si>
   <si>
-    <t>Calling name (what we call you)</t>
-  </si>
-  <si>
-    <t>SA ID number</t>
-  </si>
-  <si>
-    <t>Date of birth (worked out from the ID, or as typed below)</t>
-  </si>
-  <si>
-    <t>Date of birth (only if no SA ID number)</t>
-  </si>
-  <si>
-    <t>Gender (only if no SA ID number)</t>
-  </si>
-  <si>
-    <t>Smoker</t>
-  </si>
-  <si>
-    <t>Cell</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>Home telephone</t>
-  </si>
-  <si>
-    <t>Work telephone</t>
-  </si>
-  <si>
-    <t>Physical address</t>
-  </si>
-  <si>
-    <t>Postal address</t>
-  </si>
-  <si>
-    <t>Occupation</t>
-  </si>
-  <si>
-    <t>Employer</t>
-  </si>
-  <si>
-    <t>Gross income a month (R)</t>
-  </si>
-  <si>
-    <t>Working?</t>
-  </si>
-  <si>
-    <t>Tax number</t>
-  </si>
-  <si>
-    <t>Highest education</t>
-  </si>
-  <si>
-    <t>Qualification</t>
-  </si>
-  <si>
-    <t>Marital status and regime</t>
-  </si>
-  <si>
-    <t>Wedding anniversary</t>
-  </si>
-  <si>
-    <t>Lead or client</t>
-  </si>
-  <si>
-    <t>2. Children and other family members</t>
-  </si>
-  <si>
-    <t>Your children first, then anyone else in the family. Your spouse goes above, not here.</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>IDNumber</t>
-  </si>
-  <si>
-    <t>DOB</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Dependent</t>
-  </si>
-  <si>
-    <t>_id</t>
-  </si>
-  <si>
     <t>Date of birth (if no SA ID)</t>
   </si>
   <si>
@@ -502,7 +536,7 @@
     <t>1. Income</t>
   </si>
   <si>
-    <t>Every regular income, before tax. One row per source.</t>
+    <t>Every regular income before tax, one row per source, including your salary or business income. The gross income on the Client and family sheet adds up the Salary and Business Income rows.</t>
   </si>
   <si>
     <t>desc</t>
@@ -1528,15 +1562,21 @@
     <t>holdKind</t>
   </si>
   <si>
+    <t>earned</t>
+  </si>
+  <si>
     <t>passes</t>
   </si>
   <si>
-    <t>forWhom</t>
+    <t>full names</t>
   </si>
   <si>
     <t>ClientID</t>
   </si>
   <si>
+    <t>w_e_status</t>
+  </si>
+  <si>
     <t>w_tr_choice</t>
   </si>
   <si>
@@ -1633,6 +1673,9 @@
     <t>ClientName</t>
   </si>
   <si>
+    <t>I do not have an existing will</t>
+  </si>
+  <si>
     <t>Yes — establish a testamentary trust</t>
   </si>
   <si>
@@ -1711,16 +1754,19 @@
     <t>Bond</t>
   </si>
   <si>
+    <t>Business Income</t>
+  </si>
+  <si>
     <t>Disability</t>
   </si>
   <si>
-    <t>Once-off capital</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>1.1</t>
+    <t>1.2</t>
+  </si>
+  <si>
+    <t>No — distribute directly</t>
   </si>
   <si>
     <t>Trustees may pay capital sooner for education, medical, first home, etc.</t>
@@ -1801,6 +1847,9 @@
     <t>ExportedAt</t>
   </si>
   <si>
+    <t>I have a codicil / amendment to a prior will</t>
+  </si>
+  <si>
     <t>Only if beneficiaries are still minors at date of death</t>
   </si>
   <si>
@@ -1835,9 +1884,6 @@
   </si>
   <si>
     <t>Dependant</t>
-  </si>
-  <si>
-    <t>Business Income</t>
   </si>
   <si>
     <t>School / university fees</t>
@@ -2110,7 +2156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
@@ -2158,25 +2204,28 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="12" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2557,702 +2606,711 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AR34"/>
+  <dimension ref="A1:AS34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B1" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="C1" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D1" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="E1" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="F1" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="G1" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="H1" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="I1" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="J1" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="K1" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="L1" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="M1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="N1" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="O1" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="P1" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="Q1" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="R1" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="S1" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="T1" t="s">
-        <v>110</v>
+        <v>412</v>
       </c>
       <c r="U1" t="s">
-        <v>403</v>
+        <v>119</v>
       </c>
       <c r="V1" t="s">
-        <v>208</v>
+        <v>413</v>
       </c>
       <c r="W1" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="X1" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="Y1" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="Z1" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="AA1" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="AB1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="AC1" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="AD1" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AE1" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="AF1" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="AG1" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="AH1" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="AI1" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="AJ1" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="AK1" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="AL1" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="AM1" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="AN1" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="AO1" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="AP1" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="AQ1" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="AR1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+        <v>434</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2">
-        <f>IF('Client and family'!$C$11&lt;&gt;"",'Client and family'!$C$11,IF('Client and family'!$C$10&lt;&gt;"",LEFT(TRIM('Client and family'!$C$10),FIND(" ",TRIM('Client and family'!$C$10)&amp;" ")-1),"Client"))</f>
+        <f>IF('Client and family'!$C$12&lt;&gt;"",'Client and family'!$C$12,IF('Lists'!$X$2&lt;&gt;"",LEFT(TRIM('Lists'!$X$2),FIND(" ",TRIM('Lists'!$X$2)&amp;" ")-1),"Client"))</f>
       </c>
       <c r="B2">
-        <f>IF('Client and family'!$D$10="","",'Client and family'!$D$10)</f>
+        <f>IF('Lists'!$X$3="","",'Lists'!$X$3)</f>
       </c>
       <c r="C2">
         <f>IF('Assets and debts'!$B$12="",""," "&amp;'Assets and debts'!$B$12)</f>
       </c>
       <c r="D2" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="E2" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="F2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="H2" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="I2" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="J2" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="K2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="L2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="M2" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="N2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="O2" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="P2" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="Q2" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="R2" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="S2" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="T2" t="s">
-        <v>436</v>
+        <v>85</v>
       </c>
       <c r="U2" t="s">
-        <v>128</v>
+        <v>447</v>
       </c>
       <c r="V2" t="s">
-        <v>223</v>
+        <v>137</v>
       </c>
       <c r="W2" t="s">
-        <v>224</v>
-      </c>
-      <c r="X2" t="s">
-        <v>128</v>
+        <v>232</v>
+      </c>
+      <c r="X2">
+        <f>TRIM('Client and family'!$C$10&amp;" "&amp;'Client and family'!$C$11)</f>
       </c>
       <c r="Y2" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="Z2" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="AA2" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="AB2" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="AC2" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="AD2" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="AE2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AF2" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="AG2" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="AH2" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="AI2" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="AJ2" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="AK2" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="AL2" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="AM2" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="AN2" t="s">
-        <v>77</v>
+        <v>461</v>
       </c>
       <c r="AO2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AP2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AQ2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AR2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f>IF('Client and family'!$D$10&lt;&gt;"",LEFT(TRIM('Client and family'!$D$10),FIND(" ",TRIM('Client and family'!$D$10)&amp;" ")-1),"Spouse")</f>
+        <f>IF('Lists'!$X$3&lt;&gt;"",LEFT(TRIM('Lists'!$X$3),FIND(" ",TRIM('Lists'!$X$3)&amp;" ")-1),"Spouse")</f>
       </c>
       <c r="B3">
-        <f>IF('Client and family'!$B$38="","",'Client and family'!$B$38)</f>
+        <f>IF('Client and family'!$B$40="","",'Client and family'!$B$40)</f>
       </c>
       <c r="C3">
         <f>IF('Assets and debts'!$B$13="",""," "&amp;'Assets and debts'!$B$13)</f>
       </c>
       <c r="D3" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="E3" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="G3" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="H3" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="I3" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="J3" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="K3" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="L3" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="M3" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="N3" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="O3" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="P3" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="Q3" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="R3" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="S3" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="T3" t="s">
-        <v>149</v>
+        <v>476</v>
       </c>
       <c r="U3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="V3" t="s">
-        <v>464</v>
+        <v>157</v>
       </c>
       <c r="W3" t="s">
-        <v>465</v>
-      </c>
-      <c r="X3" t="s">
-        <v>148</v>
+        <v>477</v>
+      </c>
+      <c r="X3">
+        <f>TRIM('Client and family'!$D$10&amp;" "&amp;'Client and family'!$D$11)</f>
       </c>
       <c r="Y3" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="Z3" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="AA3" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="AB3" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="AC3" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="AD3" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="AE3" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="AF3" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="AG3" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="AH3" t="s">
-        <v>435</v>
+        <v>487</v>
       </c>
       <c r="AI3" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="AJ3" t="s">
-        <v>129</v>
+        <v>488</v>
       </c>
       <c r="AK3" t="s">
-        <v>476</v>
+        <v>138</v>
       </c>
       <c r="AL3" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="AM3" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="AN3" t="s">
-        <v>129</v>
+        <v>491</v>
       </c>
       <c r="AO3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AP3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AQ3" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="AR3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B4">
-        <f>IF('Client and family'!$B$39="","",'Client and family'!$B$39)</f>
+        <f>IF('Client and family'!$B$41="","",'Client and family'!$B$41)</f>
       </c>
       <c r="C4">
         <f>IF('Assets and debts'!$B$14="",""," "&amp;'Assets and debts'!$B$14)</f>
       </c>
       <c r="D4" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="H4" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="I4" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="J4" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="K4" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="L4" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="M4" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
       <c r="N4" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="O4" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
       <c r="P4" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="Q4" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="R4" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="S4" t="s">
-        <v>491</v>
-      </c>
-      <c r="T4" t="s">
-        <v>194</v>
+        <v>504</v>
       </c>
       <c r="U4" t="s">
-        <v>122</v>
+        <v>203</v>
       </c>
       <c r="V4" t="s">
-        <v>492</v>
-      </c>
-      <c r="X4" t="s">
-        <v>122</v>
+        <v>131</v>
+      </c>
+      <c r="W4" t="s">
+        <v>505</v>
       </c>
       <c r="Y4" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
       <c r="Z4" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="AA4" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="AB4" t="s">
-        <v>496</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>497</v>
+        <v>509</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>510</v>
       </c>
       <c r="AF4" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="AG4" t="s">
-        <v>499</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>500</v>
-      </c>
-      <c r="AM4" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="5" spans="2:28" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>513</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>514</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="5" spans="2:29" x14ac:dyDescent="0.25">
       <c r="B5">
-        <f>IF('Client and family'!$B$40="","",'Client and family'!$B$40)</f>
+        <f>IF('Client and family'!$B$42="","",'Client and family'!$B$42)</f>
       </c>
       <c r="C5">
         <f>IF('Assets and debts'!$B$15="",""," "&amp;'Assets and debts'!$B$15)</f>
       </c>
       <c r="D5" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="H5" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="I5" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="J5" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="K5" t="s">
-        <v>506</v>
+        <v>476</v>
       </c>
       <c r="L5" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
       <c r="M5" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="N5" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="O5" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="Q5" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="S5" t="s">
-        <v>512</v>
-      </c>
-      <c r="T5" t="s">
-        <v>130</v>
-      </c>
-      <c r="V5" t="s">
-        <v>513</v>
+        <v>525</v>
+      </c>
+      <c r="U5" t="s">
+        <v>139</v>
+      </c>
+      <c r="W5" t="s">
+        <v>526</v>
       </c>
       <c r="Y5" t="s">
-        <v>514</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="6" spans="2:22" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B6">
-        <f>IF('Client and family'!$B$41="","",'Client and family'!$B$41)</f>
+        <f>IF('Client and family'!$B$43="","",'Client and family'!$B$43)</f>
       </c>
       <c r="C6">
         <f>IF('Assets and debts'!$B$16="",""," "&amp;'Assets and debts'!$B$16)</f>
       </c>
       <c r="D6" t="s">
-        <v>516</v>
+        <v>529</v>
       </c>
       <c r="H6" t="s">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="I6" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="J6" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="K6" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="L6" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="M6" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="N6" t="s">
-        <v>522</v>
+        <v>535</v>
       </c>
       <c r="O6" t="s">
-        <v>523</v>
-      </c>
-      <c r="V6" t="s">
-        <v>488</v>
+        <v>536</v>
+      </c>
+      <c r="W6" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B7">
-        <f>IF('Client and family'!$B$42="","",'Client and family'!$B$42)</f>
+        <f>IF('Client and family'!$B$44="","",'Client and family'!$B$44)</f>
       </c>
       <c r="C7">
         <f>IF('Assets and debts'!$B$17="",""," "&amp;'Assets and debts'!$B$17)</f>
       </c>
       <c r="D7" t="s">
-        <v>524</v>
+        <v>537</v>
       </c>
       <c r="H7" t="s">
-        <v>525</v>
+        <v>538</v>
       </c>
       <c r="I7" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="K7" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="L7" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="M7" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="N7" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="O7" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="Y7" t="s">
-        <v>530</v>
+        <v>543</v>
       </c>
       <c r="Z7" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B8">
-        <f>IF('Client and family'!$B$43="","",'Client and family'!$B$43)</f>
+        <f>IF('Client and family'!$B$45="","",'Client and family'!$B$45)</f>
       </c>
       <c r="C8">
         <f>IF('Assets and debts'!$B$18="",""," "&amp;'Assets and debts'!$B$18)</f>
       </c>
       <c r="D8" t="s">
-        <v>531</v>
+        <v>544</v>
       </c>
       <c r="H8" t="s">
-        <v>532</v>
+        <v>545</v>
       </c>
       <c r="K8" t="s">
-        <v>533</v>
+        <v>546</v>
       </c>
       <c r="L8" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="M8" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="N8" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="Y8" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="Z8" t="s">
-        <v>538</v>
+        <v>551</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9">
-        <f>IF('Client and family'!$B$44="","",'Client and family'!$B$44)</f>
+        <f>IF('Client and family'!$B$46="","",'Client and family'!$B$46)</f>
       </c>
       <c r="C9">
         <f>IF('Assets and debts'!$B$19="",""," "&amp;'Assets and debts'!$B$19)</f>
       </c>
       <c r="D9" t="s">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="H9" t="s">
-        <v>540</v>
+        <v>553</v>
       </c>
       <c r="K9" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="L9" t="s">
-        <v>541</v>
+        <v>554</v>
       </c>
       <c r="M9" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="N9" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10">
-        <f>IF('Client and family'!$B$45="","",'Client and family'!$B$45)</f>
+        <f>IF('Client and family'!$B$47="","",'Client and family'!$B$47)</f>
       </c>
       <c r="C10">
         <f>IF('Assets and debts'!$B$26="",""," "&amp;'Assets and debts'!$B$26)</f>
       </c>
       <c r="L10" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="M10" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="N10" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
     </row>
     <row r="11" spans="3:3" x14ac:dyDescent="0.25">
@@ -3379,6 +3437,359 @@
   <sheetProtection sheet="1" formatRows="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:F34"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="52" customWidth="1"/>
+    <col min="3" max="6" width="18" customWidth="1"/>
+    <col min="26" max="26" width="18" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21.75" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="33" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" s="34">
+        <f>IF('Start here'!$C$19="","Not yet given",'Start here'!$C$19)</f>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="35">
+        <f>'Lists'!$A$2</f>
+      </c>
+      <c r="D8" s="35">
+        <f>'Lists'!$A$3</f>
+      </c>
+      <c r="E8" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="F8" s="35" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="28" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C10" s="19">
+        <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$2)</f>
+      </c>
+      <c r="D10" s="19">
+        <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$3)</f>
+      </c>
+      <c r="E10" s="19">
+        <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,"Joint")</f>
+      </c>
+      <c r="F10" s="19">
+        <f>SUM(C10:E10)</f>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C11" s="19">
+        <f>N('Companies and trusts'!$C$49)+N('Companies and trusts'!$C$94)+N('Companies and trusts'!$C$139)+N('Companies and trusts'!$C$184)</f>
+      </c>
+      <c r="D11" s="19">
+        <f>N('Companies and trusts'!$D$49)+N('Companies and trusts'!$D$94)+N('Companies and trusts'!$D$139)+N('Companies and trusts'!$D$184)</f>
+      </c>
+      <c r="E11" s="19">
+        <v>0</v>
+      </c>
+      <c r="F11" s="19">
+        <f>SUM(C11:E11)</f>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="19">
+        <f>IF('Companies and trusts'!$C$22="Credit",N('Companies and trusts'!$C$23),0)+IF('Companies and trusts'!$C$68="Credit",N('Companies and trusts'!$C$69),0)+IF('Companies and trusts'!$C$113="Credit",N('Companies and trusts'!$C$114),0)+IF('Companies and trusts'!$C$158="Credit",N('Companies and trusts'!$C$159),0)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
+      </c>
+      <c r="D12" s="19">
+        <f>IF('Companies and trusts'!$D$22="Credit",N('Companies and trusts'!$D$23),0)+IF('Companies and trusts'!$D$68="Credit",N('Companies and trusts'!$D$69),0)+IF('Companies and trusts'!$D$113="Credit",N('Companies and trusts'!$D$114),0)+IF('Companies and trusts'!$D$158="Credit",N('Companies and trusts'!$D$159),0)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$3,'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
+      </c>
+      <c r="E12" s="19">
+        <f>SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,"Joint",'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
+      </c>
+      <c r="F12" s="19">
+        <f>SUM(C12:E12)</f>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C13" s="19">
+        <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
+      </c>
+      <c r="D13" s="19">
+        <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$3,'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
+      </c>
+      <c r="E13" s="19">
+        <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,"Joint",'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
+      </c>
+      <c r="F13" s="19">
+        <f>SUM(C13:E13)</f>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="C14" s="19">
+        <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$2)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
+      </c>
+      <c r="D14" s="19">
+        <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$3)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$3,'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
+      </c>
+      <c r="E14" s="19">
+        <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,"Joint")+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,"Joint",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
+      </c>
+      <c r="F14" s="19">
+        <f>SUM(C14:E14)</f>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="36" t="s">
+        <v>380</v>
+      </c>
+      <c r="C15" s="25">
+        <f>C10+C11+C12+C13+C14</f>
+      </c>
+      <c r="D15" s="25">
+        <f>D10+D11+D12+D13+D14</f>
+      </c>
+      <c r="E15" s="25">
+        <f>E10+E11+E12+E13+E14</f>
+      </c>
+      <c r="F15" s="25">
+        <f>SUM(C15:E15)</f>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="C18" s="19">
+        <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$2)</f>
+      </c>
+      <c r="D18" s="19">
+        <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$3)</f>
+      </c>
+      <c r="E18" s="19">
+        <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,"Joint")</f>
+      </c>
+      <c r="F18" s="19">
+        <f>SUM(C18:E18)</f>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C19" s="19">
+        <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$2)</f>
+      </c>
+      <c r="D19" s="19">
+        <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$3)</f>
+      </c>
+      <c r="E19" s="19">
+        <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,"Joint")</f>
+      </c>
+      <c r="F19" s="19">
+        <f>SUM(C19:E19)</f>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="C20" s="19">
+        <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,'Lists'!$A$2)</f>
+      </c>
+      <c r="D20" s="19">
+        <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,'Lists'!$A$3)</f>
+      </c>
+      <c r="E20" s="19">
+        <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,"Joint")</f>
+      </c>
+      <c r="F20" s="19">
+        <f>SUM(C20:E20)</f>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="C21" s="19">
+        <f>IF('Companies and trusts'!$C$22="Debit",N('Companies and trusts'!$C$23),0)+IF('Companies and trusts'!$C$68="Debit",N('Companies and trusts'!$C$69),0)+IF('Companies and trusts'!$C$113="Debit",N('Companies and trusts'!$C$114),0)+IF('Companies and trusts'!$C$158="Debit",N('Companies and trusts'!$C$159),0)</f>
+      </c>
+      <c r="D21" s="19">
+        <f>IF('Companies and trusts'!$D$22="Debit",N('Companies and trusts'!$D$23),0)+IF('Companies and trusts'!$D$68="Debit",N('Companies and trusts'!$D$69),0)+IF('Companies and trusts'!$D$113="Debit",N('Companies and trusts'!$D$114),0)+IF('Companies and trusts'!$D$158="Debit",N('Companies and trusts'!$D$159),0)</f>
+      </c>
+      <c r="E21" s="19">
+        <v>0</v>
+      </c>
+      <c r="F21" s="19">
+        <f>SUM(C21:E21)</f>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="36" t="s">
+        <v>386</v>
+      </c>
+      <c r="C22" s="25">
+        <f>C18+C19+C20+C21</f>
+      </c>
+      <c r="D22" s="25">
+        <f>D18+D19+D20+D21</f>
+      </c>
+      <c r="E22" s="25">
+        <f>E18+E19+E20+E21</f>
+      </c>
+      <c r="F22" s="25">
+        <f>SUM(C22:E22)</f>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="37" t="s">
+        <v>387</v>
+      </c>
+      <c r="C24" s="38">
+        <f>C15-C22</f>
+      </c>
+      <c r="D24" s="38">
+        <f>D15-D22</f>
+      </c>
+      <c r="E24" s="38">
+        <f>E15-E22</f>
+      </c>
+      <c r="F24" s="38">
+        <f>SUM(C24:E24)</f>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="F27" s="19">
+        <f>SUMIFS('Companies and trusts'!$D$34:$D$43,'Companies and trusts'!$C$34:$C$43,"Property")+SUMIFS('Companies and trusts'!$D$79:$D$88,'Companies and trusts'!$C$79:$C$88,"Property")+SUMIFS('Companies and trusts'!$D$124:$D$133,'Companies and trusts'!$C$124:$C$133,"Property")+SUMIFS('Companies and trusts'!$D$169:$D$178,'Companies and trusts'!$C$169:$C$178,"Property")</f>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F28" s="19">
+        <f>SUMIFS('Companies and trusts'!$D$34:$D$43,'Companies and trusts'!$C$34:$C$43,"Bond")+SUMIFS('Companies and trusts'!$D$79:$D$88,'Companies and trusts'!$C$79:$C$88,"Bond")+SUMIFS('Companies and trusts'!$D$124:$D$133,'Companies and trusts'!$C$124:$C$133,"Bond")+SUMIFS('Companies and trusts'!$D$169:$D$178,'Companies and trusts'!$C$169:$C$178,"Bond")+SUMIFS('Companies and trusts'!$D$34:$D$43,'Companies and trusts'!$C$34:$C$43,"Other debt")+SUMIFS('Companies and trusts'!$D$79:$D$88,'Companies and trusts'!$C$79:$C$88,"Other debt")+SUMIFS('Companies and trusts'!$D$124:$D$133,'Companies and trusts'!$C$124:$C$133,"Other debt")+SUMIFS('Companies and trusts'!$D$169:$D$178,'Companies and trusts'!$C$169:$C$178,"Other debt")</f>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="28" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="F31" s="20">
+        <f>COUNTIF('Assets and debts'!$P$12:$P$19,"Estimate")+COUNTIF('Assets and debts'!$J$26:$J$31,"Estimate")+COUNTIF('Assets and debts'!$J$38:$J$52,"Estimate")+COUNTIF('Assets and debts'!$I$59:$I$70,"Estimate")+COUNTIF('Companies and trusts'!$C$14,"Estimate")+COUNTIF('Companies and trusts'!$C$60,"Estimate")+COUNTIF('Companies and trusts'!$C$105,"Estimate")+COUNTIF('Companies and trusts'!$C$150,"Estimate")+COUNTIF('Companies and trusts'!$F$34:$F$43,"Estimate")+COUNTIF('Companies and trusts'!$F$79:$F$88,"Estimate")+COUNTIF('Companies and trusts'!$F$124:$F$133,"Estimate")+COUNTIF('Companies and trusts'!$F$169:$F$178,"Estimate")</f>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="F32" s="20">
+        <f>SUMPRODUCT(('Assets and debts'!$D$12:$D$19&gt;0)*('Assets and debts'!$F$12:$F$19=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Shares / Unit Trusts")*('Assets and debts'!$F$38:$F$52=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Business Interest")*('Assets and debts'!$F$38:$F$52=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Crypto")*('Assets and debts'!$F$38:$F$52=""))+IF(AND(N('Companies and trusts'!$C$21)&gt;0,'Companies and trusts'!$C$24=""),1,0)+IF(AND(N('Companies and trusts'!$D$21)&gt;0,'Companies and trusts'!$D$24=""),1,0)+IF(AND(N('Companies and trusts'!$C$67)&gt;0,'Companies and trusts'!$C$70=""),1,0)+IF(AND(N('Companies and trusts'!$D$67)&gt;0,'Companies and trusts'!$D$70=""),1,0)+IF(AND(N('Companies and trusts'!$C$112)&gt;0,'Companies and trusts'!$C$115=""),1,0)+IF(AND(N('Companies and trusts'!$D$112)&gt;0,'Companies and trusts'!$D$115=""),1,0)+IF(AND(N('Companies and trusts'!$C$157)&gt;0,'Companies and trusts'!$C$160=""),1,0)+IF(AND(N('Companies and trusts'!$D$157)&gt;0,'Companies and trusts'!$D$160=""),1,0)+SUMPRODUCT(('Companies and trusts'!$D$34:$D$43&gt;0)*('Companies and trusts'!$C$34:$C$43="Property")*('Companies and trusts'!$E$34:$E$43=""))+SUMPRODUCT(('Companies and trusts'!$D$79:$D$88&gt;0)*('Companies and trusts'!$C$79:$C$88="Property")*('Companies and trusts'!$E$79:$E$88=""))+SUMPRODUCT(('Companies and trusts'!$D$124:$D$133&gt;0)*('Companies and trusts'!$C$124:$C$133="Property")*('Companies and trusts'!$E$124:$E$133=""))+SUMPRODUCT(('Companies and trusts'!$D$169:$D$178&gt;0)*('Companies and trusts'!$C$169:$C$178="Property")*('Companies and trusts'!$E$169:$E$178=""))</f>
+      </c>
+    </row>
+    <row r="34" ht="44" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="39">
+        <f>IF('Lists'!$X$3="","You own R ","Together you own R ")&amp;TEXT(F15,"#,##0")&amp;" and owe R "&amp;TEXT(F22,"#,##0")&amp;", a net worth of R "&amp;TEXT(F24,"#,##0")&amp;"."&amp;IF(F31&gt;0," "&amp;F31&amp;IF(F31=1," figure is an estimate."," figures are estimates."),"")&amp;IF(F32&gt;0," "&amp;F32&amp;IF(F32=1," asset has"," assets have")&amp;" no base cost yet, which we need for capital gains tax.","")</f>
+      </c>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" formatRows="0"/>
+  <mergeCells count="4">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B34:F34"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.6" header="0.25" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Fact find&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -3417,7 +3828,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
-        <f>"Fact find for "&amp;IF('Client and family'!$C$10="","a new client",'Client and family'!$C$10)&amp;IF('Client and family'!$D$10="",""," and "&amp;'Client and family'!$D$10)</f>
+        <f>"Fact find for "&amp;IF('Lists'!$X$2="","a new client",'Lists'!$X$2)&amp;IF('Lists'!$X$3="",""," and "&amp;'Lists'!$X$3)</f>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
@@ -3568,7 +3979,223 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:Z49"/>
+  <dimension ref="B1:Z44"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="2" customWidth="1"/>
+    <col min="2" max="2" width="92" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="26" max="26" width="18" hidden="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21.75" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="12"/>
+    </row>
+    <row r="7" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+    </row>
+    <row r="12" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+    </row>
+    <row r="13" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+    </row>
+    <row r="19" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+    </row>
+    <row r="22" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+    </row>
+    <row r="23" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+    </row>
+    <row r="32" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+    </row>
+    <row r="34" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+    </row>
+    <row r="35" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+    </row>
+    <row r="44" ht="20" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" formatRows="0"/>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B5:C5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.6" header="0.25" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Fact find&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:Z51"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -3601,12 +4228,12 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -3616,7 +4243,7 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -3626,265 +4253,267 @@
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="13" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C8" s="13">
-        <f>IF(C10="","You",C10)</f>
+        <f>IF(TRIM(C10&amp;" "&amp;C11)="","You",TRIM(C10&amp;" "&amp;C11))</f>
       </c>
       <c r="D8" s="13">
-        <f>IF(D10="","Your spouse or partner",D10)</f>
+        <f>IF(TRIM(D10&amp;" "&amp;D11)="","Your spouse or partner",TRIM(D10&amp;" "&amp;D11))</f>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C9" s="14"/>
       <c r="D9" s="9"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C10" s="11"/>
       <c r="D10" s="11"/>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C11" s="11"/>
-      <c r="D11" s="9"/>
+      <c r="D11" s="11"/>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
+        <v>30</v>
+      </c>
+      <c r="C12" s="11"/>
+      <c r="D12" s="9"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="17">
-        <f>IF(LEN(C12)=13,IFERROR(DATE(IF(VALUE(LEFT(C12,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C12,2)),VALUE(MID(C12,3,2)),VALUE(MID(C12,5,2))),""),IF(C14="","",C14))</f>
-      </c>
-      <c r="D13" s="17">
-        <f>IF(LEN(D12)=13,IFERROR(DATE(IF(VALUE(LEFT(D12,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(D12,2)),VALUE(MID(D12,3,2)),VALUE(MID(D12,5,2))),""),IF(D14="","",D14))</f>
-      </c>
+      <c r="B13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="10"/>
+      <c r="B14" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="17">
+        <f>IF(C13="","",IF(OR(LEN(C13)&lt;&gt;13,ISERROR(VALUE(C13))),"✗ An SA ID number has 13 digits",IF(AND(MOD(SUMPRODUCT(VALUE(MID(C13,{1,3,5,7,9,11,13},1)))+SUMPRODUCT(INT(VALUE(MID(C13,{2,4,6,8,10,12},1))*2/10)+MOD(VALUE(MID(C13,{2,4,6,8,10,12},1))*2,10)),10)=0,VALUE(MID(C13,3,2))&gt;=1,VALUE(MID(C13,3,2))&lt;=12,VALUE(MID(C13,5,2))&gt;=1,VALUE(MID(C13,5,2))&lt;=DAY(DATE(IF(VALUE(LEFT(C13,2))&lt;30,2000,1900)+VALUE(LEFT(C13,2)),VALUE(MID(C13,3,2))+1,0))),"✓ Valid ID number","✗ Not a valid ID number: please check every digit"))</f>
+      </c>
+      <c r="D14" s="17">
+        <f>IF(D13="","",IF(OR(LEN(D13)&lt;&gt;13,ISERROR(VALUE(D13))),"✗ An SA ID number has 13 digits",IF(AND(MOD(SUMPRODUCT(VALUE(MID(D13,{1,3,5,7,9,11,13},1)))+SUMPRODUCT(INT(VALUE(MID(D13,{2,4,6,8,10,12},1))*2/10)+MOD(VALUE(MID(D13,{2,4,6,8,10,12},1))*2,10)),10)=0,VALUE(MID(D13,3,2))&gt;=1,VALUE(MID(D13,3,2))&lt;=12,VALUE(MID(D13,5,2))&gt;=1,VALUE(MID(D13,5,2))&lt;=DAY(DATE(IF(VALUE(LEFT(D13,2))&lt;30,2000,1900)+VALUE(LEFT(D13,2)),VALUE(MID(D13,3,2))+1,0))),"✓ Valid ID number","✗ Not a valid ID number: please check every digit"))</f>
+      </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="9"/>
+      <c r="B15" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C15" s="18">
+        <f>IF(LEFT(C14,1)="✓",DATE(IF(VALUE(LEFT(C13,2))&lt;30,2000,1900)+VALUE(LEFT(C13,2)),VALUE(MID(C13,3,2)),VALUE(MID(C13,5,2))),IF(C16="","",C16))</f>
+      </c>
+      <c r="D15" s="18">
+        <f>IF(LEFT(D14,1)="✓",DATE(IF(VALUE(LEFT(D13,2))&lt;30,2000,1900)+VALUE(LEFT(D13,2)),VALUE(MID(D13,3,2)),VALUE(MID(D13,5,2))),IF(D16="","",D16))</f>
+      </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="9"/>
+        <v>34</v>
+      </c>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="9"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+        <v>36</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="9"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C19" s="15"/>
-      <c r="D19" s="9"/>
+      <c r="D19" s="15"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="9"/>
-    </row>
-    <row r="21" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="11"/>
+        <v>39</v>
+      </c>
+      <c r="C21" s="15"/>
       <c r="D21" s="9"/>
     </row>
-    <row r="22" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="11"/>
+        <v>40</v>
+      </c>
+      <c r="C22" s="15"/>
       <c r="D22" s="9"/>
     </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="23" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="9"/>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="9"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
+        <v>43</v>
+      </c>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="9"/>
-      <c r="D26" s="14"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+      <c r="C26" s="11"/>
+      <c r="D26" s="9"/>
+    </row>
+    <row r="27" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="9"/>
+        <v>45</v>
+      </c>
+      <c r="C27" s="19">
+        <f>SUMIFS('Income and expenses'!$E$11:$E$20,'Income and expenses'!$C$11:$C$20,'Lists'!$A$2,'Income and expenses'!$D$11:$D$20,"Salary")+SUMIFS('Income and expenses'!$E$11:$E$20,'Income and expenses'!$C$11:$C$20,'Lists'!$A$2,'Income and expenses'!$D$11:$D$20,"Business Income")</f>
+      </c>
+      <c r="D27" s="19">
+        <f>SUMIFS('Income and expenses'!$E$11:$E$20,'Income and expenses'!$C$11:$C$20,'Lists'!$A$3,'Income and expenses'!$D$11:$D$20,"Salary")+SUMIFS('Income and expenses'!$E$11:$E$20,'Income and expenses'!$C$11:$C$20,'Lists'!$A$3,'Income and expenses'!$D$11:$D$20,"Business Income")</f>
+      </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="9"/>
+        <v>46</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="14"/>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="11"/>
+        <v>47</v>
+      </c>
+      <c r="C29" s="15"/>
       <c r="D29" s="9"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C30" s="14"/>
       <c r="D30" s="9"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="10"/>
+        <v>49</v>
+      </c>
+      <c r="C31" s="11"/>
       <c r="D31" s="9"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C32" s="14"/>
       <c r="D32" s="9"/>
     </row>
-    <row r="34" ht="18" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B34" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B35" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-    </row>
-    <row r="36" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" t="s">
-        <v>47</v>
-      </c>
-      <c r="D36" t="s">
-        <v>48</v>
-      </c>
-      <c r="E36" t="s">
-        <v>49</v>
-      </c>
-      <c r="F36" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z36" t="s">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="37" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B37" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="D37" s="13" t="s">
+      <c r="C33" s="10"/>
+      <c r="D33" s="9"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="C34" s="14"/>
+      <c r="D34" s="9"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B36" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+    </row>
+    <row r="38" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B38" s="11"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="19">
-        <f>IF(AND(LEN(C38)&lt;&gt;13,D38=""),"",DATEDIF(IF(LEN(C38)=13,IFERROR(DATE(IF(VALUE(LEFT(C38,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C38,2)),VALUE(MID(C38,3,2)),VALUE(MID(C38,5,2))),D38),D38),TODAY(),"Y"))</f>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B39" s="11"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="19">
-        <f>IF(AND(LEN(C39)&lt;&gt;13,D39=""),"",DATEDIF(IF(LEN(C39)=13,IFERROR(DATE(IF(VALUE(LEFT(C39,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C39,2)),VALUE(MID(C39,3,2)),VALUE(MID(C39,5,2))),D39),D39),TODAY(),"Y"))</f>
+      <c r="C38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D38" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" t="s">
+        <v>58</v>
+      </c>
+      <c r="F38" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -3893,7 +4522,7 @@
       <c r="D40" s="10"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
-      <c r="G40" s="19">
+      <c r="G40" s="20">
         <f>IF(AND(LEN(C40)&lt;&gt;13,D40=""),"",DATEDIF(IF(LEN(C40)=13,IFERROR(DATE(IF(VALUE(LEFT(C40,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C40,2)),VALUE(MID(C40,3,2)),VALUE(MID(C40,5,2))),D40),D40),TODAY(),"Y"))</f>
       </c>
     </row>
@@ -3903,7 +4532,7 @@
       <c r="D41" s="10"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14"/>
-      <c r="G41" s="19">
+      <c r="G41" s="20">
         <f>IF(AND(LEN(C41)&lt;&gt;13,D41=""),"",DATEDIF(IF(LEN(C41)=13,IFERROR(DATE(IF(VALUE(LEFT(C41,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C41,2)),VALUE(MID(C41,3,2)),VALUE(MID(C41,5,2))),D41),D41),TODAY(),"Y"))</f>
       </c>
     </row>
@@ -3913,7 +4542,7 @@
       <c r="D42" s="10"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
-      <c r="G42" s="19">
+      <c r="G42" s="20">
         <f>IF(AND(LEN(C42)&lt;&gt;13,D42=""),"",DATEDIF(IF(LEN(C42)=13,IFERROR(DATE(IF(VALUE(LEFT(C42,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C42,2)),VALUE(MID(C42,3,2)),VALUE(MID(C42,5,2))),D42),D42),TODAY(),"Y"))</f>
       </c>
     </row>
@@ -3923,7 +4552,7 @@
       <c r="D43" s="10"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14"/>
-      <c r="G43" s="19">
+      <c r="G43" s="20">
         <f>IF(AND(LEN(C43)&lt;&gt;13,D43=""),"",DATEDIF(IF(LEN(C43)=13,IFERROR(DATE(IF(VALUE(LEFT(C43,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C43,2)),VALUE(MID(C43,3,2)),VALUE(MID(C43,5,2))),D43),D43),TODAY(),"Y"))</f>
       </c>
     </row>
@@ -3933,7 +4562,7 @@
       <c r="D44" s="10"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
-      <c r="G44" s="19">
+      <c r="G44" s="20">
         <f>IF(AND(LEN(C44)&lt;&gt;13,D44=""),"",DATEDIF(IF(LEN(C44)=13,IFERROR(DATE(IF(VALUE(LEFT(C44,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C44,2)),VALUE(MID(C44,3,2)),VALUE(MID(C44,5,2))),D44),D44),TODAY(),"Y"))</f>
       </c>
     </row>
@@ -3943,39 +4572,59 @@
       <c r="D45" s="10"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
-      <c r="G45" s="19">
+      <c r="G45" s="20">
         <f>IF(AND(LEN(C45)&lt;&gt;13,D45=""),"",DATEDIF(IF(LEN(C45)=13,IFERROR(DATE(IF(VALUE(LEFT(C45,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C45,2)),VALUE(MID(C45,3,2)),VALUE(MID(C45,5,2))),D45),D45),TODAY(),"Y"))</f>
       </c>
     </row>
-    <row r="47" ht="18" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B47" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
-      <c r="G47" s="5"/>
-    </row>
-    <row r="48" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B48" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
-    </row>
-    <row r="49" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B49" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" s="11"/>
-      <c r="D49" s="11"/>
-      <c r="E49" s="11"/>
-      <c r="F49" s="11"/>
-      <c r="G49" s="11"/>
+    <row r="46" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="11"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="20">
+        <f>IF(AND(LEN(C46)&lt;&gt;13,D46=""),"",DATEDIF(IF(LEN(C46)=13,IFERROR(DATE(IF(VALUE(LEFT(C46,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C46,2)),VALUE(MID(C46,3,2)),VALUE(MID(C46,5,2))),D46),D46),TODAY(),"Y"))</f>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="11"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="20">
+        <f>IF(AND(LEN(C47)&lt;&gt;13,D47=""),"",DATEDIF(IF(LEN(C47)=13,IFERROR(DATE(IF(VALUE(LEFT(C47,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C47,2)),VALUE(MID(C47,3,2)),VALUE(MID(C47,5,2))),D47),D47),TODAY(),"Y"))</f>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+    </row>
+    <row r="50" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C50" s="12"/>
+      <c r="D50" s="12"/>
+      <c r="E50" s="12"/>
+      <c r="F50" s="12"/>
+      <c r="G50" s="12"/>
+    </row>
+    <row r="51" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B51" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
@@ -3983,51 +4632,48 @@
     <mergeCell ref="B1:G1"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="C51:G51"/>
   </mergeCells>
-  <dataValidations count="13">
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C14:D14">
+  <dataValidations count="12">
+    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C16:D16">
       <formula1>7306</formula1>
       <formula2>73415</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C15">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C17">
       <formula1>'Lists'!$E$2:$E$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C16">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C18">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="C25:D25">
-      <formula1>0</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C28">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C30">
       <formula1>'Lists'!$I$2:$I$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C30">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C32">
       <formula1>'Lists'!$H$2:$H$9</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C31">
+    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C33">
       <formula1>7306</formula1>
       <formula2>73415</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C32">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C34">
       <formula1>'Lists'!$G$2:$G$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C9">
       <formula1>'Lists'!$D$2:$D$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D26">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D28">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="D38:D45">
+    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="D40:D47">
       <formula1>7306</formula1>
       <formula2>73415</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="E38:E45">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="E40:E47">
       <formula1>'Lists'!$J$2:$J$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="F38:F45">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="F40:F47">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -4040,7 +4686,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4082,12 +4728,12 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -4096,9 +4742,9 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" ht="26" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -4109,82 +4755,82 @@
     </row>
     <row r="8" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z8" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C10" s="20">
+      <c r="B10" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" s="21">
         <f>'Lists'!$A$2</f>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="21">
+      <c r="D10" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="22">
         <v>45000</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="22">
         <v>45000</v>
       </c>
-      <c r="G10" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="H10" s="20" t="s">
-        <v>78</v>
+      <c r="G10" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="11"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23"/>
       <c r="G11" s="14"/>
       <c r="H11" s="11"/>
     </row>
@@ -4192,8 +4838,8 @@
       <c r="B12" s="11"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="14"/>
       <c r="H12" s="11"/>
     </row>
@@ -4201,8 +4847,8 @@
       <c r="B13" s="11"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
       <c r="G13" s="14"/>
       <c r="H13" s="11"/>
     </row>
@@ -4210,8 +4856,8 @@
       <c r="B14" s="11"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
       <c r="G14" s="14"/>
       <c r="H14" s="11"/>
     </row>
@@ -4219,8 +4865,8 @@
       <c r="B15" s="11"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
       <c r="G15" s="14"/>
       <c r="H15" s="11"/>
     </row>
@@ -4228,8 +4874,8 @@
       <c r="B16" s="11"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
       <c r="G16" s="14"/>
       <c r="H16" s="11"/>
     </row>
@@ -4237,8 +4883,8 @@
       <c r="B17" s="11"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="14"/>
       <c r="H17" s="11"/>
     </row>
@@ -4246,8 +4892,8 @@
       <c r="B18" s="11"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
       <c r="G18" s="14"/>
       <c r="H18" s="11"/>
     </row>
@@ -4255,8 +4901,8 @@
       <c r="B19" s="11"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="14"/>
       <c r="H19" s="11"/>
     </row>
@@ -4264,22 +4910,22 @@
       <c r="B20" s="11"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
       <c r="G20" s="14"/>
       <c r="H20" s="11"/>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B21" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" s="23">
+      <c r="B21" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="25">
         <f>SUM(E11:E20)</f>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -4290,7 +4936,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="12" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
@@ -4301,150 +4947,150 @@
     </row>
     <row r="25" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C25" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z25" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D27" s="21">
+      <c r="B27" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="22">
         <v>18000</v>
       </c>
-      <c r="E27" s="20" t="s">
-        <v>88</v>
+      <c r="E27" s="21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="11"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="18"/>
+      <c r="D28" s="23"/>
       <c r="E28" s="11"/>
     </row>
     <row r="29" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="11"/>
       <c r="C29" s="14"/>
-      <c r="D29" s="18"/>
+      <c r="D29" s="23"/>
       <c r="E29" s="11"/>
     </row>
     <row r="30" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="14"/>
-      <c r="D30" s="18"/>
+      <c r="D30" s="23"/>
       <c r="E30" s="11"/>
     </row>
     <row r="31" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="11"/>
       <c r="C31" s="14"/>
-      <c r="D31" s="18"/>
+      <c r="D31" s="23"/>
       <c r="E31" s="11"/>
     </row>
     <row r="32" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="11"/>
       <c r="C32" s="14"/>
-      <c r="D32" s="18"/>
+      <c r="D32" s="23"/>
       <c r="E32" s="11"/>
     </row>
     <row r="33" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="11"/>
       <c r="C33" s="14"/>
-      <c r="D33" s="18"/>
+      <c r="D33" s="23"/>
       <c r="E33" s="11"/>
     </row>
     <row r="34" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="11"/>
       <c r="C34" s="14"/>
-      <c r="D34" s="18"/>
+      <c r="D34" s="23"/>
       <c r="E34" s="11"/>
     </row>
     <row r="35" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="11"/>
       <c r="C35" s="14"/>
-      <c r="D35" s="18"/>
+      <c r="D35" s="23"/>
       <c r="E35" s="11"/>
     </row>
     <row r="36" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="11"/>
       <c r="C36" s="14"/>
-      <c r="D36" s="18"/>
+      <c r="D36" s="23"/>
       <c r="E36" s="11"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="11"/>
       <c r="C37" s="14"/>
-      <c r="D37" s="18"/>
+      <c r="D37" s="23"/>
       <c r="E37" s="11"/>
     </row>
     <row r="38" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="11"/>
       <c r="C38" s="14"/>
-      <c r="D38" s="18"/>
+      <c r="D38" s="23"/>
       <c r="E38" s="11"/>
     </row>
     <row r="39" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
       <c r="C39" s="14"/>
-      <c r="D39" s="18"/>
+      <c r="D39" s="23"/>
       <c r="E39" s="11"/>
     </row>
     <row r="40" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="11"/>
       <c r="C40" s="14"/>
-      <c r="D40" s="18"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="11"/>
     </row>
     <row r="41" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="11"/>
       <c r="C41" s="14"/>
-      <c r="D41" s="18"/>
+      <c r="D41" s="23"/>
       <c r="E41" s="11"/>
     </row>
     <row r="42" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="11"/>
       <c r="C42" s="14"/>
-      <c r="D42" s="18"/>
+      <c r="D42" s="23"/>
       <c r="E42" s="11"/>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="D43" s="23">
+      <c r="B43" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" s="25">
         <f>SUM(D28:D42)</f>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="5"/>
@@ -4455,25 +5101,25 @@
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="24">
+        <v>100</v>
+      </c>
+      <c r="C46" s="19">
         <f>E21</f>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="24">
+        <v>101</v>
+      </c>
+      <c r="C47" s="19">
         <f>D43</f>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B48" s="22" t="s">
-        <v>93</v>
-      </c>
-      <c r="C48" s="23">
+      <c r="B48" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="25">
         <f>E21-D43</f>
       </c>
     </row>
@@ -4514,7 +5160,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4571,12 +5217,12 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -4596,7 +5242,7 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -4616,7 +5262,7 @@
     </row>
     <row r="8" ht="26" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="12" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12"/>
@@ -4636,167 +5282,167 @@
     </row>
     <row r="9" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="I9" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="J9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="L9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="M9" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="N9" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="O9" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="P9" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="Q9" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z9" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="13" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="L10" s="13" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="O10" s="13" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="B11" s="20" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>127</v>
-      </c>
-      <c r="D11" s="21">
+      <c r="B11" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="D11" s="22">
         <v>3500000</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>46295</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="22">
         <v>1800000</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="26">
         <v>41030</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="22">
         <v>1200000</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="22">
         <v>14500</v>
       </c>
-      <c r="J11" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="K11" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="L11" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="M11" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="N11" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="O11" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="P11" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q11" s="20" t="s">
-        <v>131</v>
+      <c r="J11" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="N11" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="O11" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="P11" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q11" s="21" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="11"/>
       <c r="C12" s="14"/>
-      <c r="D12" s="18"/>
+      <c r="D12" s="23"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="18"/>
+      <c r="F12" s="23"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
       <c r="K12" s="14"/>
       <c r="L12" s="14"/>
       <c r="M12" s="11"/>
@@ -4808,13 +5454,13 @@
     <row r="13" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="11"/>
       <c r="C13" s="14"/>
-      <c r="D13" s="18"/>
+      <c r="D13" s="23"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="18"/>
+      <c r="F13" s="23"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="18"/>
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="11"/>
@@ -4826,13 +5472,13 @@
     <row r="14" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="11"/>
       <c r="C14" s="14"/>
-      <c r="D14" s="18"/>
+      <c r="D14" s="23"/>
       <c r="E14" s="10"/>
-      <c r="F14" s="18"/>
+      <c r="F14" s="23"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
       <c r="M14" s="11"/>
@@ -4844,13 +5490,13 @@
     <row r="15" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="11"/>
       <c r="C15" s="14"/>
-      <c r="D15" s="18"/>
+      <c r="D15" s="23"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="18"/>
+      <c r="F15" s="23"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
-      <c r="J15" s="18"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
       <c r="M15" s="11"/>
@@ -4862,13 +5508,13 @@
     <row r="16" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
       <c r="C16" s="14"/>
-      <c r="D16" s="18"/>
+      <c r="D16" s="23"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="18"/>
+      <c r="F16" s="23"/>
       <c r="G16" s="10"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
-      <c r="J16" s="18"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
       <c r="M16" s="11"/>
@@ -4880,13 +5526,13 @@
     <row r="17" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="11"/>
       <c r="C17" s="14"/>
-      <c r="D17" s="18"/>
+      <c r="D17" s="23"/>
       <c r="E17" s="10"/>
-      <c r="F17" s="18"/>
+      <c r="F17" s="23"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
-      <c r="J17" s="18"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
       <c r="M17" s="11"/>
@@ -4898,13 +5544,13 @@
     <row r="18" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="11"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="18"/>
+      <c r="D18" s="23"/>
       <c r="E18" s="10"/>
-      <c r="F18" s="18"/>
+      <c r="F18" s="23"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
-      <c r="J18" s="18"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
       <c r="M18" s="11"/>
@@ -4916,13 +5562,13 @@
     <row r="19" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="11"/>
       <c r="C19" s="14"/>
-      <c r="D19" s="18"/>
+      <c r="D19" s="23"/>
       <c r="E19" s="10"/>
-      <c r="F19" s="18"/>
+      <c r="F19" s="23"/>
       <c r="G19" s="10"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
-      <c r="J19" s="18"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
       <c r="M19" s="11"/>
@@ -4933,7 +5579,7 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -4953,7 +5599,7 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="12" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
@@ -4973,109 +5619,109 @@
     </row>
     <row r="23" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D23" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E23" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F23" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G23" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H23" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="I23" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="J23" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="K23" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z23" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="13" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="D24" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="J24" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="21">
+        <f>'Lists'!$A$2</f>
+      </c>
+      <c r="D25" s="22">
+        <v>520000</v>
+      </c>
+      <c r="E25" s="22">
+        <v>180000</v>
+      </c>
+      <c r="F25" s="22">
+        <v>9800</v>
+      </c>
+      <c r="G25" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="H25" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="I25" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="J25" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="G24" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="J24" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="K24" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="20" t="s">
-        <v>140</v>
-      </c>
-      <c r="C25" s="20">
-        <f>'Lists'!$A$2</f>
-      </c>
-      <c r="D25" s="21">
-        <v>520000</v>
-      </c>
-      <c r="E25" s="21">
-        <v>180000</v>
-      </c>
-      <c r="F25" s="21">
-        <v>9800</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="I25" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="J25" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="K25" s="20" t="s">
-        <v>88</v>
+      <c r="K25" s="21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="11"/>
       <c r="C26" s="14"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23"/>
       <c r="G26" s="14"/>
       <c r="H26" s="11"/>
       <c r="I26" s="14"/>
@@ -5085,9 +5731,9 @@
     <row r="27" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="11"/>
       <c r="C27" s="14"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="23"/>
       <c r="G27" s="14"/>
       <c r="H27" s="11"/>
       <c r="I27" s="14"/>
@@ -5097,9 +5743,9 @@
     <row r="28" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="11"/>
       <c r="C28" s="14"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23"/>
       <c r="G28" s="14"/>
       <c r="H28" s="11"/>
       <c r="I28" s="14"/>
@@ -5109,9 +5755,9 @@
     <row r="29" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="11"/>
       <c r="C29" s="14"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="23"/>
       <c r="G29" s="14"/>
       <c r="H29" s="11"/>
       <c r="I29" s="14"/>
@@ -5121,9 +5767,9 @@
     <row r="30" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
       <c r="C30" s="14"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23"/>
       <c r="G30" s="14"/>
       <c r="H30" s="11"/>
       <c r="I30" s="14"/>
@@ -5133,9 +5779,9 @@
     <row r="31" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="11"/>
       <c r="C31" s="14"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="23"/>
       <c r="G31" s="14"/>
       <c r="H31" s="11"/>
       <c r="I31" s="14"/>
@@ -5144,7 +5790,7 @@
     </row>
     <row r="33" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -5164,7 +5810,7 @@
     </row>
     <row r="34" ht="26" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B34" s="12" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
@@ -5184,109 +5830,109 @@
     </row>
     <row r="35" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D35" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="E35" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="F35" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="G35" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="H35" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I35" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="J35" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="K35" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z35" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="F36" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="I36" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="J36" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="K36" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E36" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="F36" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="G36" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="I36" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="J36" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="K36" s="13" t="s">
-        <v>74</v>
-      </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="C37" s="20">
+      <c r="B37" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="21">
         <f>'Lists'!$A$2</f>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="E37" s="21">
+      <c r="D37" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="E37" s="22">
         <v>85000</v>
       </c>
-      <c r="F37" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="G37" s="25" t="s">
-        <v>88</v>
-      </c>
-      <c r="H37" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="I37" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="J37" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="K37" s="20" t="s">
-        <v>88</v>
+      <c r="F37" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="I37" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J37" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="K37" s="21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="11"/>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
       <c r="G38" s="10"/>
       <c r="H38" s="14"/>
       <c r="I38" s="11"/>
@@ -5297,8 +5943,8 @@
       <c r="B39" s="11"/>
       <c r="C39" s="14"/>
       <c r="D39" s="14"/>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
       <c r="G39" s="10"/>
       <c r="H39" s="14"/>
       <c r="I39" s="11"/>
@@ -5309,8 +5955,8 @@
       <c r="B40" s="11"/>
       <c r="C40" s="14"/>
       <c r="D40" s="14"/>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
       <c r="G40" s="10"/>
       <c r="H40" s="14"/>
       <c r="I40" s="11"/>
@@ -5321,8 +5967,8 @@
       <c r="B41" s="11"/>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="23"/>
       <c r="G41" s="10"/>
       <c r="H41" s="14"/>
       <c r="I41" s="11"/>
@@ -5333,8 +5979,8 @@
       <c r="B42" s="11"/>
       <c r="C42" s="14"/>
       <c r="D42" s="14"/>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="23"/>
       <c r="G42" s="10"/>
       <c r="H42" s="14"/>
       <c r="I42" s="11"/>
@@ -5345,8 +5991,8 @@
       <c r="B43" s="11"/>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="23"/>
       <c r="G43" s="10"/>
       <c r="H43" s="14"/>
       <c r="I43" s="11"/>
@@ -5357,8 +6003,8 @@
       <c r="B44" s="11"/>
       <c r="C44" s="14"/>
       <c r="D44" s="14"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="23"/>
       <c r="G44" s="10"/>
       <c r="H44" s="14"/>
       <c r="I44" s="11"/>
@@ -5369,8 +6015,8 @@
       <c r="B45" s="11"/>
       <c r="C45" s="14"/>
       <c r="D45" s="14"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="23"/>
       <c r="G45" s="10"/>
       <c r="H45" s="14"/>
       <c r="I45" s="11"/>
@@ -5381,8 +6027,8 @@
       <c r="B46" s="11"/>
       <c r="C46" s="14"/>
       <c r="D46" s="14"/>
-      <c r="E46" s="18"/>
-      <c r="F46" s="18"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="23"/>
       <c r="G46" s="10"/>
       <c r="H46" s="14"/>
       <c r="I46" s="11"/>
@@ -5393,8 +6039,8 @@
       <c r="B47" s="11"/>
       <c r="C47" s="14"/>
       <c r="D47" s="14"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="18"/>
+      <c r="E47" s="23"/>
+      <c r="F47" s="23"/>
       <c r="G47" s="10"/>
       <c r="H47" s="14"/>
       <c r="I47" s="11"/>
@@ -5405,8 +6051,8 @@
       <c r="B48" s="11"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="18"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
       <c r="G48" s="10"/>
       <c r="H48" s="14"/>
       <c r="I48" s="11"/>
@@ -5417,8 +6063,8 @@
       <c r="B49" s="11"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
       <c r="G49" s="10"/>
       <c r="H49" s="14"/>
       <c r="I49" s="11"/>
@@ -5429,8 +6075,8 @@
       <c r="B50" s="11"/>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
+      <c r="E50" s="23"/>
+      <c r="F50" s="23"/>
       <c r="G50" s="10"/>
       <c r="H50" s="14"/>
       <c r="I50" s="11"/>
@@ -5441,8 +6087,8 @@
       <c r="B51" s="11"/>
       <c r="C51" s="14"/>
       <c r="D51" s="14"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="18"/>
+      <c r="E51" s="23"/>
+      <c r="F51" s="23"/>
       <c r="G51" s="10"/>
       <c r="H51" s="14"/>
       <c r="I51" s="11"/>
@@ -5453,8 +6099,8 @@
       <c r="B52" s="11"/>
       <c r="C52" s="14"/>
       <c r="D52" s="14"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
+      <c r="E52" s="23"/>
+      <c r="F52" s="23"/>
       <c r="G52" s="10"/>
       <c r="H52" s="14"/>
       <c r="I52" s="11"/>
@@ -5463,7 +6109,7 @@
     </row>
     <row r="54" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B54" s="4" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
@@ -5483,7 +6129,7 @@
     </row>
     <row r="55" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B55" s="12" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C55" s="12"/>
       <c r="D55" s="12"/>
@@ -5503,101 +6149,101 @@
     </row>
     <row r="56" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C56" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E56" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="F56" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G56" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="H56" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="I56" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="J56" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z56" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="13" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="C57" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="F57" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="G57" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H57" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I57" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="J57" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C58" s="21">
+        <f>'Lists'!$A$2</f>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E58" s="22">
+        <v>25000</v>
+      </c>
+      <c r="F58" s="21">
+        <v>19.5</v>
+      </c>
+      <c r="G58" s="22">
+        <v>1500</v>
+      </c>
+      <c r="H58" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="I58" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="D57" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="H57" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="C58" s="20">
-        <f>'Lists'!$A$2</f>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="E58" s="21">
-        <v>25000</v>
-      </c>
-      <c r="F58" s="20">
-        <v>19.5</v>
-      </c>
-      <c r="G58" s="21">
-        <v>1500</v>
-      </c>
-      <c r="H58" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="I58" s="20" t="s">
-        <v>149</v>
-      </c>
-      <c r="J58" s="20" t="s">
-        <v>88</v>
+      <c r="J58" s="21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="11"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
-      <c r="E59" s="18"/>
-      <c r="F59" s="26"/>
-      <c r="G59" s="18"/>
+      <c r="E59" s="23"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="23"/>
       <c r="H59" s="14"/>
       <c r="I59" s="14"/>
       <c r="J59" s="11"/>
@@ -5606,9 +6252,9 @@
       <c r="B60" s="11"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
-      <c r="E60" s="18"/>
-      <c r="F60" s="26"/>
-      <c r="G60" s="18"/>
+      <c r="E60" s="23"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="23"/>
       <c r="H60" s="14"/>
       <c r="I60" s="14"/>
       <c r="J60" s="11"/>
@@ -5617,9 +6263,9 @@
       <c r="B61" s="11"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
-      <c r="E61" s="18"/>
-      <c r="F61" s="26"/>
-      <c r="G61" s="18"/>
+      <c r="E61" s="23"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="23"/>
       <c r="H61" s="14"/>
       <c r="I61" s="14"/>
       <c r="J61" s="11"/>
@@ -5628,9 +6274,9 @@
       <c r="B62" s="11"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
-      <c r="E62" s="18"/>
-      <c r="F62" s="26"/>
-      <c r="G62" s="18"/>
+      <c r="E62" s="23"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="23"/>
       <c r="H62" s="14"/>
       <c r="I62" s="14"/>
       <c r="J62" s="11"/>
@@ -5639,9 +6285,9 @@
       <c r="B63" s="11"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
-      <c r="E63" s="18"/>
-      <c r="F63" s="26"/>
-      <c r="G63" s="18"/>
+      <c r="E63" s="23"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="23"/>
       <c r="H63" s="14"/>
       <c r="I63" s="14"/>
       <c r="J63" s="11"/>
@@ -5650,9 +6296,9 @@
       <c r="B64" s="11"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
-      <c r="E64" s="18"/>
-      <c r="F64" s="26"/>
-      <c r="G64" s="18"/>
+      <c r="E64" s="23"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="23"/>
       <c r="H64" s="14"/>
       <c r="I64" s="14"/>
       <c r="J64" s="11"/>
@@ -5661,9 +6307,9 @@
       <c r="B65" s="11"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
-      <c r="E65" s="18"/>
-      <c r="F65" s="26"/>
-      <c r="G65" s="18"/>
+      <c r="E65" s="23"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="23"/>
       <c r="H65" s="14"/>
       <c r="I65" s="14"/>
       <c r="J65" s="11"/>
@@ -5672,9 +6318,9 @@
       <c r="B66" s="11"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
-      <c r="E66" s="18"/>
-      <c r="F66" s="26"/>
-      <c r="G66" s="18"/>
+      <c r="E66" s="23"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="23"/>
       <c r="H66" s="14"/>
       <c r="I66" s="14"/>
       <c r="J66" s="11"/>
@@ -5683,9 +6329,9 @@
       <c r="B67" s="11"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
-      <c r="E67" s="18"/>
-      <c r="F67" s="26"/>
-      <c r="G67" s="18"/>
+      <c r="E67" s="23"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="23"/>
       <c r="H67" s="14"/>
       <c r="I67" s="14"/>
       <c r="J67" s="11"/>
@@ -5694,9 +6340,9 @@
       <c r="B68" s="11"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
-      <c r="E68" s="18"/>
-      <c r="F68" s="26"/>
-      <c r="G68" s="18"/>
+      <c r="E68" s="23"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="23"/>
       <c r="H68" s="14"/>
       <c r="I68" s="14"/>
       <c r="J68" s="11"/>
@@ -5705,9 +6351,9 @@
       <c r="B69" s="11"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
-      <c r="E69" s="18"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="18"/>
+      <c r="E69" s="23"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="23"/>
       <c r="H69" s="14"/>
       <c r="I69" s="14"/>
       <c r="J69" s="11"/>
@@ -5716,9 +6362,9 @@
       <c r="B70" s="11"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
-      <c r="E70" s="18"/>
-      <c r="F70" s="26"/>
-      <c r="G70" s="18"/>
+      <c r="E70" s="23"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="23"/>
       <c r="H70" s="14"/>
       <c r="I70" s="14"/>
       <c r="J70" s="11"/>
@@ -5781,7 +6427,7 @@
       <formula2>73415</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="G26:G31">
-      <formula1>'Lists'!$U$2:$U$4</formula1>
+      <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
     <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="G38:G52">
       <formula1>7306</formula1>
@@ -5794,7 +6440,7 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="H38:H52">
-      <formula1>'Lists'!$U$2:$U$4</formula1>
+      <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="H59:H70">
       <formula1>'Lists'!$F$2:$F$3</formula1>
@@ -5803,25 +6449,25 @@
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="I59:I70">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="J26:J31">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="J38:J52">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="K12:K19">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="L12:L19">
-      <formula1>'Lists'!$U$2:$U$4</formula1>
+      <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="N12:O19">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="P12:P19">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -5836,7 +6482,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -5875,12 +6521,12 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" ht="26" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -5890,7 +6536,7 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -5900,7 +6546,7 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
@@ -5908,49 +6554,49 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C9" s="14"/>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C10" s="14"/>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C11" s="14"/>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C12" s="14"/>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C13" s="10"/>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C14" s="14"/>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B15" s="7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C15" s="14"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -5958,19 +6604,19 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C17" s="14"/>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C18" s="14"/>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -5978,7 +6624,7 @@
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="13" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C20" s="13">
         <f>'Lists'!$A$2</f>
@@ -5989,61 +6635,61 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
+        <v>187</v>
+      </c>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
     </row>
     <row r="22" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
+        <v>189</v>
+      </c>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B24" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
+        <v>190</v>
+      </c>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" s="7" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B26" s="7" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
     </row>
     <row r="27" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
+        <v>193</v>
+      </c>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="27" t="s">
-        <v>185</v>
+      <c r="B29" s="28" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="12" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
@@ -6053,174 +6699,174 @@
     </row>
     <row r="31" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C31" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D31" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E31" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F31" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G31" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z31" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="13" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="D33" s="21">
+      <c r="B33" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="D33" s="22">
         <v>5000000</v>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="22">
         <v>2000000</v>
       </c>
-      <c r="F33" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>88</v>
+      <c r="F33" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="11"/>
       <c r="C34" s="14"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
       <c r="F34" s="14"/>
       <c r="G34" s="11"/>
     </row>
     <row r="35" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="11"/>
       <c r="C35" s="14"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="18"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
       <c r="F35" s="14"/>
       <c r="G35" s="11"/>
     </row>
     <row r="36" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="11"/>
       <c r="C36" s="14"/>
-      <c r="D36" s="18"/>
-      <c r="E36" s="18"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
       <c r="F36" s="14"/>
       <c r="G36" s="11"/>
     </row>
     <row r="37" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B37" s="11"/>
       <c r="C37" s="14"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
       <c r="F37" s="14"/>
       <c r="G37" s="11"/>
     </row>
     <row r="38" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="11"/>
       <c r="C38" s="14"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
       <c r="F38" s="14"/>
       <c r="G38" s="11"/>
     </row>
     <row r="39" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B39" s="11"/>
       <c r="C39" s="14"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="18"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
       <c r="F39" s="14"/>
       <c r="G39" s="11"/>
     </row>
     <row r="40" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="11"/>
       <c r="C40" s="14"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="18"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
       <c r="F40" s="14"/>
       <c r="G40" s="11"/>
     </row>
     <row r="41" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="11"/>
       <c r="C41" s="14"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
       <c r="F41" s="14"/>
       <c r="G41" s="11"/>
     </row>
     <row r="42" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="11"/>
       <c r="C42" s="14"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="18"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
       <c r="F42" s="14"/>
       <c r="G42" s="11"/>
     </row>
     <row r="43" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="11"/>
       <c r="C43" s="14"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
       <c r="F43" s="14"/>
       <c r="G43" s="11"/>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C44" s="24">
+        <v>204</v>
+      </c>
+      <c r="C44" s="19">
         <f>SUMIFS(D34:D43,C34:C43,"Property")+SUMIFS(D34:D43,C34:C43,"Other asset")+IF(C22="Debit",N(C23),0)+IF(D22="Debit",N(D23),0)</f>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C45" s="24">
+        <v>205</v>
+      </c>
+      <c r="C45" s="19">
         <f>SUMIFS(D34:D43,C34:C43,"Bond")+SUMIFS(D34:D43,C34:C43,"Other debt")+IF(C22="Credit",N(C23),0)+IF(D22="Credit",N(D23),0)</f>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B46" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="C46" s="23">
+      <c r="B46" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C46" s="25">
         <f>C44-C45</f>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B47" s="13" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C47" s="13">
         <f>'Lists'!$A$2</f>
@@ -6231,34 +6877,34 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C48" s="24">
+        <v>208</v>
+      </c>
+      <c r="C48" s="19">
         <f>IF(OR(C9="Trust",C21=""),"",ROUND(IF(OR(C9="Partnership",C9="Sole Proprietor"),C46,MAX(0,C46))*N(C21)/100,0))</f>
       </c>
-      <c r="D48" s="24">
+      <c r="D48" s="19">
         <f>IF(OR(C9="Trust",D21=""),"",ROUND(IF(OR(C9="Partnership",C9="Sole Proprietor"),C46,MAX(0,C46))*N(D21)/100,0))</f>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B49" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="C49" s="23">
+      <c r="B49" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="C49" s="25">
         <f>IF(C9="Trust","",IF(C27&lt;&gt;"",C27,C48))</f>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="25">
         <f>IF(C9="Trust","",IF(D27&lt;&gt;"",D27,D48))</f>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="28" t="s">
-        <v>201</v>
+      <c r="B50" s="29" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -6268,7 +6914,7 @@
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="7" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
@@ -6276,49 +6922,49 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C55" s="14"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C56" s="14"/>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B57" s="7" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C57" s="14"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="7" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C58" s="14"/>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="7" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C59" s="10"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="7" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C60" s="14"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C61" s="14"/>
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
@@ -6326,19 +6972,19 @@
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="7" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C63" s="14"/>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B64" s="7" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C64" s="14"/>
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11"/>
@@ -6346,7 +6992,7 @@
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="13" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C66" s="13">
         <f>'Lists'!$A$2</f>
@@ -6357,61 +7003,61 @@
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C67" s="26"/>
-      <c r="D67" s="26"/>
+        <v>187</v>
+      </c>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
     </row>
     <row r="68" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="7" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C69" s="18"/>
-      <c r="D69" s="18"/>
+        <v>189</v>
+      </c>
+      <c r="C69" s="23"/>
+      <c r="D69" s="23"/>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C70" s="18"/>
-      <c r="D70" s="18"/>
+        <v>190</v>
+      </c>
+      <c r="C70" s="23"/>
+      <c r="D70" s="23"/>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="7" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C71" s="10"/>
       <c r="D71" s="10"/>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="7" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C72" s="14"/>
       <c r="D72" s="14"/>
     </row>
     <row r="73" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
+        <v>193</v>
+      </c>
+      <c r="C73" s="23"/>
+      <c r="D73" s="23"/>
     </row>
     <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75" s="27" t="s">
-        <v>185</v>
+      <c r="B75" s="28" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B76" s="12" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C76" s="12"/>
       <c r="D76" s="12"/>
@@ -6421,154 +7067,154 @@
     </row>
     <row r="77" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C77" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D77" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E77" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F77" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G77" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z77" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B78" s="13" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="E78" s="13" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G78" s="13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B79" s="11"/>
       <c r="C79" s="14"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
+      <c r="D79" s="23"/>
+      <c r="E79" s="23"/>
       <c r="F79" s="14"/>
       <c r="G79" s="11"/>
     </row>
     <row r="80" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B80" s="11"/>
       <c r="C80" s="14"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
+      <c r="D80" s="23"/>
+      <c r="E80" s="23"/>
       <c r="F80" s="14"/>
       <c r="G80" s="11"/>
     </row>
     <row r="81" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B81" s="11"/>
       <c r="C81" s="14"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
+      <c r="D81" s="23"/>
+      <c r="E81" s="23"/>
       <c r="F81" s="14"/>
       <c r="G81" s="11"/>
     </row>
     <row r="82" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B82" s="11"/>
       <c r="C82" s="14"/>
-      <c r="D82" s="18"/>
-      <c r="E82" s="18"/>
+      <c r="D82" s="23"/>
+      <c r="E82" s="23"/>
       <c r="F82" s="14"/>
       <c r="G82" s="11"/>
     </row>
     <row r="83" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B83" s="11"/>
       <c r="C83" s="14"/>
-      <c r="D83" s="18"/>
-      <c r="E83" s="18"/>
+      <c r="D83" s="23"/>
+      <c r="E83" s="23"/>
       <c r="F83" s="14"/>
       <c r="G83" s="11"/>
     </row>
     <row r="84" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B84" s="11"/>
       <c r="C84" s="14"/>
-      <c r="D84" s="18"/>
-      <c r="E84" s="18"/>
+      <c r="D84" s="23"/>
+      <c r="E84" s="23"/>
       <c r="F84" s="14"/>
       <c r="G84" s="11"/>
     </row>
     <row r="85" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B85" s="11"/>
       <c r="C85" s="14"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
+      <c r="D85" s="23"/>
+      <c r="E85" s="23"/>
       <c r="F85" s="14"/>
       <c r="G85" s="11"/>
     </row>
     <row r="86" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B86" s="11"/>
       <c r="C86" s="14"/>
-      <c r="D86" s="18"/>
-      <c r="E86" s="18"/>
+      <c r="D86" s="23"/>
+      <c r="E86" s="23"/>
       <c r="F86" s="14"/>
       <c r="G86" s="11"/>
     </row>
     <row r="87" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B87" s="11"/>
       <c r="C87" s="14"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
+      <c r="D87" s="23"/>
+      <c r="E87" s="23"/>
       <c r="F87" s="14"/>
       <c r="G87" s="11"/>
     </row>
     <row r="88" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B88" s="11"/>
       <c r="C88" s="14"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
       <c r="F88" s="14"/>
       <c r="G88" s="11"/>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B89" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C89" s="24">
+        <v>204</v>
+      </c>
+      <c r="C89" s="19">
         <f>SUMIFS(D79:D88,C79:C88,"Property")+SUMIFS(D79:D88,C79:C88,"Other asset")+IF(C68="Debit",N(C69),0)+IF(D68="Debit",N(D69),0)</f>
       </c>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B90" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C90" s="24">
+        <v>205</v>
+      </c>
+      <c r="C90" s="19">
         <f>SUMIFS(D79:D88,C79:C88,"Bond")+SUMIFS(D79:D88,C79:C88,"Other debt")+IF(C68="Credit",N(C69),0)+IF(D68="Credit",N(D69),0)</f>
       </c>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B91" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="C91" s="23">
+      <c r="B91" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C91" s="25">
         <f>C89-C90</f>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="13" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C92" s="13">
         <f>'Lists'!$A$2</f>
@@ -6579,34 +7225,34 @@
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C93" s="24">
+        <v>208</v>
+      </c>
+      <c r="C93" s="19">
         <f>IF(OR(C55="Trust",C67=""),"",ROUND(IF(OR(C55="Partnership",C55="Sole Proprietor"),C91,MAX(0,C91))*N(C67)/100,0))</f>
       </c>
-      <c r="D93" s="24">
+      <c r="D93" s="19">
         <f>IF(OR(C55="Trust",D67=""),"",ROUND(IF(OR(C55="Partnership",C55="Sole Proprietor"),C91,MAX(0,C91))*N(D67)/100,0))</f>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B94" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="C94" s="23">
+      <c r="B94" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="C94" s="25">
         <f>IF(C55="Trust","",IF(C73&lt;&gt;"",C73,C93))</f>
       </c>
-      <c r="D94" s="23">
+      <c r="D94" s="25">
         <f>IF(C55="Trust","",IF(D73&lt;&gt;"",D73,D93))</f>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B95" s="28" t="s">
-        <v>201</v>
+      <c r="B95" s="29" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="98" ht="18" customHeight="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B98" s="4" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C98" s="5"/>
       <c r="D98" s="5"/>
@@ -6616,7 +7262,7 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B99" s="7" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11"/>
@@ -6624,49 +7270,49 @@
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B100" s="7" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C100" s="14"/>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B101" s="7" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C101" s="14"/>
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B102" s="7" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C102" s="14"/>
     </row>
     <row r="103" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B103" s="7" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C103" s="14"/>
     </row>
     <row r="104" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B104" s="7" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C104" s="10"/>
     </row>
     <row r="105" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B105" s="7" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C105" s="14"/>
     </row>
     <row r="106" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B106" s="7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C106" s="14"/>
     </row>
     <row r="107" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B107" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C107" s="11"/>
       <c r="D107" s="11"/>
@@ -6674,19 +7320,19 @@
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B108" s="7" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C108" s="14"/>
     </row>
     <row r="109" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B109" s="7" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C109" s="14"/>
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B110" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11"/>
@@ -6694,7 +7340,7 @@
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="13" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C111" s="13">
         <f>'Lists'!$A$2</f>
@@ -6705,61 +7351,61 @@
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C112" s="26"/>
-      <c r="D112" s="26"/>
+        <v>187</v>
+      </c>
+      <c r="C112" s="27"/>
+      <c r="D112" s="27"/>
     </row>
     <row r="113" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="7" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C113" s="14"/>
       <c r="D113" s="14"/>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C114" s="18"/>
-      <c r="D114" s="18"/>
+        <v>189</v>
+      </c>
+      <c r="C114" s="23"/>
+      <c r="D114" s="23"/>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C115" s="18"/>
-      <c r="D115" s="18"/>
+        <v>190</v>
+      </c>
+      <c r="C115" s="23"/>
+      <c r="D115" s="23"/>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="7" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C116" s="10"/>
       <c r="D116" s="10"/>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="7" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C117" s="14"/>
       <c r="D117" s="14"/>
     </row>
     <row r="118" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C118" s="18"/>
-      <c r="D118" s="18"/>
+        <v>193</v>
+      </c>
+      <c r="C118" s="23"/>
+      <c r="D118" s="23"/>
     </row>
     <row r="120" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B120" s="27" t="s">
-        <v>185</v>
+      <c r="B120" s="28" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B121" s="12" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C121" s="12"/>
       <c r="D121" s="12"/>
@@ -6769,154 +7415,154 @@
     </row>
     <row r="122" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B122" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C122" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D122" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E122" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F122" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G122" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z122" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B123" s="13" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C123" s="13" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D123" s="13" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F123" s="13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G123" s="13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B124" s="11"/>
       <c r="C124" s="14"/>
-      <c r="D124" s="18"/>
-      <c r="E124" s="18"/>
+      <c r="D124" s="23"/>
+      <c r="E124" s="23"/>
       <c r="F124" s="14"/>
       <c r="G124" s="11"/>
     </row>
     <row r="125" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B125" s="11"/>
       <c r="C125" s="14"/>
-      <c r="D125" s="18"/>
-      <c r="E125" s="18"/>
+      <c r="D125" s="23"/>
+      <c r="E125" s="23"/>
       <c r="F125" s="14"/>
       <c r="G125" s="11"/>
     </row>
     <row r="126" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B126" s="11"/>
       <c r="C126" s="14"/>
-      <c r="D126" s="18"/>
-      <c r="E126" s="18"/>
+      <c r="D126" s="23"/>
+      <c r="E126" s="23"/>
       <c r="F126" s="14"/>
       <c r="G126" s="11"/>
     </row>
     <row r="127" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B127" s="11"/>
       <c r="C127" s="14"/>
-      <c r="D127" s="18"/>
-      <c r="E127" s="18"/>
+      <c r="D127" s="23"/>
+      <c r="E127" s="23"/>
       <c r="F127" s="14"/>
       <c r="G127" s="11"/>
     </row>
     <row r="128" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B128" s="11"/>
       <c r="C128" s="14"/>
-      <c r="D128" s="18"/>
-      <c r="E128" s="18"/>
+      <c r="D128" s="23"/>
+      <c r="E128" s="23"/>
       <c r="F128" s="14"/>
       <c r="G128" s="11"/>
     </row>
     <row r="129" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B129" s="11"/>
       <c r="C129" s="14"/>
-      <c r="D129" s="18"/>
-      <c r="E129" s="18"/>
+      <c r="D129" s="23"/>
+      <c r="E129" s="23"/>
       <c r="F129" s="14"/>
       <c r="G129" s="11"/>
     </row>
     <row r="130" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B130" s="11"/>
       <c r="C130" s="14"/>
-      <c r="D130" s="18"/>
-      <c r="E130" s="18"/>
+      <c r="D130" s="23"/>
+      <c r="E130" s="23"/>
       <c r="F130" s="14"/>
       <c r="G130" s="11"/>
     </row>
     <row r="131" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B131" s="11"/>
       <c r="C131" s="14"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
+      <c r="D131" s="23"/>
+      <c r="E131" s="23"/>
       <c r="F131" s="14"/>
       <c r="G131" s="11"/>
     </row>
     <row r="132" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B132" s="11"/>
       <c r="C132" s="14"/>
-      <c r="D132" s="18"/>
-      <c r="E132" s="18"/>
+      <c r="D132" s="23"/>
+      <c r="E132" s="23"/>
       <c r="F132" s="14"/>
       <c r="G132" s="11"/>
     </row>
     <row r="133" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B133" s="11"/>
       <c r="C133" s="14"/>
-      <c r="D133" s="18"/>
-      <c r="E133" s="18"/>
+      <c r="D133" s="23"/>
+      <c r="E133" s="23"/>
       <c r="F133" s="14"/>
       <c r="G133" s="11"/>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B134" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C134" s="24">
+        <v>204</v>
+      </c>
+      <c r="C134" s="19">
         <f>SUMIFS(D124:D133,C124:C133,"Property")+SUMIFS(D124:D133,C124:C133,"Other asset")+IF(C113="Debit",N(C114),0)+IF(D113="Debit",N(D114),0)</f>
       </c>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B135" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C135" s="24">
+        <v>205</v>
+      </c>
+      <c r="C135" s="19">
         <f>SUMIFS(D124:D133,C124:C133,"Bond")+SUMIFS(D124:D133,C124:C133,"Other debt")+IF(C113="Credit",N(C114),0)+IF(D113="Credit",N(D114),0)</f>
       </c>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B136" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="C136" s="23">
+      <c r="B136" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C136" s="25">
         <f>C134-C135</f>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="13" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C137" s="13">
         <f>'Lists'!$A$2</f>
@@ -6927,34 +7573,34 @@
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C138" s="24">
+        <v>208</v>
+      </c>
+      <c r="C138" s="19">
         <f>IF(OR(C100="Trust",C112=""),"",ROUND(IF(OR(C100="Partnership",C100="Sole Proprietor"),C136,MAX(0,C136))*N(C112)/100,0))</f>
       </c>
-      <c r="D138" s="24">
+      <c r="D138" s="19">
         <f>IF(OR(C100="Trust",D112=""),"",ROUND(IF(OR(C100="Partnership",C100="Sole Proprietor"),C136,MAX(0,C136))*N(D112)/100,0))</f>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B139" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="C139" s="23">
+      <c r="B139" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="C139" s="25">
         <f>IF(C100="Trust","",IF(C118&lt;&gt;"",C118,C138))</f>
       </c>
-      <c r="D139" s="23">
+      <c r="D139" s="25">
         <f>IF(C100="Trust","",IF(D118&lt;&gt;"",D118,D138))</f>
       </c>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B140" s="28" t="s">
-        <v>201</v>
+      <c r="B140" s="29" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="143" ht="18" customHeight="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B143" s="4" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C143" s="5"/>
       <c r="D143" s="5"/>
@@ -6964,7 +7610,7 @@
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B144" s="7" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="C144" s="11"/>
       <c r="D144" s="11"/>
@@ -6972,49 +7618,49 @@
     </row>
     <row r="145" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B145" s="7" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C145" s="14"/>
     </row>
     <row r="146" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B146" s="7" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="C146" s="14"/>
     </row>
     <row r="147" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B147" s="7" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="C147" s="14"/>
     </row>
     <row r="148" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B148" s="7" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C148" s="14"/>
     </row>
     <row r="149" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B149" s="7" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="C149" s="10"/>
     </row>
     <row r="150" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B150" s="7" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="C150" s="14"/>
     </row>
     <row r="151" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B151" s="7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="C151" s="14"/>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B152" s="7" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="C152" s="11"/>
       <c r="D152" s="11"/>
@@ -7022,19 +7668,19 @@
     </row>
     <row r="153" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B153" s="7" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="C153" s="14"/>
     </row>
     <row r="154" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B154" s="7" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="C154" s="14"/>
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B155" s="7" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="C155" s="11"/>
       <c r="D155" s="11"/>
@@ -7042,7 +7688,7 @@
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B156" s="13" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="C156" s="13">
         <f>'Lists'!$A$2</f>
@@ -7053,61 +7699,61 @@
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B157" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="C157" s="26"/>
-      <c r="D157" s="26"/>
+        <v>187</v>
+      </c>
+      <c r="C157" s="27"/>
+      <c r="D157" s="27"/>
     </row>
     <row r="158" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158" s="7" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="C158" s="14"/>
       <c r="D158" s="14"/>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C159" s="18"/>
-      <c r="D159" s="18"/>
+        <v>189</v>
+      </c>
+      <c r="C159" s="23"/>
+      <c r="D159" s="23"/>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C160" s="18"/>
-      <c r="D160" s="18"/>
+        <v>190</v>
+      </c>
+      <c r="C160" s="23"/>
+      <c r="D160" s="23"/>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="7" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="C161" s="10"/>
       <c r="D161" s="10"/>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162" s="7" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="C162" s="14"/>
       <c r="D162" s="14"/>
     </row>
     <row r="163" ht="26" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B163" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C163" s="18"/>
-      <c r="D163" s="18"/>
+        <v>193</v>
+      </c>
+      <c r="C163" s="23"/>
+      <c r="D163" s="23"/>
     </row>
     <row r="165" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B165" s="27" t="s">
-        <v>185</v>
+      <c r="B165" s="28" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B166" s="12" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="C166" s="12"/>
       <c r="D166" s="12"/>
@@ -7117,154 +7763,154 @@
     </row>
     <row r="167" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B167" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C167" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="D167" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E167" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F167" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="G167" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z167" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="168" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B168" s="13" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="C168" s="13" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="E168" s="13" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="F168" s="13" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G168" s="13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B169" s="11"/>
       <c r="C169" s="14"/>
-      <c r="D169" s="18"/>
-      <c r="E169" s="18"/>
+      <c r="D169" s="23"/>
+      <c r="E169" s="23"/>
       <c r="F169" s="14"/>
       <c r="G169" s="11"/>
     </row>
     <row r="170" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B170" s="11"/>
       <c r="C170" s="14"/>
-      <c r="D170" s="18"/>
-      <c r="E170" s="18"/>
+      <c r="D170" s="23"/>
+      <c r="E170" s="23"/>
       <c r="F170" s="14"/>
       <c r="G170" s="11"/>
     </row>
     <row r="171" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B171" s="11"/>
       <c r="C171" s="14"/>
-      <c r="D171" s="18"/>
-      <c r="E171" s="18"/>
+      <c r="D171" s="23"/>
+      <c r="E171" s="23"/>
       <c r="F171" s="14"/>
       <c r="G171" s="11"/>
     </row>
     <row r="172" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B172" s="11"/>
       <c r="C172" s="14"/>
-      <c r="D172" s="18"/>
-      <c r="E172" s="18"/>
+      <c r="D172" s="23"/>
+      <c r="E172" s="23"/>
       <c r="F172" s="14"/>
       <c r="G172" s="11"/>
     </row>
     <row r="173" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B173" s="11"/>
       <c r="C173" s="14"/>
-      <c r="D173" s="18"/>
-      <c r="E173" s="18"/>
+      <c r="D173" s="23"/>
+      <c r="E173" s="23"/>
       <c r="F173" s="14"/>
       <c r="G173" s="11"/>
     </row>
     <row r="174" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B174" s="11"/>
       <c r="C174" s="14"/>
-      <c r="D174" s="18"/>
-      <c r="E174" s="18"/>
+      <c r="D174" s="23"/>
+      <c r="E174" s="23"/>
       <c r="F174" s="14"/>
       <c r="G174" s="11"/>
     </row>
     <row r="175" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B175" s="11"/>
       <c r="C175" s="14"/>
-      <c r="D175" s="18"/>
-      <c r="E175" s="18"/>
+      <c r="D175" s="23"/>
+      <c r="E175" s="23"/>
       <c r="F175" s="14"/>
       <c r="G175" s="11"/>
     </row>
     <row r="176" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B176" s="11"/>
       <c r="C176" s="14"/>
-      <c r="D176" s="18"/>
-      <c r="E176" s="18"/>
+      <c r="D176" s="23"/>
+      <c r="E176" s="23"/>
       <c r="F176" s="14"/>
       <c r="G176" s="11"/>
     </row>
     <row r="177" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B177" s="11"/>
       <c r="C177" s="14"/>
-      <c r="D177" s="18"/>
-      <c r="E177" s="18"/>
+      <c r="D177" s="23"/>
+      <c r="E177" s="23"/>
       <c r="F177" s="14"/>
       <c r="G177" s="11"/>
     </row>
     <row r="178" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B178" s="11"/>
       <c r="C178" s="14"/>
-      <c r="D178" s="18"/>
-      <c r="E178" s="18"/>
+      <c r="D178" s="23"/>
+      <c r="E178" s="23"/>
       <c r="F178" s="14"/>
       <c r="G178" s="11"/>
     </row>
     <row r="179" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B179" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C179" s="24">
+        <v>204</v>
+      </c>
+      <c r="C179" s="19">
         <f>SUMIFS(D169:D178,C169:C178,"Property")+SUMIFS(D169:D178,C169:C178,"Other asset")+IF(C158="Debit",N(C159),0)+IF(D158="Debit",N(D159),0)</f>
       </c>
     </row>
     <row r="180" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B180" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C180" s="24">
+        <v>205</v>
+      </c>
+      <c r="C180" s="19">
         <f>SUMIFS(D169:D178,C169:C178,"Bond")+SUMIFS(D169:D178,C169:C178,"Other debt")+IF(C158="Credit",N(C159),0)+IF(D158="Credit",N(D159),0)</f>
       </c>
     </row>
     <row r="181" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B181" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="C181" s="23">
+      <c r="B181" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C181" s="25">
         <f>C179-C180</f>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B182" s="13" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C182" s="13">
         <f>'Lists'!$A$2</f>
@@ -7275,29 +7921,29 @@
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B183" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="C183" s="24">
+        <v>208</v>
+      </c>
+      <c r="C183" s="19">
         <f>IF(OR(C145="Trust",C157=""),"",ROUND(IF(OR(C145="Partnership",C145="Sole Proprietor"),C181,MAX(0,C181))*N(C157)/100,0))</f>
       </c>
-      <c r="D183" s="24">
+      <c r="D183" s="19">
         <f>IF(OR(C145="Trust",D157=""),"",ROUND(IF(OR(C145="Partnership",C145="Sole Proprietor"),C181,MAX(0,C181))*N(D157)/100,0))</f>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B184" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="C184" s="23">
+      <c r="B184" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="C184" s="25">
         <f>IF(C145="Trust","",IF(C163&lt;&gt;"",C163,C183))</f>
       </c>
-      <c r="D184" s="23">
+      <c r="D184" s="25">
         <f>IF(C145="Trust","",IF(D163&lt;&gt;"",D163,D183))</f>
       </c>
     </row>
     <row r="185" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B185" s="28" t="s">
-        <v>201</v>
+      <c r="B185" s="29" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -7344,10 +7990,10 @@
       <formula2>73415</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C105">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C106">
-      <formula1>'Lists'!$U$2:$U$4</formula1>
+      <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C108:C109">
       <formula1>'Lists'!$F$2:$F$3</formula1>
@@ -7386,7 +8032,7 @@
       <formula2>73415</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C14">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C145">
       <formula1>'Lists'!$O$2:$O$7</formula1>
@@ -7405,13 +8051,13 @@
       <formula2>73415</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C15">
-      <formula1>'Lists'!$U$2:$U$4</formula1>
+      <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C150">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C151">
-      <formula1>'Lists'!$U$2:$U$4</formula1>
+      <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C153:C154">
       <formula1>'Lists'!$F$2:$F$3</formula1>
@@ -7482,10 +8128,10 @@
       <formula2>73415</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C60">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C61">
-      <formula1>'Lists'!$U$2:$U$4</formula1>
+      <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C63:C64">
       <formula1>'Lists'!$F$2:$F$3</formula1>
@@ -7529,16 +8175,16 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="F124:F133">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="F169:F178">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="F34:F43">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="F79:F88">
-      <formula1>'Lists'!$T$2:$T$5</formula1>
+      <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -7555,7 +8201,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7602,12 +8248,12 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -7620,7 +8266,7 @@
     </row>
     <row r="7" ht="26" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12"/>
@@ -7633,101 +8279,101 @@
     </row>
     <row r="8" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="D8" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="E8" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="F8" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G8" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="H8" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="I8" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="J8" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="Z8" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="20" t="s">
-        <v>222</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="E10" s="21">
+      <c r="B10" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="E10" s="22">
         <v>40000</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="21">
         <v>20</v>
       </c>
-      <c r="G10" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="I10" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="J10" s="20" t="s">
-        <v>88</v>
+      <c r="G10" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="11"/>
       <c r="C11" s="14"/>
       <c r="D11" s="14"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
+      <c r="E11" s="23"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="14"/>
       <c r="I11" s="11"/>
       <c r="J11" s="11"/>
@@ -7736,9 +8382,9 @@
       <c r="B12" s="11"/>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="14"/>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
@@ -7747,9 +8393,9 @@
       <c r="B13" s="11"/>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
       <c r="H13" s="14"/>
       <c r="I13" s="11"/>
       <c r="J13" s="11"/>
@@ -7758,9 +8404,9 @@
       <c r="B14" s="11"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
       <c r="H14" s="14"/>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
@@ -7769,9 +8415,9 @@
       <c r="B15" s="11"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
       <c r="H15" s="14"/>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
@@ -7780,9 +8426,9 @@
       <c r="B16" s="11"/>
       <c r="C16" s="14"/>
       <c r="D16" s="14"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="26"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
       <c r="H16" s="14"/>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
@@ -7791,9 +8437,9 @@
       <c r="B17" s="11"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="26"/>
-      <c r="G17" s="26"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
       <c r="H17" s="14"/>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
@@ -7802,9 +8448,9 @@
       <c r="B18" s="11"/>
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
       <c r="H18" s="14"/>
       <c r="I18" s="11"/>
       <c r="J18" s="11"/>
@@ -7813,9 +8459,9 @@
       <c r="B19" s="11"/>
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
       <c r="H19" s="14"/>
       <c r="I19" s="11"/>
       <c r="J19" s="11"/>
@@ -7824,9 +8470,9 @@
       <c r="B20" s="11"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
       <c r="H20" s="14"/>
       <c r="I20" s="11"/>
       <c r="J20" s="11"/>
@@ -7835,9 +8481,9 @@
       <c r="B21" s="11"/>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="26"/>
-      <c r="G21" s="26"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
       <c r="H21" s="14"/>
       <c r="I21" s="11"/>
       <c r="J21" s="11"/>
@@ -7846,9 +8492,9 @@
       <c r="B22" s="11"/>
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="27"/>
+      <c r="G22" s="27"/>
       <c r="H22" s="14"/>
       <c r="I22" s="11"/>
       <c r="J22" s="11"/>
@@ -7862,10 +8508,10 @@
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C11:C22">
-      <formula1>'Lists'!$V$2:$V$6</formula1>
+      <formula1>'Lists'!$W$2:$W$6</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D11:D22">
-      <formula1>'Lists'!$W$2:$W$3</formula1>
+      <formula1>'Lists'!$X$2:$X$3</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="E11:E22">
       <formula1>0</formula1>
@@ -7875,7 +8521,7 @@
       <formula2>1000</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="H11:H22">
-      <formula1>'Lists'!$X$2:$X$4</formula1>
+      <formula1>'Lists'!$Y$2:$Y$4</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -7887,7 +8533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7920,12 +8566,12 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="12" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
@@ -7933,7 +8579,7 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="4" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -7941,37 +8587,37 @@
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="29">
-        <f>'Client and family'!$C$10</f>
-      </c>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
+        <v>60</v>
+      </c>
+      <c r="C9" s="30">
+        <f>'Lists'!$X$2</f>
+      </c>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="C10" s="30">
-        <f>'Client and family'!$C$12</f>
-      </c>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
+        <v>237</v>
+      </c>
+      <c r="C10" s="31">
+        <f>'Client and family'!$C$13</f>
+      </c>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="29">
-        <f>'Client and family'!$C$30</f>
-      </c>
-      <c r="D11" s="29"/>
-      <c r="E11" s="29"/>
+        <v>50</v>
+      </c>
+      <c r="C11" s="30">
+        <f>'Client and family'!$C$32</f>
+      </c>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="7" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
@@ -7979,7 +8625,7 @@
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -7987,7 +8633,7 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="4" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -7995,27 +8641,27 @@
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C16" s="29">
-        <f>'Client and family'!$D$10</f>
-      </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
+        <v>241</v>
+      </c>
+      <c r="C16" s="30">
+        <f>'Lists'!$X$3</f>
+      </c>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C17" s="31">
-        <f>IF('Client and family'!$C$31="","",'Client and family'!$C$31)</f>
-      </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
+        <v>242</v>
+      </c>
+      <c r="C17" s="32">
+        <f>IF('Client and family'!$C$33="","",'Client and family'!$C$33)</f>
+      </c>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -8023,7 +8669,7 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="C19" s="11"/>
       <c r="D19" s="11"/>
@@ -8031,7 +8677,7 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
@@ -8039,17 +8685,17 @@
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="13" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="9">
-        <f>IF('Client and family'!$B$38="","",'Client and family'!$B$38)</f>
+        <f>IF('Client and family'!$B$40="","",'Client and family'!$B$40)</f>
       </c>
       <c r="C23" s="11"/>
       <c r="D23" s="11"/>
@@ -8057,7 +8703,7 @@
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="9">
-        <f>IF('Client and family'!$B$39="","",'Client and family'!$B$39)</f>
+        <f>IF('Client and family'!$B$41="","",'Client and family'!$B$41)</f>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -8065,7 +8711,7 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="9">
-        <f>IF('Client and family'!$B$40="","",'Client and family'!$B$40)</f>
+        <f>IF('Client and family'!$B$42="","",'Client and family'!$B$42)</f>
       </c>
       <c r="C25" s="11"/>
       <c r="D25" s="11"/>
@@ -8073,7 +8719,7 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="9">
-        <f>IF('Client and family'!$B$41="","",'Client and family'!$B$41)</f>
+        <f>IF('Client and family'!$B$43="","",'Client and family'!$B$43)</f>
       </c>
       <c r="C26" s="11"/>
       <c r="D26" s="11"/>
@@ -8081,7 +8727,7 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="9">
-        <f>IF('Client and family'!$B$42="","",'Client and family'!$B$42)</f>
+        <f>IF('Client and family'!$B$44="","",'Client and family'!$B$44)</f>
       </c>
       <c r="C27" s="11"/>
       <c r="D27" s="11"/>
@@ -8089,7 +8735,7 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="9">
-        <f>IF('Client and family'!$B$43="","",'Client and family'!$B$43)</f>
+        <f>IF('Client and family'!$B$45="","",'Client and family'!$B$45)</f>
       </c>
       <c r="C28" s="11"/>
       <c r="D28" s="11"/>
@@ -8097,7 +8743,7 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="9">
-        <f>IF('Client and family'!$B$44="","",'Client and family'!$B$44)</f>
+        <f>IF('Client and family'!$B$46="","",'Client and family'!$B$46)</f>
       </c>
       <c r="C29" s="11"/>
       <c r="D29" s="11"/>
@@ -8105,7 +8751,7 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="9">
-        <f>IF('Client and family'!$B$45="","",'Client and family'!$B$45)</f>
+        <f>IF('Client and family'!$B$47="","",'Client and family'!$B$47)</f>
       </c>
       <c r="C30" s="11"/>
       <c r="D30" s="11"/>
@@ -8113,17 +8759,17 @@
     </row>
     <row r="31" ht="30" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="29">
-        <f>IF('Client and family'!$C$49="","",'Client and family'!$C$49)</f>
-      </c>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
+        <v>67</v>
+      </c>
+      <c r="C31" s="30">
+        <f>IF('Client and family'!$C$51="","",'Client and family'!$C$51)</f>
+      </c>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
     </row>
     <row r="33" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="4" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -8131,7 +8777,7 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="7" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="C34" s="11"/>
       <c r="D34" s="11"/>
@@ -8139,7 +8785,7 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -8147,7 +8793,7 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
@@ -8155,7 +8801,7 @@
     </row>
     <row r="37" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="7" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
@@ -8163,7 +8809,7 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="7" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="C38" s="14"/>
       <c r="D38" s="14"/>
@@ -8171,7 +8817,7 @@
     </row>
     <row r="40" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
@@ -8179,7 +8825,7 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C41" s="14"/>
       <c r="D41" s="14"/>
@@ -8187,7 +8833,7 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
@@ -8195,7 +8841,7 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="15"/>
@@ -8203,7 +8849,7 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="C44" s="11"/>
       <c r="D44" s="11"/>
@@ -8211,7 +8857,7 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="7" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="15"/>
@@ -8219,7 +8865,7 @@
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="7" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
@@ -8227,7 +8873,7 @@
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="7" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="15"/>
@@ -8235,7 +8881,7 @@
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C48" s="11"/>
       <c r="D48" s="11"/>
@@ -8243,7 +8889,7 @@
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="15"/>
@@ -8251,7 +8897,7 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="C50" s="14"/>
       <c r="D50" s="14"/>
@@ -8259,7 +8905,7 @@
     </row>
     <row r="51" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="7" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="C51" s="11"/>
       <c r="D51" s="11"/>
@@ -8267,7 +8913,7 @@
     </row>
     <row r="53" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="4" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
@@ -8275,7 +8921,7 @@
     </row>
     <row r="54" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="7" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
@@ -8283,7 +8929,7 @@
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="7" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="C55" s="11"/>
       <c r="D55" s="11"/>
@@ -8291,7 +8937,7 @@
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="7" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="15"/>
@@ -8299,7 +8945,7 @@
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="7" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="C57" s="11"/>
       <c r="D57" s="11"/>
@@ -8307,7 +8953,7 @@
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="7" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="15"/>
@@ -8315,7 +8961,7 @@
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="7" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11"/>
@@ -8323,7 +8969,7 @@
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" s="7" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="15"/>
@@ -8331,7 +8977,7 @@
     </row>
     <row r="61" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" s="7" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11"/>
@@ -8339,7 +8985,7 @@
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B62" s="7" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
@@ -8347,7 +8993,7 @@
     </row>
     <row r="63" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B63" s="7" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11"/>
@@ -8355,7 +9001,7 @@
     </row>
     <row r="65" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="5"/>
@@ -8363,24 +9009,24 @@
     </row>
     <row r="66" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="C66" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="D66" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="13" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
@@ -8415,7 +9061,7 @@
     </row>
     <row r="75" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B75" s="4" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C75" s="5"/>
       <c r="D75" s="5"/>
@@ -8423,7 +9069,7 @@
     </row>
     <row r="76" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B76" s="7" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11"/>
@@ -8431,70 +9077,70 @@
     </row>
     <row r="77" hidden="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="C77" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="D77" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="13" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="C78" s="13" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="11"/>
-      <c r="C79" s="26"/>
+      <c r="C79" s="27"/>
       <c r="D79" s="11"/>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="11"/>
-      <c r="C80" s="26"/>
+      <c r="C80" s="27"/>
       <c r="D80" s="11"/>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="11"/>
-      <c r="C81" s="26"/>
+      <c r="C81" s="27"/>
       <c r="D81" s="11"/>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="11"/>
-      <c r="C82" s="26"/>
+      <c r="C82" s="27"/>
       <c r="D82" s="11"/>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="11"/>
-      <c r="C83" s="26"/>
+      <c r="C83" s="27"/>
       <c r="D83" s="11"/>
     </row>
     <row r="85" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B85" s="4" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C85" s="5"/>
       <c r="D85" s="5"/>
       <c r="E85" s="5"/>
     </row>
     <row r="86" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B86" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="C86" s="28"/>
-      <c r="D86" s="28"/>
-      <c r="E86" s="28"/>
+      <c r="B86" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="C86" s="29"/>
+      <c r="D86" s="29"/>
+      <c r="E86" s="29"/>
     </row>
     <row r="87" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B87" s="7" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11"/>
@@ -8502,7 +9148,7 @@
     </row>
     <row r="88" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B88" s="7" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11"/>
@@ -8510,7 +9156,7 @@
     </row>
     <row r="89" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B89" s="7" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11"/>
@@ -8518,7 +9164,7 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B90" s="7" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11"/>
@@ -8526,7 +9172,7 @@
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B91" s="7" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11"/>
@@ -8534,7 +9180,7 @@
     </row>
     <row r="93" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B93" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C93" s="5"/>
       <c r="D93" s="5"/>
@@ -8542,7 +9188,7 @@
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B94" s="7" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11"/>
@@ -8550,7 +9196,7 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B95" s="7" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11"/>
@@ -8558,7 +9204,7 @@
     </row>
     <row r="96" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B96" s="7" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11"/>
@@ -8566,7 +9212,7 @@
     </row>
     <row r="97" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B97" s="7" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C97" s="14"/>
       <c r="D97" s="14"/>
@@ -8574,7 +9220,7 @@
     </row>
     <row r="99" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B99" s="4" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C99" s="5"/>
       <c r="D99" s="5"/>
@@ -8582,7 +9228,7 @@
     </row>
     <row r="100" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B100" s="7" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11"/>
@@ -8590,7 +9236,7 @@
     </row>
     <row r="101" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B101" s="7" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C101" s="11"/>
       <c r="D101" s="11"/>
@@ -8598,7 +9244,7 @@
     </row>
     <row r="102" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B102" s="7" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11"/>
@@ -8606,7 +9252,7 @@
     </row>
     <row r="103" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B103" s="7" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C103" s="11"/>
       <c r="D103" s="11"/>
@@ -8614,7 +9260,7 @@
     </row>
     <row r="104" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B104" s="7" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11"/>
@@ -8622,7 +9268,7 @@
     </row>
     <row r="105" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B105" s="7" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="C105" s="15"/>
       <c r="D105" s="15"/>
@@ -8630,7 +9276,7 @@
     </row>
     <row r="106" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B106" s="7" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11"/>
@@ -8638,7 +9284,7 @@
     </row>
     <row r="108" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B108" s="4" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C108" s="5"/>
       <c r="D108" s="5"/>
@@ -8646,7 +9292,7 @@
     </row>
     <row r="109" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B109" s="7" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C109" s="14"/>
       <c r="D109" s="14"/>
@@ -8654,7 +9300,7 @@
     </row>
     <row r="110" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B110" s="7" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11"/>
@@ -8662,7 +9308,7 @@
     </row>
     <row r="111" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B111" s="7" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11"/>
@@ -8670,7 +9316,7 @@
     </row>
     <row r="112" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B112" s="7" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="C112" s="14"/>
       <c r="D112" s="14"/>
@@ -8678,7 +9324,7 @@
     </row>
     <row r="113" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B113" s="7" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="C113" s="11"/>
       <c r="D113" s="11"/>
@@ -8686,7 +9332,7 @@
     </row>
     <row r="115" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B115" s="4" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="C115" s="5"/>
       <c r="D115" s="5"/>
@@ -8694,7 +9340,7 @@
     </row>
     <row r="116" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B116" s="7" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C116" s="14"/>
       <c r="D116" s="14"/>
@@ -8702,7 +9348,7 @@
     </row>
     <row r="117" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B117" s="7" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="C117" s="11"/>
       <c r="D117" s="11"/>
@@ -8710,7 +9356,7 @@
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B118" s="7" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11"/>
@@ -8718,7 +9364,7 @@
     </row>
     <row r="120" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B120" s="4" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="C120" s="5"/>
       <c r="D120" s="5"/>
@@ -8726,7 +9372,7 @@
     </row>
     <row r="121" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B121" s="7" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="C121" s="11"/>
       <c r="D121" s="11"/>
@@ -8734,7 +9380,7 @@
     </row>
     <row r="123" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B123" s="4" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C123" s="5"/>
       <c r="D123" s="5"/>
@@ -8742,7 +9388,7 @@
     </row>
     <row r="124" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B124" s="7" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="C124" s="11"/>
       <c r="D124" s="11"/>
@@ -8750,7 +9396,7 @@
     </row>
     <row r="126" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B126" s="4" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="C126" s="5"/>
       <c r="D126" s="5"/>
@@ -8758,7 +9404,7 @@
     </row>
     <row r="127" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B127" s="7" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="C127" s="11"/>
       <c r="D127" s="11"/>
@@ -8766,7 +9412,7 @@
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B128" s="7" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C128" s="15"/>
       <c r="D128" s="15"/>
@@ -8774,7 +9420,7 @@
     </row>
     <row r="129" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B129" s="7" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="C129" s="11"/>
       <c r="D129" s="11"/>
@@ -8782,7 +9428,7 @@
     </row>
     <row r="130" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B130" s="7" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="C130" s="15"/>
       <c r="D130" s="15"/>
@@ -8790,7 +9436,7 @@
     </row>
     <row r="131" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B131" s="7" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="C131" s="11"/>
       <c r="D131" s="11"/>
@@ -8798,7 +9444,7 @@
     </row>
     <row r="132" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B132" s="7" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="C132" s="11"/>
       <c r="D132" s="11"/>
@@ -8806,7 +9452,7 @@
     </row>
     <row r="133" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B133" s="7" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="C133" s="15"/>
       <c r="D133" s="15"/>
@@ -8814,7 +9460,7 @@
     </row>
     <row r="134" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B134" s="7" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="11"/>
@@ -8822,7 +9468,7 @@
     </row>
     <row r="135" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B135" s="7" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="C135" s="15"/>
       <c r="D135" s="15"/>
@@ -8830,7 +9476,7 @@
     </row>
     <row r="136" ht="26" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B136" s="7" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="C136" s="11"/>
       <c r="D136" s="11"/>
@@ -8838,7 +9484,7 @@
     </row>
     <row r="137" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B137" s="7" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C137" s="11"/>
       <c r="D137" s="11"/>
@@ -8846,7 +9492,7 @@
     </row>
     <row r="138" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B138" s="7" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C138" s="11"/>
       <c r="D138" s="11"/>
@@ -8854,7 +9500,7 @@
     </row>
     <row r="139" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B139" s="7" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="C139" s="14"/>
       <c r="D139" s="14"/>
@@ -8862,7 +9508,7 @@
     </row>
     <row r="140" ht="36" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B140" s="7" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="C140" s="11"/>
       <c r="D140" s="11"/>
@@ -8870,7 +9516,7 @@
     </row>
     <row r="142" ht="18" customHeight="1" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B142" s="4" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="C142" s="5"/>
       <c r="D142" s="5"/>
@@ -8878,7 +9524,7 @@
     </row>
     <row r="143" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B143" s="7" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="C143" s="11"/>
       <c r="D143" s="11"/>
@@ -8886,7 +9532,7 @@
     </row>
     <row r="144" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B144" s="7" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C144" s="11"/>
       <c r="D144" s="11"/>
@@ -8894,7 +9540,7 @@
     </row>
     <row r="145" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B145" s="7" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="C145" s="11"/>
       <c r="D145" s="11"/>
@@ -8902,7 +9548,7 @@
     </row>
     <row r="146" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B146" s="7" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="C146" s="11"/>
       <c r="D146" s="11"/>
@@ -8910,7 +9556,7 @@
     </row>
     <row r="147" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B147" s="7" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="C147" s="11"/>
       <c r="D147" s="11"/>
@@ -8918,7 +9564,7 @@
     </row>
     <row r="148" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B148" s="7" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="C148" s="11"/>
       <c r="D148" s="11"/>
@@ -8926,7 +9572,7 @@
     </row>
     <row r="149" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B149" s="7" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="C149" s="11"/>
       <c r="D149" s="11"/>
@@ -8934,7 +9580,7 @@
     </row>
     <row r="150" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B150" s="7" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="C150" s="11"/>
       <c r="D150" s="11"/>
@@ -8942,7 +9588,7 @@
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B151" s="7" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C151" s="11"/>
       <c r="D151" s="11"/>
@@ -8950,7 +9596,7 @@
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B152" s="7" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="C152" s="11"/>
       <c r="D152" s="11"/>
@@ -8958,7 +9604,7 @@
     </row>
     <row r="153" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B153" s="7" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="C153" s="11"/>
       <c r="D153" s="11"/>
@@ -8966,7 +9612,7 @@
     </row>
     <row r="154" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B154" s="7" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="C154" s="11"/>
       <c r="D154" s="11"/>
@@ -8974,7 +9620,7 @@
     </row>
     <row r="155" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B155" s="7" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="C155" s="11"/>
       <c r="D155" s="11"/>
@@ -8982,7 +9628,7 @@
     </row>
     <row r="156" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B156" s="7" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C156" s="11"/>
       <c r="D156" s="11"/>
@@ -8990,7 +9636,7 @@
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B157" s="7" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C157" s="11"/>
       <c r="D157" s="11"/>
@@ -8998,7 +9644,7 @@
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B158" s="7" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C158" s="15"/>
       <c r="D158" s="15"/>
@@ -9006,7 +9652,7 @@
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B159" s="7" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="C159" s="11"/>
       <c r="D159" s="11"/>
@@ -9014,7 +9660,7 @@
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B160" s="7" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="C160" s="11"/>
       <c r="D160" s="11"/>
@@ -9022,7 +9668,7 @@
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B161" s="7" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C161" s="15"/>
       <c r="D161" s="15"/>
@@ -9030,7 +9676,7 @@
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B162" s="7" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="C162" s="11"/>
       <c r="D162" s="11"/>
@@ -9038,7 +9684,7 @@
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B163" s="7" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C163" s="11"/>
       <c r="D163" s="11"/>
@@ -9046,7 +9692,7 @@
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B164" s="7" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="C164" s="15"/>
       <c r="D164" s="15"/>
@@ -9054,7 +9700,7 @@
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B165" s="7" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="C165" s="11"/>
       <c r="D165" s="11"/>
@@ -9062,7 +9708,7 @@
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B166" s="7" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="C166" s="11"/>
       <c r="D166" s="11"/>
@@ -9070,7 +9716,7 @@
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B167" s="7" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="C167" s="11"/>
       <c r="D167" s="11"/>
@@ -9078,7 +9724,7 @@
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B168" s="7" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C168" s="15"/>
       <c r="D168" s="15"/>
@@ -9086,7 +9732,7 @@
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B169" s="7" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C169" s="11"/>
       <c r="D169" s="11"/>
@@ -9094,7 +9740,7 @@
     </row>
     <row r="170" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B170" s="7" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="C170" s="11"/>
       <c r="D170" s="11"/>
@@ -9102,7 +9748,7 @@
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B171" s="7" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="C171" s="15"/>
       <c r="D171" s="15"/>
@@ -9110,7 +9756,7 @@
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B172" s="7" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C172" s="11"/>
       <c r="D172" s="11"/>
@@ -9118,7 +9764,7 @@
     </row>
     <row r="173" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B173" s="7" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="C173" s="11"/>
       <c r="D173" s="11"/>
@@ -9257,16 +9903,16 @@
       <formula1>'Lists'!$B$2:$B$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C100">
-      <formula1>'Lists'!$AG$2:$AG$4</formula1>
+      <formula1>'Lists'!$AH$2:$AH$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C103">
-      <formula1>'Lists'!$AH$2:$AH$3</formula1>
+      <formula1>'Lists'!$AI$2:$AI$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C109">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C111">
-      <formula1>'Lists'!$AI$2:$AI$4</formula1>
+      <formula1>'Lists'!$AJ$2:$AJ$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C112">
       <formula1>'Lists'!$F$2:$F$3</formula1>
@@ -9275,37 +9921,37 @@
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C121">
-      <formula1>'Lists'!$AJ$2:$AJ$3</formula1>
+      <formula1>'Lists'!$AK$2:$AK$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C136">
-      <formula1>'Lists'!$AK$2:$AK$3</formula1>
+      <formula1>'Lists'!$AL$2:$AL$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C137">
-      <formula1>'Lists'!$AL$2:$AL$3</formula1>
+      <formula1>'Lists'!$AM$2:$AM$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C139">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C143">
-      <formula1>'Lists'!$AM$2:$AM$4</formula1>
+      <formula1>'Lists'!$AN$2:$AN$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C145">
-      <formula1>'Lists'!$AN$2:$AN$3</formula1>
+      <formula1>'Lists'!$AO$2:$AO$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C146">
-      <formula1>'Lists'!$AO$2:$AO$3</formula1>
+      <formula1>'Lists'!$AP$2:$AP$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C147">
-      <formula1>'Lists'!$AP$2:$AP$3</formula1>
+      <formula1>'Lists'!$AQ$2:$AQ$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C166">
-      <formula1>'Lists'!$AQ$2:$AQ$3</formula1>
+      <formula1>'Lists'!$AR$2:$AR$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C173">
-      <formula1>'Lists'!$AR$2:$AR$3</formula1>
+      <formula1>'Lists'!$AS$2:$AS$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C34">
-      <formula1>'Lists'!$Y$2:$Y$4</formula1>
+      <formula1>'Lists'!$Z$2:$Z$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C38">
       <formula1>'Lists'!$F$2:$F$3</formula1>
@@ -9317,32 +9963,32 @@
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C54">
-      <formula1>'Lists'!$Z$2:$Z$4</formula1>
+      <formula1>'Lists'!$AA$2:$AA$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C61">
-      <formula1>'Lists'!$AA$2:$AA$4</formula1>
+      <formula1>'Lists'!$AB$2:$AB$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Name" prompt="Pick a family member from the list, or type any name." sqref="C68:D73">
       <formula1>'Lists'!$B$2:$B$10</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C76">
-      <formula1>'Lists'!$AB$2:$AB$5</formula1>
+      <formula1>'Lists'!$AC$2:$AC$5</formula1>
     </dataValidation>
     <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Percentage" error="Please type the percentage as a plain number from 1 to 100, e.g. 60 for 60%. Do not add the % sign." sqref="C79:C83">
       <formula1>1</formula1>
       <formula2>100</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C87">
-      <formula1>'Lists'!$AC$2:$AC$3</formula1>
+      <formula1>'Lists'!$AD$2:$AD$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C89">
-      <formula1>'Lists'!$AD$2:$AD$3</formula1>
+      <formula1>'Lists'!$AE$2:$AE$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C94">
-      <formula1>'Lists'!$AE$2:$AE$4</formula1>
+      <formula1>'Lists'!$AF$2:$AF$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C96">
-      <formula1>'Lists'!$AF$2:$AF$4</formula1>
+      <formula1>'Lists'!$AG$2:$AG$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C97">
       <formula1>'Lists'!$F$2:$F$3</formula1>
@@ -9361,357 +10007,4 @@
     <brk id="63" max="16838" man="1"/>
   </rowBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:F34"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="52" customWidth="1"/>
-    <col min="3" max="6" width="18" customWidth="1"/>
-    <col min="26" max="26" width="18" hidden="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="3" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="C6" s="33">
-        <f>IF('Start here'!$C$19="","Not yet given",'Start here'!$C$19)</f>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="34">
-        <f>'Lists'!$A$2</f>
-      </c>
-      <c r="D8" s="34">
-        <f>'Lists'!$A$3</f>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="27" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="C10" s="24">
-        <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$2)</f>
-      </c>
-      <c r="D10" s="24">
-        <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$3)</f>
-      </c>
-      <c r="E10" s="24">
-        <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,"Joint")</f>
-      </c>
-      <c r="F10" s="24">
-        <f>SUM(C10:E10)</f>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C11" s="24">
-        <f>N('Companies and trusts'!$C$49)+N('Companies and trusts'!$C$94)+N('Companies and trusts'!$C$139)+N('Companies and trusts'!$C$184)</f>
-      </c>
-      <c r="D11" s="24">
-        <f>N('Companies and trusts'!$D$49)+N('Companies and trusts'!$D$94)+N('Companies and trusts'!$D$139)+N('Companies and trusts'!$D$184)</f>
-      </c>
-      <c r="E11" s="24">
-        <v>0</v>
-      </c>
-      <c r="F11" s="24">
-        <f>SUM(C11:E11)</f>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="C12" s="24">
-        <f>IF('Companies and trusts'!$C$22="Credit",N('Companies and trusts'!$C$23),0)+IF('Companies and trusts'!$C$68="Credit",N('Companies and trusts'!$C$69),0)+IF('Companies and trusts'!$C$113="Credit",N('Companies and trusts'!$C$114),0)+IF('Companies and trusts'!$C$158="Credit",N('Companies and trusts'!$C$159),0)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
-      </c>
-      <c r="D12" s="24">
-        <f>IF('Companies and trusts'!$D$22="Credit",N('Companies and trusts'!$D$23),0)+IF('Companies and trusts'!$D$68="Credit",N('Companies and trusts'!$D$69),0)+IF('Companies and trusts'!$D$113="Credit",N('Companies and trusts'!$D$114),0)+IF('Companies and trusts'!$D$158="Credit",N('Companies and trusts'!$D$159),0)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$3,'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
-      </c>
-      <c r="E12" s="24">
-        <f>SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,"Joint",'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
-      </c>
-      <c r="F12" s="24">
-        <f>SUM(C12:E12)</f>
-      </c>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="C13" s="24">
-        <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
-      </c>
-      <c r="D13" s="24">
-        <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$3,'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
-      </c>
-      <c r="E13" s="24">
-        <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,"Joint",'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
-      </c>
-      <c r="F13" s="24">
-        <f>SUM(C13:E13)</f>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="C14" s="24">
-        <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$2)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
-      </c>
-      <c r="D14" s="24">
-        <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$3)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$3,'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
-      </c>
-      <c r="E14" s="24">
-        <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,"Joint")+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,"Joint",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
-      </c>
-      <c r="F14" s="24">
-        <f>SUM(C14:E14)</f>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="35" t="s">
-        <v>371</v>
-      </c>
-      <c r="C15" s="23">
-        <f>C10+C11+C12+C13+C14</f>
-      </c>
-      <c r="D15" s="23">
-        <f>D10+D11+D12+D13+D14</f>
-      </c>
-      <c r="E15" s="23">
-        <f>E10+E11+E12+E13+E14</f>
-      </c>
-      <c r="F15" s="23">
-        <f>SUM(C15:E15)</f>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="27" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="C18" s="24">
-        <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$2)</f>
-      </c>
-      <c r="D18" s="24">
-        <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$3)</f>
-      </c>
-      <c r="E18" s="24">
-        <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,"Joint")</f>
-      </c>
-      <c r="F18" s="24">
-        <f>SUM(C18:E18)</f>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="C19" s="24">
-        <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$2)</f>
-      </c>
-      <c r="D19" s="24">
-        <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$3)</f>
-      </c>
-      <c r="E19" s="24">
-        <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,"Joint")</f>
-      </c>
-      <c r="F19" s="24">
-        <f>SUM(C19:E19)</f>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="C20" s="24">
-        <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,'Lists'!$A$2)</f>
-      </c>
-      <c r="D20" s="24">
-        <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,'Lists'!$A$3)</f>
-      </c>
-      <c r="E20" s="24">
-        <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,"Joint")</f>
-      </c>
-      <c r="F20" s="24">
-        <f>SUM(C20:E20)</f>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="C21" s="24">
-        <f>IF('Companies and trusts'!$C$22="Debit",N('Companies and trusts'!$C$23),0)+IF('Companies and trusts'!$C$68="Debit",N('Companies and trusts'!$C$69),0)+IF('Companies and trusts'!$C$113="Debit",N('Companies and trusts'!$C$114),0)+IF('Companies and trusts'!$C$158="Debit",N('Companies and trusts'!$C$159),0)</f>
-      </c>
-      <c r="D21" s="24">
-        <f>IF('Companies and trusts'!$D$22="Debit",N('Companies and trusts'!$D$23),0)+IF('Companies and trusts'!$D$68="Debit",N('Companies and trusts'!$D$69),0)+IF('Companies and trusts'!$D$113="Debit",N('Companies and trusts'!$D$114),0)+IF('Companies and trusts'!$D$158="Debit",N('Companies and trusts'!$D$159),0)</f>
-      </c>
-      <c r="E21" s="24">
-        <v>0</v>
-      </c>
-      <c r="F21" s="24">
-        <f>SUM(C21:E21)</f>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="35" t="s">
-        <v>377</v>
-      </c>
-      <c r="C22" s="23">
-        <f>C18+C19+C20+C21</f>
-      </c>
-      <c r="D22" s="23">
-        <f>D18+D19+D20+D21</f>
-      </c>
-      <c r="E22" s="23">
-        <f>E18+E19+E20+E21</f>
-      </c>
-      <c r="F22" s="23">
-        <f>SUM(C22:E22)</f>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="36" t="s">
-        <v>378</v>
-      </c>
-      <c r="C24" s="37">
-        <f>C15-C22</f>
-      </c>
-      <c r="D24" s="37">
-        <f>D15-D22</f>
-      </c>
-      <c r="E24" s="37">
-        <f>E15-E22</f>
-      </c>
-      <c r="F24" s="37">
-        <f>SUM(C24:E24)</f>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="27" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="F27" s="24">
-        <f>SUMIFS('Companies and trusts'!$D$34:$D$43,'Companies and trusts'!$C$34:$C$43,"Property")+SUMIFS('Companies and trusts'!$D$79:$D$88,'Companies and trusts'!$C$79:$C$88,"Property")+SUMIFS('Companies and trusts'!$D$124:$D$133,'Companies and trusts'!$C$124:$C$133,"Property")+SUMIFS('Companies and trusts'!$D$169:$D$178,'Companies and trusts'!$C$169:$C$178,"Property")</f>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="F28" s="24">
-        <f>SUMIFS('Companies and trusts'!$D$34:$D$43,'Companies and trusts'!$C$34:$C$43,"Bond")+SUMIFS('Companies and trusts'!$D$79:$D$88,'Companies and trusts'!$C$79:$C$88,"Bond")+SUMIFS('Companies and trusts'!$D$124:$D$133,'Companies and trusts'!$C$124:$C$133,"Bond")+SUMIFS('Companies and trusts'!$D$169:$D$178,'Companies and trusts'!$C$169:$C$178,"Bond")+SUMIFS('Companies and trusts'!$D$34:$D$43,'Companies and trusts'!$C$34:$C$43,"Other debt")+SUMIFS('Companies and trusts'!$D$79:$D$88,'Companies and trusts'!$C$79:$C$88,"Other debt")+SUMIFS('Companies and trusts'!$D$124:$D$133,'Companies and trusts'!$C$124:$C$133,"Other debt")+SUMIFS('Companies and trusts'!$D$169:$D$178,'Companies and trusts'!$C$169:$C$178,"Other debt")</f>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="27" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="F31" s="19">
-        <f>COUNTIF('Assets and debts'!$P$12:$P$19,"Estimate")+COUNTIF('Assets and debts'!$J$26:$J$31,"Estimate")+COUNTIF('Assets and debts'!$J$38:$J$52,"Estimate")+COUNTIF('Assets and debts'!$I$59:$I$70,"Estimate")+COUNTIF('Companies and trusts'!$C$14,"Estimate")+COUNTIF('Companies and trusts'!$C$60,"Estimate")+COUNTIF('Companies and trusts'!$C$105,"Estimate")+COUNTIF('Companies and trusts'!$C$150,"Estimate")+COUNTIF('Companies and trusts'!$F$34:$F$43,"Estimate")+COUNTIF('Companies and trusts'!$F$79:$F$88,"Estimate")+COUNTIF('Companies and trusts'!$F$124:$F$133,"Estimate")+COUNTIF('Companies and trusts'!$F$169:$F$178,"Estimate")</f>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="F32" s="19">
-        <f>SUMPRODUCT(('Assets and debts'!$D$12:$D$19&gt;0)*('Assets and debts'!$F$12:$F$19=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Shares / Unit Trusts")*('Assets and debts'!$F$38:$F$52=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Business Interest")*('Assets and debts'!$F$38:$F$52=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Crypto")*('Assets and debts'!$F$38:$F$52=""))+IF(AND(N('Companies and trusts'!$C$21)&gt;0,'Companies and trusts'!$C$24=""),1,0)+IF(AND(N('Companies and trusts'!$D$21)&gt;0,'Companies and trusts'!$D$24=""),1,0)+IF(AND(N('Companies and trusts'!$C$67)&gt;0,'Companies and trusts'!$C$70=""),1,0)+IF(AND(N('Companies and trusts'!$D$67)&gt;0,'Companies and trusts'!$D$70=""),1,0)+IF(AND(N('Companies and trusts'!$C$112)&gt;0,'Companies and trusts'!$C$115=""),1,0)+IF(AND(N('Companies and trusts'!$D$112)&gt;0,'Companies and trusts'!$D$115=""),1,0)+IF(AND(N('Companies and trusts'!$C$157)&gt;0,'Companies and trusts'!$C$160=""),1,0)+IF(AND(N('Companies and trusts'!$D$157)&gt;0,'Companies and trusts'!$D$160=""),1,0)+SUMPRODUCT(('Companies and trusts'!$D$34:$D$43&gt;0)*('Companies and trusts'!$C$34:$C$43="Property")*('Companies and trusts'!$E$34:$E$43=""))+SUMPRODUCT(('Companies and trusts'!$D$79:$D$88&gt;0)*('Companies and trusts'!$C$79:$C$88="Property")*('Companies and trusts'!$E$79:$E$88=""))+SUMPRODUCT(('Companies and trusts'!$D$124:$D$133&gt;0)*('Companies and trusts'!$C$124:$C$133="Property")*('Companies and trusts'!$E$124:$E$133=""))+SUMPRODUCT(('Companies and trusts'!$D$169:$D$178&gt;0)*('Companies and trusts'!$C$169:$C$178="Property")*('Companies and trusts'!$E$169:$E$178=""))</f>
-      </c>
-    </row>
-    <row r="34" ht="44" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="38">
-        <f>IF('Client and family'!$D$10="","You own R ","Together you own R ")&amp;TEXT(F15,"#,##0")&amp;" and owe R "&amp;TEXT(F22,"#,##0")&amp;", a net worth of R "&amp;TEXT(F24,"#,##0")&amp;"."&amp;IF(F31&gt;0," "&amp;F31&amp;IF(F31=1," figure is an estimate."," figures are estimates."),"")&amp;IF(F32&gt;0," "&amp;F32&amp;IF(F32=1," asset has"," assets have")&amp;" no base cost yet, which we need for capital gains tax.","")</f>
-      </c>
-      <c r="C34" s="38"/>
-      <c r="D34" s="38"/>
-      <c r="E34" s="38"/>
-      <c r="F34" s="38"/>
-    </row>
-  </sheetData>
-  <sheetProtection sheet="1" formatRows="0"/>
-  <mergeCells count="4">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B34:F34"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.6" header="0.25" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Fact find&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/Duwalcoe_Fact_Find_Template.xlsx
+++ b/Duwalcoe_Fact_Find_Template.xlsx
@@ -51,12 +51,12 @@
     <definedName name="FF_K_kids">'Client and family'!$B$38:$Z$38</definedName>
     <definedName name="FF_T_kids">'Client and family'!$B$40:$Z$47</definedName>
     <definedName name="FF_W_dep_notes">'Client and family'!$C$51</definedName>
-    <definedName name="FF_M_ClientID">Lists!$Z$1</definedName>
-    <definedName name="FF_M_ClientName">Lists!$Z$2</definedName>
-    <definedName name="FF_M_Version">Lists!$Z$3</definedName>
-    <definedName name="FF_M_ExportedAt">Lists!$Z$4</definedName>
-    <definedName name="FF_M_ExportedBy">Lists!$Z$5</definedName>
-    <definedName name="FF_M_TemplateVersion">Lists!$Z$7</definedName>
+    <definedName name="FF_M_ClientID">Lists!$AX$1</definedName>
+    <definedName name="FF_M_ClientName">Lists!$AX$2</definedName>
+    <definedName name="FF_M_Version">Lists!$AX$3</definedName>
+    <definedName name="FF_M_ExportedAt">Lists!$AX$4</definedName>
+    <definedName name="FF_M_ExportedBy">Lists!$AX$5</definedName>
+    <definedName name="FF_M_TemplateVersion">Lists!$AX$7</definedName>
     <definedName name="FF_G_ValDate">'Start here'!$C$19</definedName>
     <definedName name="FF_G_CompletedBy">'Start here'!$C$20</definedName>
     <definedName name="FF_G_DateCompleted">'Start here'!$C$21</definedName>
@@ -299,7 +299,7 @@
     <definedName name="FF_W_cl_ce2_id">Will!$C$171</definedName>
     <definedName name="FF_W_cl_ce2_rel">Will!$C$172</definedName>
     <definedName name="FF_W_cl_collect">Will!$C$173</definedName>
-    <definedName name="FF_M_Breaks">Lists!$Z$8</definedName>
+    <definedName name="FF_M_Breaks">Lists!$AX$8</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Start here'!$A1:$F22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Start here'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Meeting notes'!$A1:$C44</definedName>
@@ -324,7 +324,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="842" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="560">
   <si>
     <t>Duwalcoe Financial Consultants CC</t>
   </si>
@@ -1568,72 +1568,75 @@
     <t>passes</t>
   </si>
   <si>
+    <t>forWhom</t>
+  </si>
+  <si>
+    <t>w_e_status</t>
+  </si>
+  <si>
+    <t>w_tr_choice</t>
+  </si>
+  <si>
+    <t>w_tr_term</t>
+  </si>
+  <si>
+    <t>w_res_choice</t>
+  </si>
+  <si>
+    <t>w_sa_off</t>
+  </si>
+  <si>
+    <t>w_sa_fire</t>
+  </si>
+  <si>
+    <t>w_lw</t>
+  </si>
+  <si>
+    <t>w_organ</t>
+  </si>
+  <si>
+    <t>w_fw</t>
+  </si>
+  <si>
+    <t>w_fw_cover</t>
+  </si>
+  <si>
+    <t>w_da_social</t>
+  </si>
+  <si>
+    <t>w_lo</t>
+  </si>
+  <si>
+    <t>w_ex_security</t>
+  </si>
+  <si>
+    <t>w_ex_fee</t>
+  </si>
+  <si>
+    <t>w_cl_lang</t>
+  </si>
+  <si>
+    <t>w_cl_wt</t>
+  </si>
+  <si>
+    <t>w_cl_wt_sp_inc</t>
+  </si>
+  <si>
+    <t>w_cl_wt_kids_cap</t>
+  </si>
+  <si>
+    <t>w_cl_exec</t>
+  </si>
+  <si>
+    <t>w_cl_collect</t>
+  </si>
+  <si>
     <t>full names</t>
   </si>
   <si>
     <t>ClientID</t>
   </si>
   <si>
-    <t>w_e_status</t>
-  </si>
-  <si>
-    <t>w_tr_choice</t>
-  </si>
-  <si>
-    <t>w_tr_term</t>
-  </si>
-  <si>
-    <t>w_res_choice</t>
-  </si>
-  <si>
-    <t>w_sa_off</t>
-  </si>
-  <si>
-    <t>w_sa_fire</t>
-  </si>
-  <si>
-    <t>w_lw</t>
-  </si>
-  <si>
-    <t>w_organ</t>
-  </si>
-  <si>
-    <t>w_fw</t>
-  </si>
-  <si>
-    <t>w_fw_cover</t>
-  </si>
-  <si>
-    <t>w_da_social</t>
-  </si>
-  <si>
-    <t>w_lo</t>
-  </si>
-  <si>
-    <t>w_ex_security</t>
-  </si>
-  <si>
-    <t>w_ex_fee</t>
-  </si>
-  <si>
-    <t>w_cl_lang</t>
-  </si>
-  <si>
-    <t>w_cl_wt</t>
-  </si>
-  <si>
-    <t>w_cl_wt_sp_inc</t>
-  </si>
-  <si>
-    <t>w_cl_wt_kids_cap</t>
-  </si>
-  <si>
-    <t>w_cl_exec</t>
-  </si>
-  <si>
-    <t>w_cl_collect</t>
-  </si>
-  <si>
     <t>Mr.</t>
   </si>
   <si>
@@ -1670,48 +1673,48 @@
     <t>Books</t>
   </si>
   <si>
+    <t>I do not have an existing will</t>
+  </si>
+  <si>
+    <t>Yes — establish a testamentary trust</t>
+  </si>
+  <si>
+    <t>Terminates when beneficiary reaches a set age (below)</t>
+  </si>
+  <si>
+    <t>Entire residue to my spouse / life partner</t>
+  </si>
+  <si>
+    <t>Yes — I wish a living will to be drafted</t>
+  </si>
+  <si>
+    <t>I wish to donate my organs and tissues where medically suitable</t>
+  </si>
+  <si>
+    <t>Burial</t>
+  </si>
+  <si>
+    <t>I have a funeral policy (details below)</t>
+  </si>
+  <si>
+    <t>Memorialised</t>
+  </si>
+  <si>
+    <t>Yes — a separate letter of wishes will be drafted</t>
+  </si>
+  <si>
+    <t>Waive security (bond of security) — usual for a family executor</t>
+  </si>
+  <si>
+    <t>Agreed reduced rate (below)</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
     <t>ClientName</t>
   </si>
   <si>
-    <t>I do not have an existing will</t>
-  </si>
-  <si>
-    <t>Yes — establish a testamentary trust</t>
-  </si>
-  <si>
-    <t>Terminates when beneficiary reaches a set age (below)</t>
-  </si>
-  <si>
-    <t>Entire residue to my spouse / life partner</t>
-  </si>
-  <si>
-    <t>Yes — I wish a living will to be drafted</t>
-  </si>
-  <si>
-    <t>I wish to donate my organs and tissues where medically suitable</t>
-  </si>
-  <si>
-    <t>Burial</t>
-  </si>
-  <si>
-    <t>I have a funeral policy (details below)</t>
-  </si>
-  <si>
-    <t>Memorialised</t>
-  </si>
-  <si>
-    <t>Yes — a separate letter of wishes will be drafted</t>
-  </si>
-  <si>
-    <t>Waive security (bond of security) — usual for a family executor</t>
-  </si>
-  <si>
-    <t>Agreed reduced rate (below)</t>
-  </si>
-  <si>
-    <t>English</t>
-  </si>
-  <si>
     <t>Mrs.</t>
   </si>
   <si>
@@ -1760,46 +1763,52 @@
     <t>Disability</t>
   </si>
   <si>
+    <t>Once-off capital</t>
+  </si>
+  <si>
+    <t>I have an existing will</t>
+  </si>
+  <si>
+    <t>No — distribute directly</t>
+  </si>
+  <si>
+    <t>Trustees may pay capital sooner for education, medical, first home, etc.</t>
+  </si>
+  <si>
+    <t>Entire residue to my children equally, per stirpes</t>
+  </si>
+  <si>
+    <t>I hold assets offshore (a separate offshore will may be recommended)</t>
+  </si>
+  <si>
+    <t>I own firearms (beneficiary must hold a valid licence)</t>
+  </si>
+  <si>
+    <t>No — I do not want a living will</t>
+  </si>
+  <si>
+    <t>I do not wish to donate organs or tissues</t>
+  </si>
+  <si>
+    <t>Cremation</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Require security</t>
+  </si>
+  <si>
+    <t>Full statutory rate of 3.5% + VAT</t>
+  </si>
+  <si>
+    <t>Afrikaans</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>1.2</t>
-  </si>
-  <si>
-    <t>No — distribute directly</t>
-  </si>
-  <si>
-    <t>Trustees may pay capital sooner for education, medical, first home, etc.</t>
-  </si>
-  <si>
-    <t>Entire residue to my children equally, per stirpes</t>
-  </si>
-  <si>
-    <t>I hold assets offshore (a separate offshore will may be recommended)</t>
-  </si>
-  <si>
-    <t>I own firearms (beneficiary must hold a valid licence)</t>
-  </si>
-  <si>
-    <t>No — I do not want a living will</t>
-  </si>
-  <si>
-    <t>I do not wish to donate organs or tissues</t>
-  </si>
-  <si>
-    <t>Cremation</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>Require security</t>
-  </si>
-  <si>
-    <t>Full statutory rate of 3.5% + VAT</t>
-  </si>
-  <si>
-    <t>Afrikaans</t>
+    <t>1.3</t>
   </si>
   <si>
     <t>Ms.</t>
@@ -1844,36 +1853,36 @@
     <t>Dread Disease</t>
   </si>
   <si>
+    <t>I have a codicil / amendment to a prior will</t>
+  </si>
+  <si>
+    <t>Only if beneficiaries are still minors at date of death</t>
+  </si>
+  <si>
+    <t>Income distributed as needed; capital held until termination age</t>
+  </si>
+  <si>
+    <t>Entire residue to my children equally, per capita</t>
+  </si>
+  <si>
+    <t>I already have a living will (date below)</t>
+  </si>
+  <si>
+    <t>I am already a registered organ donor</t>
+  </si>
+  <si>
+    <t>No preference — leave to family</t>
+  </si>
+  <si>
+    <t>Transferred</t>
+  </si>
+  <si>
+    <t>Other (below)</t>
+  </si>
+  <si>
     <t>ExportedAt</t>
   </si>
   <si>
-    <t>I have a codicil / amendment to a prior will</t>
-  </si>
-  <si>
-    <t>Only if beneficiaries are still minors at date of death</t>
-  </si>
-  <si>
-    <t>Income distributed as needed; capital held until termination age</t>
-  </si>
-  <si>
-    <t>Entire residue to my children equally, per capita</t>
-  </si>
-  <si>
-    <t>I already have a living will (date below)</t>
-  </si>
-  <si>
-    <t>I am already a registered organ donor</t>
-  </si>
-  <si>
-    <t>No preference — leave to family</t>
-  </si>
-  <si>
-    <t>Transferred</t>
-  </si>
-  <si>
-    <t>Other (below)</t>
-  </si>
-  <si>
     <t>Miss</t>
   </si>
   <si>
@@ -1907,10 +1916,10 @@
     <t>Retirement</t>
   </si>
   <si>
+    <t>Split as follows (table below)</t>
+  </si>
+  <si>
     <t>ExportedBy</t>
-  </si>
-  <si>
-    <t>Split as follows (table below)</t>
   </si>
   <si>
     <t>Dr.</t>
@@ -2606,10 +2615,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AS34"/>
+  <dimension ref="A1:AX34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>394</v>
       </c>
@@ -2680,102 +2689,108 @@
         <v>217</v>
       </c>
       <c r="X1" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y1" t="s">
         <v>414</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>415</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>416</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>417</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>418</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>419</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>420</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>421</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>422</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>423</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>424</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>425</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>426</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>427</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>428</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>429</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>430</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>431</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>432</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>433</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>434</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>435</v>
       </c>
-    </row>
-    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AW1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2">
-        <f>IF('Client and family'!$C$12&lt;&gt;"",'Client and family'!$C$12,IF('Lists'!$X$2&lt;&gt;"",LEFT(TRIM('Lists'!$X$2),FIND(" ",TRIM('Lists'!$X$2)&amp;" ")-1),"Client"))</f>
+        <f>IF('Client and family'!$C$12&lt;&gt;"",'Client and family'!$C$12,IF('Lists'!$AU$2&lt;&gt;"",LEFT(TRIM('Lists'!$AU$2),FIND(" ",TRIM('Lists'!$AU$2)&amp;" ")-1),"Client"))</f>
       </c>
       <c r="B2">
-        <f>IF('Lists'!$X$3="","",'Lists'!$X$3)</f>
+        <f>IF('Lists'!$AU$3="","",'Lists'!$AU$3)</f>
       </c>
       <c r="C2">
         <f>IF('Assets and debts'!$B$12="",""," "&amp;'Assets and debts'!$B$12)</f>
       </c>
       <c r="D2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F2" t="s">
         <v>86</v>
       </c>
       <c r="G2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="I2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="K2" t="s">
         <v>85</v>
@@ -2784,22 +2799,22 @@
         <v>96</v>
       </c>
       <c r="M2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N2" t="s">
         <v>156</v>
       </c>
       <c r="O2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="S2" t="s">
         <v>202</v>
@@ -2808,7 +2823,7 @@
         <v>85</v>
       </c>
       <c r="U2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="V2" t="s">
         <v>137</v>
@@ -2816,11 +2831,11 @@
       <c r="W2" t="s">
         <v>232</v>
       </c>
-      <c r="X2">
-        <f>TRIM('Client and family'!$C$10&amp;" "&amp;'Client and family'!$C$11)</f>
+      <c r="X2" t="s">
+        <v>233</v>
       </c>
       <c r="Y2" t="s">
-        <v>448</v>
+        <v>137</v>
       </c>
       <c r="Z2" t="s">
         <v>449</v>
@@ -2835,10 +2850,10 @@
         <v>452</v>
       </c>
       <c r="AD2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AE2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AF2" t="s">
         <v>453</v>
@@ -2882,10 +2897,16 @@
       <c r="AS2" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AU2">
+        <f>TRIM('Client and family'!$C$10&amp;" "&amp;'Client and family'!$C$11)</f>
+      </c>
+      <c r="AW2" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f>IF('Lists'!$X$3&lt;&gt;"",LEFT(TRIM('Lists'!$X$3),FIND(" ",TRIM('Lists'!$X$3)&amp;" ")-1),"Spouse")</f>
+        <f>IF('Lists'!$AU$3&lt;&gt;"",LEFT(TRIM('Lists'!$AU$3),FIND(" ",TRIM('Lists'!$AU$3)&amp;" ")-1),"Spouse")</f>
       </c>
       <c r="B3">
         <f>IF('Client and family'!$B$40="","",'Client and family'!$B$40)</f>
@@ -2894,55 +2915,55 @@
         <f>IF('Assets and debts'!$B$13="",""," "&amp;'Assets and debts'!$B$13)</f>
       </c>
       <c r="D3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F3" t="s">
         <v>138</v>
       </c>
       <c r="G3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="I3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="K3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M3" t="s">
         <v>173</v>
       </c>
       <c r="N3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="R3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="S3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="T3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="U3" t="s">
         <v>158</v>
@@ -2951,58 +2972,58 @@
         <v>157</v>
       </c>
       <c r="W3" t="s">
-        <v>477</v>
-      </c>
-      <c r="X3">
-        <f>TRIM('Client and family'!$D$10&amp;" "&amp;'Client and family'!$D$11)</f>
+        <v>478</v>
+      </c>
+      <c r="X3" t="s">
+        <v>479</v>
       </c>
       <c r="Y3" t="s">
-        <v>478</v>
+        <v>157</v>
       </c>
       <c r="Z3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AB3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AC3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AD3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AE3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AF3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AH3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AI3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AJ3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AK3" t="s">
         <v>138</v>
       </c>
       <c r="AL3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AM3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AN3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AO3" t="s">
         <v>138</v>
@@ -3019,8 +3040,17 @@
       <c r="AS3" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="4" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="AU3">
+        <f>TRIM('Client and family'!$D$10&amp;" "&amp;'Client and family'!$D$11)</f>
+      </c>
+      <c r="AW3" t="s">
+        <v>493</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>136</v>
       </c>
@@ -3031,43 +3061,43 @@
         <f>IF('Assets and debts'!$B$14="",""," "&amp;'Assets and debts'!$B$14)</f>
       </c>
       <c r="D4" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="H4" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="I4" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="J4" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="K4" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L4" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="M4" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="N4" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="O4" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="P4" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="Q4" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="R4" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="S4" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="U4" t="s">
         <v>203</v>
@@ -3076,40 +3106,43 @@
         <v>131</v>
       </c>
       <c r="W4" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="Y4" t="s">
-        <v>506</v>
+        <v>131</v>
       </c>
       <c r="Z4" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AA4" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AB4" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AC4" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AF4" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG4" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AH4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AJ4" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AN4" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="5" spans="2:49" x14ac:dyDescent="0.25">
       <c r="B5">
         <f>IF('Client and family'!$B$42="","",'Client and family'!$B$42)</f>
       </c>
@@ -3117,49 +3150,49 @@
         <f>IF('Assets and debts'!$B$15="",""," "&amp;'Assets and debts'!$B$15)</f>
       </c>
       <c r="D5" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="H5" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="I5" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="J5" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="K5" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L5" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="M5" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="N5" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="O5" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="Q5" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="S5" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="U5" t="s">
         <v>139</v>
       </c>
       <c r="W5" t="s">
-        <v>526</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AC5" t="s">
-        <v>528</v>
+        <v>530</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>531</v>
       </c>
     </row>
     <row r="6" spans="2:23" x14ac:dyDescent="0.25">
@@ -3170,37 +3203,37 @@
         <f>IF('Assets and debts'!$B$16="",""," "&amp;'Assets and debts'!$B$16)</f>
       </c>
       <c r="D6" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="H6" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="I6" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="J6" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K6" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L6" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="M6" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="N6" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="O6" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="W6" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="7" spans="2:26" x14ac:dyDescent="0.25">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="7" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B7">
         <f>IF('Client and family'!$B$44="","",'Client and family'!$B$44)</f>
       </c>
@@ -3208,37 +3241,37 @@
         <f>IF('Assets and debts'!$B$17="",""," "&amp;'Assets and debts'!$B$17)</f>
       </c>
       <c r="D7" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="H7" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="I7" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="K7" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L7" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="M7" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="N7" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="O7" t="s">
-        <v>501</v>
-      </c>
-      <c r="Y7" t="s">
-        <v>543</v>
-      </c>
-      <c r="Z7" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="8" spans="2:26" x14ac:dyDescent="0.25">
+        <v>504</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>546</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="8" spans="2:50" x14ac:dyDescent="0.25">
       <c r="B8">
         <f>IF('Client and family'!$B$45="","",'Client and family'!$B$45)</f>
       </c>
@@ -3246,28 +3279,28 @@
         <f>IF('Assets and debts'!$B$18="",""," "&amp;'Assets and debts'!$B$18)</f>
       </c>
       <c r="D8" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="H8" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="K8" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L8" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="M8" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="N8" t="s">
-        <v>549</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>550</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>551</v>
+        <v>552</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>553</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>554</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
@@ -3278,22 +3311,22 @@
         <f>IF('Assets and debts'!$B$19="",""," "&amp;'Assets and debts'!$B$19)</f>
       </c>
       <c r="D9" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="H9" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="K9" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="L9" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="M9" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="N9" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
@@ -3304,13 +3337,13 @@
         <f>IF('Assets and debts'!$B$26="",""," "&amp;'Assets and debts'!$B$26)</f>
       </c>
       <c r="L10" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M10" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="N10" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="3:3" x14ac:dyDescent="0.25">
@@ -3769,7 +3802,7 @@
     </row>
     <row r="34" ht="44" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="39">
-        <f>IF('Lists'!$X$3="","You own R ","Together you own R ")&amp;TEXT(F15,"#,##0")&amp;" and owe R "&amp;TEXT(F22,"#,##0")&amp;", a net worth of R "&amp;TEXT(F24,"#,##0")&amp;"."&amp;IF(F31&gt;0," "&amp;F31&amp;IF(F31=1," figure is an estimate."," figures are estimates."),"")&amp;IF(F32&gt;0," "&amp;F32&amp;IF(F32=1," asset has"," assets have")&amp;" no base cost yet, which we need for capital gains tax.","")</f>
+        <f>IF('Lists'!$AU$3="","You own R ","Together you own R ")&amp;TEXT(F15,"#,##0")&amp;" and owe R "&amp;TEXT(F22,"#,##0")&amp;", a net worth of R "&amp;TEXT(F24,"#,##0")&amp;"."&amp;IF(F31&gt;0," "&amp;F31&amp;IF(F31=1," figure is an estimate."," figures are estimates."),"")&amp;IF(F32&gt;0," "&amp;F32&amp;IF(F32=1," asset has"," assets have")&amp;" no base cost yet, which we need for capital gains tax.","")</f>
       </c>
       <c r="C34" s="39"/>
       <c r="D34" s="39"/>
@@ -3828,7 +3861,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
-        <f>"Fact find for "&amp;IF('Lists'!$X$2="","a new client",'Lists'!$X$2)&amp;IF('Lists'!$X$3="",""," and "&amp;'Lists'!$X$3)</f>
+        <f>"Fact find for "&amp;IF('Lists'!$AU$2="","a new client",'Lists'!$AU$2)&amp;IF('Lists'!$AU$3="",""," and "&amp;'Lists'!$AU$3)</f>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
@@ -4302,10 +4335,10 @@
         <v>32</v>
       </c>
       <c r="C14" s="17">
-        <f>IF(C13="","",IF(OR(LEN(C13)&lt;&gt;13,ISERROR(VALUE(C13))),"✗ An SA ID number has 13 digits",IF(AND(MOD(SUMPRODUCT(VALUE(MID(C13,{1,3,5,7,9,11,13},1)))+SUMPRODUCT(INT(VALUE(MID(C13,{2,4,6,8,10,12},1))*2/10)+MOD(VALUE(MID(C13,{2,4,6,8,10,12},1))*2,10)),10)=0,VALUE(MID(C13,3,2))&gt;=1,VALUE(MID(C13,3,2))&lt;=12,VALUE(MID(C13,5,2))&gt;=1,VALUE(MID(C13,5,2))&lt;=DAY(DATE(IF(VALUE(LEFT(C13,2))&lt;30,2000,1900)+VALUE(LEFT(C13,2)),VALUE(MID(C13,3,2))+1,0))),"✓ Valid ID number","✗ Not a valid ID number: please check every digit"))</f>
+        <f>IF(C13="","",IF(OR(LEN(C13)&lt;&gt;13,ISERROR(VALUE(C13))),"✗ An SA ID number has 13 digits",IF(IFERROR(AND(MOD(MID(C13,1,1)+MID(C13,3,1)+MID(C13,5,1)+MID(C13,7,1)+MID(C13,9,1)+MID(C13,11,1)+MID(C13,13,1)+MID("0246813579",MID(C13,2,1)+1,1)+MID("0246813579",MID(C13,4,1)+1,1)+MID("0246813579",MID(C13,6,1)+1,1)+MID("0246813579",MID(C13,8,1)+1,1)+MID("0246813579",MID(C13,10,1)+1,1)+MID("0246813579",MID(C13,12,1)+1,1),10)=0,VALUE(MID(C13,3,2))&gt;=1,VALUE(MID(C13,3,2))&lt;=12,VALUE(MID(C13,5,2))&gt;=1,VALUE(MID(C13,5,2))&lt;=DAY(DATE(IF(VALUE(LEFT(C13,2))&lt;30,2000,1900)+VALUE(LEFT(C13,2)),VALUE(MID(C13,3,2))+1,0))),FALSE),"✓ Valid ID number","✗ Not a valid ID number: please check every digit")))</f>
       </c>
       <c r="D14" s="17">
-        <f>IF(D13="","",IF(OR(LEN(D13)&lt;&gt;13,ISERROR(VALUE(D13))),"✗ An SA ID number has 13 digits",IF(AND(MOD(SUMPRODUCT(VALUE(MID(D13,{1,3,5,7,9,11,13},1)))+SUMPRODUCT(INT(VALUE(MID(D13,{2,4,6,8,10,12},1))*2/10)+MOD(VALUE(MID(D13,{2,4,6,8,10,12},1))*2,10)),10)=0,VALUE(MID(D13,3,2))&gt;=1,VALUE(MID(D13,3,2))&lt;=12,VALUE(MID(D13,5,2))&gt;=1,VALUE(MID(D13,5,2))&lt;=DAY(DATE(IF(VALUE(LEFT(D13,2))&lt;30,2000,1900)+VALUE(LEFT(D13,2)),VALUE(MID(D13,3,2))+1,0))),"✓ Valid ID number","✗ Not a valid ID number: please check every digit"))</f>
+        <f>IF(D13="","",IF(OR(LEN(D13)&lt;&gt;13,ISERROR(VALUE(D13))),"✗ An SA ID number has 13 digits",IF(IFERROR(AND(MOD(MID(D13,1,1)+MID(D13,3,1)+MID(D13,5,1)+MID(D13,7,1)+MID(D13,9,1)+MID(D13,11,1)+MID(D13,13,1)+MID("0246813579",MID(D13,2,1)+1,1)+MID("0246813579",MID(D13,4,1)+1,1)+MID("0246813579",MID(D13,6,1)+1,1)+MID("0246813579",MID(D13,8,1)+1,1)+MID("0246813579",MID(D13,10,1)+1,1)+MID("0246813579",MID(D13,12,1)+1,1),10)=0,VALUE(MID(D13,3,2))&gt;=1,VALUE(MID(D13,3,2))&lt;=12,VALUE(MID(D13,5,2))&gt;=1,VALUE(MID(D13,5,2))&lt;=DAY(DATE(IF(VALUE(LEFT(D13,2))&lt;30,2000,1900)+VALUE(LEFT(D13,2)),VALUE(MID(D13,3,2))+1,0))),FALSE),"✓ Valid ID number","✗ Not a valid ID number: please check every digit")))</f>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.25">
@@ -8590,7 +8623,7 @@
         <v>60</v>
       </c>
       <c r="C9" s="30">
-        <f>'Lists'!$X$2</f>
+        <f>'Lists'!$AU$2</f>
       </c>
       <c r="D9" s="30"/>
       <c r="E9" s="30"/>
@@ -8644,7 +8677,7 @@
         <v>241</v>
       </c>
       <c r="C16" s="30">
-        <f>'Lists'!$X$3</f>
+        <f>'Lists'!$AU$3</f>
       </c>
       <c r="D16" s="30"/>
       <c r="E16" s="30"/>

--- a/Duwalcoe_Fact_Find_Template.xlsx
+++ b/Duwalcoe_Fact_Find_Template.xlsx
@@ -67,13 +67,13 @@
     <definedName name="FF_K_expense">'Income and expenses'!$B$25:$Z$25</definedName>
     <definedName name="FF_T_expense">'Income and expenses'!$B$28:$Z$42</definedName>
     <definedName name="FF_K_property">'Assets and debts'!$B$9:$Z$9</definedName>
-    <definedName name="FF_T_property">'Assets and debts'!$B$12:$Z$19</definedName>
-    <definedName name="FF_K_vehicle">'Assets and debts'!$B$23:$Z$23</definedName>
-    <definedName name="FF_T_vehicle">'Assets and debts'!$B$26:$Z$31</definedName>
-    <definedName name="FF_K_other">'Assets and debts'!$B$35:$Z$35</definedName>
-    <definedName name="FF_T_other">'Assets and debts'!$B$38:$Z$52</definedName>
-    <definedName name="FF_K_liability">'Assets and debts'!$B$56:$Z$56</definedName>
-    <definedName name="FF_T_liability">'Assets and debts'!$B$59:$Z$70</definedName>
+    <definedName name="FF_T_property">'Assets and debts'!$B$12:$Z$23</definedName>
+    <definedName name="FF_K_vehicle">'Assets and debts'!$B$27:$Z$27</definedName>
+    <definedName name="FF_T_vehicle">'Assets and debts'!$B$30:$Z$35</definedName>
+    <definedName name="FF_K_other">'Assets and debts'!$B$39:$Z$39</definedName>
+    <definedName name="FF_T_other">'Assets and debts'!$B$42:$Z$71</definedName>
+    <definedName name="FF_K_liability">'Assets and debts'!$B$75:$Z$75</definedName>
+    <definedName name="FF_T_liability">'Assets and debts'!$B$78:$Z$89</definedName>
     <definedName name="FF_B1__id">'Companies and trusts'!$Z$7</definedName>
     <definedName name="FF_B1_desc">'Companies and trusts'!$C$8</definedName>
     <definedName name="FF_B1_entityType">'Companies and trusts'!$C$9</definedName>
@@ -308,7 +308,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Client and family'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Income and expenses'!$A1:$H49</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Income and expenses'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Assets and debts'!$A1:$Q72</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Assets and debts'!$A1:$Q91</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Assets and debts'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Companies and trusts'!$A1:$G188</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Companies and trusts'!$1:$2</definedName>
@@ -1808,7 +1808,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3</t>
+    <t>1.4</t>
   </si>
   <si>
     <t>Ms.</t>
@@ -1988,7 +1988,7 @@
     <t>Breaks</t>
   </si>
   <si>
-    <t>[["Assets and debts",53],["Companies and trusts",51],["Companies and trusts",96],["Companies and trusts",141],["Will",63]]</t>
+    <t>[["Assets and debts",36],["Assets and debts",72],["Companies and trusts",51],["Companies and trusts",96],["Companies and trusts",141],["Will",63]]</t>
   </si>
   <si>
     <t>Adv.</t>
@@ -2615,7 +2615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX34"/>
+  <dimension ref="A1:AX53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -3334,7 +3334,7 @@
         <f>IF('Client and family'!$B$47="","",'Client and family'!$B$47)</f>
       </c>
       <c r="C10">
-        <f>IF('Assets and debts'!$B$26="",""," "&amp;'Assets and debts'!$B$26)</f>
+        <f>IF('Assets and debts'!$B$20="",""," "&amp;'Assets and debts'!$B$20)</f>
       </c>
       <c r="L10" t="s">
         <v>504</v>
@@ -3348,17 +3348,17 @@
     </row>
     <row r="11" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C11">
-        <f>IF('Assets and debts'!$B$27="",""," "&amp;'Assets and debts'!$B$27)</f>
+        <f>IF('Assets and debts'!$B$21="",""," "&amp;'Assets and debts'!$B$21)</f>
       </c>
     </row>
     <row r="12" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C12">
-        <f>IF('Assets and debts'!$B$28="",""," "&amp;'Assets and debts'!$B$28)</f>
+        <f>IF('Assets and debts'!$B$22="",""," "&amp;'Assets and debts'!$B$22)</f>
       </c>
     </row>
     <row r="13" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C13">
-        <f>IF('Assets and debts'!$B$29="",""," "&amp;'Assets and debts'!$B$29)</f>
+        <f>IF('Assets and debts'!$B$23="",""," "&amp;'Assets and debts'!$B$23)</f>
       </c>
     </row>
     <row r="14" spans="3:3" x14ac:dyDescent="0.25">
@@ -3373,22 +3373,22 @@
     </row>
     <row r="16" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C16">
-        <f>IF('Assets and debts'!$B$38="",""," "&amp;'Assets and debts'!$B$38)</f>
+        <f>IF('Assets and debts'!$B$32="",""," "&amp;'Assets and debts'!$B$32)</f>
       </c>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C17">
-        <f>IF('Assets and debts'!$B$39="",""," "&amp;'Assets and debts'!$B$39)</f>
+        <f>IF('Assets and debts'!$B$33="",""," "&amp;'Assets and debts'!$B$33)</f>
       </c>
     </row>
     <row r="18" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C18">
-        <f>IF('Assets and debts'!$B$40="",""," "&amp;'Assets and debts'!$B$40)</f>
+        <f>IF('Assets and debts'!$B$34="",""," "&amp;'Assets and debts'!$B$34)</f>
       </c>
     </row>
     <row r="19" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C19">
-        <f>IF('Assets and debts'!$B$41="",""," "&amp;'Assets and debts'!$B$41)</f>
+        <f>IF('Assets and debts'!$B$35="",""," "&amp;'Assets and debts'!$B$35)</f>
       </c>
     </row>
     <row r="20" spans="3:3" x14ac:dyDescent="0.25">
@@ -3448,21 +3448,116 @@
     </row>
     <row r="31" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C31">
-        <f>IF('Companies and trusts'!$C$8="",""," "&amp;'Companies and trusts'!$C$8)</f>
+        <f>IF('Assets and debts'!$B$53="",""," "&amp;'Assets and debts'!$B$53)</f>
       </c>
     </row>
     <row r="32" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C32">
-        <f>IF('Companies and trusts'!$C$54="",""," "&amp;'Companies and trusts'!$C$54)</f>
+        <f>IF('Assets and debts'!$B$54="",""," "&amp;'Assets and debts'!$B$54)</f>
       </c>
     </row>
     <row r="33" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C33">
-        <f>IF('Companies and trusts'!$C$99="",""," "&amp;'Companies and trusts'!$C$99)</f>
+        <f>IF('Assets and debts'!$B$55="",""," "&amp;'Assets and debts'!$B$55)</f>
       </c>
     </row>
     <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34">
+        <f>IF('Assets and debts'!$B$56="",""," "&amp;'Assets and debts'!$B$56)</f>
+      </c>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35">
+        <f>IF('Assets and debts'!$B$57="",""," "&amp;'Assets and debts'!$B$57)</f>
+      </c>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36">
+        <f>IF('Assets and debts'!$B$58="",""," "&amp;'Assets and debts'!$B$58)</f>
+      </c>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37">
+        <f>IF('Assets and debts'!$B$59="",""," "&amp;'Assets and debts'!$B$59)</f>
+      </c>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C38">
+        <f>IF('Assets and debts'!$B$60="",""," "&amp;'Assets and debts'!$B$60)</f>
+      </c>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C39">
+        <f>IF('Assets and debts'!$B$61="",""," "&amp;'Assets and debts'!$B$61)</f>
+      </c>
+    </row>
+    <row r="40" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <f>IF('Assets and debts'!$B$62="",""," "&amp;'Assets and debts'!$B$62)</f>
+      </c>
+    </row>
+    <row r="41" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <f>IF('Assets and debts'!$B$63="",""," "&amp;'Assets and debts'!$B$63)</f>
+      </c>
+    </row>
+    <row r="42" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <f>IF('Assets and debts'!$B$64="",""," "&amp;'Assets and debts'!$B$64)</f>
+      </c>
+    </row>
+    <row r="43" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C43">
+        <f>IF('Assets and debts'!$B$65="",""," "&amp;'Assets and debts'!$B$65)</f>
+      </c>
+    </row>
+    <row r="44" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C44">
+        <f>IF('Assets and debts'!$B$66="",""," "&amp;'Assets and debts'!$B$66)</f>
+      </c>
+    </row>
+    <row r="45" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C45">
+        <f>IF('Assets and debts'!$B$67="",""," "&amp;'Assets and debts'!$B$67)</f>
+      </c>
+    </row>
+    <row r="46" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C46">
+        <f>IF('Assets and debts'!$B$68="",""," "&amp;'Assets and debts'!$B$68)</f>
+      </c>
+    </row>
+    <row r="47" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C47">
+        <f>IF('Assets and debts'!$B$69="",""," "&amp;'Assets and debts'!$B$69)</f>
+      </c>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C48">
+        <f>IF('Assets and debts'!$B$70="",""," "&amp;'Assets and debts'!$B$70)</f>
+      </c>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C49">
+        <f>IF('Assets and debts'!$B$71="",""," "&amp;'Assets and debts'!$B$71)</f>
+      </c>
+    </row>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C50">
+        <f>IF('Companies and trusts'!$C$8="",""," "&amp;'Companies and trusts'!$C$8)</f>
+      </c>
+    </row>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C51">
+        <f>IF('Companies and trusts'!$C$54="",""," "&amp;'Companies and trusts'!$C$54)</f>
+      </c>
+    </row>
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C52">
+        <f>IF('Companies and trusts'!$C$99="",""," "&amp;'Companies and trusts'!$C$99)</f>
+      </c>
+    </row>
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C53">
         <f>IF('Companies and trusts'!$C$144="",""," "&amp;'Companies and trusts'!$C$144)</f>
       </c>
     </row>
@@ -3554,13 +3649,13 @@
         <v>375</v>
       </c>
       <c r="C10" s="19">
-        <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$2)</f>
+        <f>SUMIFS('Assets and debts'!$D$12:$D$23,'Assets and debts'!$C$12:$C$23,'Lists'!$A$2)</f>
       </c>
       <c r="D10" s="19">
-        <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$3)</f>
+        <f>SUMIFS('Assets and debts'!$D$12:$D$23,'Assets and debts'!$C$12:$C$23,'Lists'!$A$3)</f>
       </c>
       <c r="E10" s="19">
-        <f>SUMIFS('Assets and debts'!$D$12:$D$19,'Assets and debts'!$C$12:$C$19,"Joint")</f>
+        <f>SUMIFS('Assets and debts'!$D$12:$D$23,'Assets and debts'!$C$12:$C$23,"Joint")</f>
       </c>
       <c r="F10" s="19">
         <f>SUM(C10:E10)</f>
@@ -3588,13 +3683,13 @@
         <v>377</v>
       </c>
       <c r="C12" s="19">
-        <f>IF('Companies and trusts'!$C$22="Credit",N('Companies and trusts'!$C$23),0)+IF('Companies and trusts'!$C$68="Credit",N('Companies and trusts'!$C$69),0)+IF('Companies and trusts'!$C$113="Credit",N('Companies and trusts'!$C$114),0)+IF('Companies and trusts'!$C$158="Credit",N('Companies and trusts'!$C$159),0)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
+        <f>IF('Companies and trusts'!$C$22="Credit",N('Companies and trusts'!$C$23),0)+IF('Companies and trusts'!$C$68="Credit",N('Companies and trusts'!$C$69),0)+IF('Companies and trusts'!$C$113="Credit",N('Companies and trusts'!$C$114),0)+IF('Companies and trusts'!$C$158="Credit",N('Companies and trusts'!$C$159),0)+SUMIFS('Assets and debts'!$E$42:$E$71,'Assets and debts'!$C$42:$C$71,'Lists'!$A$2,'Assets and debts'!$D$42:$D$71,"Loan Account")</f>
       </c>
       <c r="D12" s="19">
-        <f>IF('Companies and trusts'!$D$22="Credit",N('Companies and trusts'!$D$23),0)+IF('Companies and trusts'!$D$68="Credit",N('Companies and trusts'!$D$69),0)+IF('Companies and trusts'!$D$113="Credit",N('Companies and trusts'!$D$114),0)+IF('Companies and trusts'!$D$158="Credit",N('Companies and trusts'!$D$159),0)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$3,'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
+        <f>IF('Companies and trusts'!$D$22="Credit",N('Companies and trusts'!$D$23),0)+IF('Companies and trusts'!$D$68="Credit",N('Companies and trusts'!$D$69),0)+IF('Companies and trusts'!$D$113="Credit",N('Companies and trusts'!$D$114),0)+IF('Companies and trusts'!$D$158="Credit",N('Companies and trusts'!$D$159),0)+SUMIFS('Assets and debts'!$E$42:$E$71,'Assets and debts'!$C$42:$C$71,'Lists'!$A$3,'Assets and debts'!$D$42:$D$71,"Loan Account")</f>
       </c>
       <c r="E12" s="19">
-        <f>SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,"Joint",'Assets and debts'!$D$38:$D$52,"Loan Account")</f>
+        <f>SUMIFS('Assets and debts'!$E$42:$E$71,'Assets and debts'!$C$42:$C$71,"Joint",'Assets and debts'!$D$42:$D$71,"Loan Account")</f>
       </c>
       <c r="F12" s="19">
         <f>SUM(C12:E12)</f>
@@ -3605,13 +3700,13 @@
         <v>378</v>
       </c>
       <c r="C13" s="19">
-        <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
+        <f>SUM(SUMIFS('Assets and debts'!$E$42:$E$71,'Assets and debts'!$C$42:$C$71,'Lists'!$A$2,'Assets and debts'!$D$42:$D$71,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
       </c>
       <c r="D13" s="19">
-        <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$3,'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
+        <f>SUM(SUMIFS('Assets and debts'!$E$42:$E$71,'Assets and debts'!$C$42:$C$71,'Lists'!$A$3,'Assets and debts'!$D$42:$D$71,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
       </c>
       <c r="E13" s="19">
-        <f>SUM(SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,"Joint",'Assets and debts'!$D$38:$D$52,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
+        <f>SUM(SUMIFS('Assets and debts'!$E$42:$E$71,'Assets and debts'!$C$42:$C$71,"Joint",'Assets and debts'!$D$42:$D$71,{"Cash / Savings","Fixed Deposit","Shares / Unit Trusts","Crypto"}))</f>
       </c>
       <c r="F13" s="19">
         <f>SUM(C13:E13)</f>
@@ -3622,13 +3717,13 @@
         <v>379</v>
       </c>
       <c r="C14" s="19">
-        <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$2)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$2,'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
+        <f>SUMIFS('Assets and debts'!$D$30:$D$35,'Assets and debts'!$C$30:$C$35,'Lists'!$A$2)+SUMIFS('Assets and debts'!$E$42:$E$71,'Assets and debts'!$C$42:$C$71,'Lists'!$A$2,'Assets and debts'!$D$42:$D$71,"&lt;&gt;Loan Account",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Crypto")</f>
       </c>
       <c r="D14" s="19">
-        <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$3)+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,'Lists'!$A$3,'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
+        <f>SUMIFS('Assets and debts'!$D$30:$D$35,'Assets and debts'!$C$30:$C$35,'Lists'!$A$3)+SUMIFS('Assets and debts'!$E$42:$E$71,'Assets and debts'!$C$42:$C$71,'Lists'!$A$3,'Assets and debts'!$D$42:$D$71,"&lt;&gt;Loan Account",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Crypto")</f>
       </c>
       <c r="E14" s="19">
-        <f>SUMIFS('Assets and debts'!$D$26:$D$31,'Assets and debts'!$C$26:$C$31,"Joint")+SUMIFS('Assets and debts'!$E$38:$E$52,'Assets and debts'!$C$38:$C$52,"Joint",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Loan Account",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$38:$D$52,"&lt;&gt;Crypto")</f>
+        <f>SUMIFS('Assets and debts'!$D$30:$D$35,'Assets and debts'!$C$30:$C$35,"Joint")+SUMIFS('Assets and debts'!$E$42:$E$71,'Assets and debts'!$C$42:$C$71,"Joint",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Loan Account",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Cash / Savings",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Fixed Deposit",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Shares / Unit Trusts",'Assets and debts'!$D$42:$D$71,"&lt;&gt;Crypto")</f>
       </c>
       <c r="F14" s="19">
         <f>SUM(C14:E14)</f>
@@ -3661,13 +3756,13 @@
         <v>382</v>
       </c>
       <c r="C18" s="19">
-        <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$2)</f>
+        <f>SUMIFS('Assets and debts'!$H$12:$H$23,'Assets and debts'!$C$12:$C$23,'Lists'!$A$2)</f>
       </c>
       <c r="D18" s="19">
-        <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,'Lists'!$A$3)</f>
+        <f>SUMIFS('Assets and debts'!$H$12:$H$23,'Assets and debts'!$C$12:$C$23,'Lists'!$A$3)</f>
       </c>
       <c r="E18" s="19">
-        <f>SUMIFS('Assets and debts'!$H$12:$H$19,'Assets and debts'!$C$12:$C$19,"Joint")</f>
+        <f>SUMIFS('Assets and debts'!$H$12:$H$23,'Assets and debts'!$C$12:$C$23,"Joint")</f>
       </c>
       <c r="F18" s="19">
         <f>SUM(C18:E18)</f>
@@ -3678,13 +3773,13 @@
         <v>383</v>
       </c>
       <c r="C19" s="19">
-        <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$2)</f>
+        <f>SUMIFS('Assets and debts'!$E$30:$E$35,'Assets and debts'!$C$30:$C$35,'Lists'!$A$2)</f>
       </c>
       <c r="D19" s="19">
-        <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,'Lists'!$A$3)</f>
+        <f>SUMIFS('Assets and debts'!$E$30:$E$35,'Assets and debts'!$C$30:$C$35,'Lists'!$A$3)</f>
       </c>
       <c r="E19" s="19">
-        <f>SUMIFS('Assets and debts'!$E$26:$E$31,'Assets and debts'!$C$26:$C$31,"Joint")</f>
+        <f>SUMIFS('Assets and debts'!$E$30:$E$35,'Assets and debts'!$C$30:$C$35,"Joint")</f>
       </c>
       <c r="F19" s="19">
         <f>SUM(C19:E19)</f>
@@ -3695,13 +3790,13 @@
         <v>384</v>
       </c>
       <c r="C20" s="19">
-        <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,'Lists'!$A$2)</f>
+        <f>SUMIFS('Assets and debts'!$E$78:$E$89,'Assets and debts'!$C$78:$C$89,'Lists'!$A$2)</f>
       </c>
       <c r="D20" s="19">
-        <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,'Lists'!$A$3)</f>
+        <f>SUMIFS('Assets and debts'!$E$78:$E$89,'Assets and debts'!$C$78:$C$89,'Lists'!$A$3)</f>
       </c>
       <c r="E20" s="19">
-        <f>SUMIFS('Assets and debts'!$E$59:$E$70,'Assets and debts'!$C$59:$C$70,"Joint")</f>
+        <f>SUMIFS('Assets and debts'!$E$78:$E$89,'Assets and debts'!$C$78:$C$89,"Joint")</f>
       </c>
       <c r="F20" s="19">
         <f>SUM(C20:E20)</f>
@@ -3789,7 +3884,7 @@
         <v>392</v>
       </c>
       <c r="F31" s="20">
-        <f>COUNTIF('Assets and debts'!$P$12:$P$19,"Estimate")+COUNTIF('Assets and debts'!$J$26:$J$31,"Estimate")+COUNTIF('Assets and debts'!$J$38:$J$52,"Estimate")+COUNTIF('Assets and debts'!$I$59:$I$70,"Estimate")+COUNTIF('Companies and trusts'!$C$14,"Estimate")+COUNTIF('Companies and trusts'!$C$60,"Estimate")+COUNTIF('Companies and trusts'!$C$105,"Estimate")+COUNTIF('Companies and trusts'!$C$150,"Estimate")+COUNTIF('Companies and trusts'!$F$34:$F$43,"Estimate")+COUNTIF('Companies and trusts'!$F$79:$F$88,"Estimate")+COUNTIF('Companies and trusts'!$F$124:$F$133,"Estimate")+COUNTIF('Companies and trusts'!$F$169:$F$178,"Estimate")</f>
+        <f>COUNTIF('Assets and debts'!$P$12:$P$23,"Estimate")+COUNTIF('Assets and debts'!$J$30:$J$35,"Estimate")+COUNTIF('Assets and debts'!$J$42:$J$71,"Estimate")+COUNTIF('Assets and debts'!$I$78:$I$89,"Estimate")+COUNTIF('Companies and trusts'!$C$14,"Estimate")+COUNTIF('Companies and trusts'!$C$60,"Estimate")+COUNTIF('Companies and trusts'!$C$105,"Estimate")+COUNTIF('Companies and trusts'!$C$150,"Estimate")+COUNTIF('Companies and trusts'!$F$34:$F$43,"Estimate")+COUNTIF('Companies and trusts'!$F$79:$F$88,"Estimate")+COUNTIF('Companies and trusts'!$F$124:$F$133,"Estimate")+COUNTIF('Companies and trusts'!$F$169:$F$178,"Estimate")</f>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
@@ -3797,7 +3892,7 @@
         <v>393</v>
       </c>
       <c r="F32" s="20">
-        <f>SUMPRODUCT(('Assets and debts'!$D$12:$D$19&gt;0)*('Assets and debts'!$F$12:$F$19=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Shares / Unit Trusts")*('Assets and debts'!$F$38:$F$52=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Business Interest")*('Assets and debts'!$F$38:$F$52=""))+SUMPRODUCT(('Assets and debts'!$E$38:$E$52&gt;0)*('Assets and debts'!$D$38:$D$52="Crypto")*('Assets and debts'!$F$38:$F$52=""))+IF(AND(N('Companies and trusts'!$C$21)&gt;0,'Companies and trusts'!$C$24=""),1,0)+IF(AND(N('Companies and trusts'!$D$21)&gt;0,'Companies and trusts'!$D$24=""),1,0)+IF(AND(N('Companies and trusts'!$C$67)&gt;0,'Companies and trusts'!$C$70=""),1,0)+IF(AND(N('Companies and trusts'!$D$67)&gt;0,'Companies and trusts'!$D$70=""),1,0)+IF(AND(N('Companies and trusts'!$C$112)&gt;0,'Companies and trusts'!$C$115=""),1,0)+IF(AND(N('Companies and trusts'!$D$112)&gt;0,'Companies and trusts'!$D$115=""),1,0)+IF(AND(N('Companies and trusts'!$C$157)&gt;0,'Companies and trusts'!$C$160=""),1,0)+IF(AND(N('Companies and trusts'!$D$157)&gt;0,'Companies and trusts'!$D$160=""),1,0)+SUMPRODUCT(('Companies and trusts'!$D$34:$D$43&gt;0)*('Companies and trusts'!$C$34:$C$43="Property")*('Companies and trusts'!$E$34:$E$43=""))+SUMPRODUCT(('Companies and trusts'!$D$79:$D$88&gt;0)*('Companies and trusts'!$C$79:$C$88="Property")*('Companies and trusts'!$E$79:$E$88=""))+SUMPRODUCT(('Companies and trusts'!$D$124:$D$133&gt;0)*('Companies and trusts'!$C$124:$C$133="Property")*('Companies and trusts'!$E$124:$E$133=""))+SUMPRODUCT(('Companies and trusts'!$D$169:$D$178&gt;0)*('Companies and trusts'!$C$169:$C$178="Property")*('Companies and trusts'!$E$169:$E$178=""))</f>
+        <f>SUMPRODUCT(('Assets and debts'!$D$12:$D$23&gt;0)*('Assets and debts'!$F$12:$F$23=""))+SUMPRODUCT(('Assets and debts'!$E$42:$E$71&gt;0)*('Assets and debts'!$D$42:$D$71="Shares / Unit Trusts")*('Assets and debts'!$F$42:$F$71=""))+SUMPRODUCT(('Assets and debts'!$E$42:$E$71&gt;0)*('Assets and debts'!$D$42:$D$71="Business Interest")*('Assets and debts'!$F$42:$F$71=""))+SUMPRODUCT(('Assets and debts'!$E$42:$E$71&gt;0)*('Assets and debts'!$D$42:$D$71="Crypto")*('Assets and debts'!$F$42:$F$71=""))+IF(AND(N('Companies and trusts'!$C$21)&gt;0,'Companies and trusts'!$C$24=""),1,0)+IF(AND(N('Companies and trusts'!$D$21)&gt;0,'Companies and trusts'!$D$24=""),1,0)+IF(AND(N('Companies and trusts'!$C$67)&gt;0,'Companies and trusts'!$C$70=""),1,0)+IF(AND(N('Companies and trusts'!$D$67)&gt;0,'Companies and trusts'!$D$70=""),1,0)+IF(AND(N('Companies and trusts'!$C$112)&gt;0,'Companies and trusts'!$C$115=""),1,0)+IF(AND(N('Companies and trusts'!$D$112)&gt;0,'Companies and trusts'!$D$115=""),1,0)+IF(AND(N('Companies and trusts'!$C$157)&gt;0,'Companies and trusts'!$C$160=""),1,0)+IF(AND(N('Companies and trusts'!$D$157)&gt;0,'Companies and trusts'!$D$160=""),1,0)+SUMPRODUCT(('Companies and trusts'!$D$34:$D$43&gt;0)*('Companies and trusts'!$C$34:$C$43="Property")*('Companies and trusts'!$E$34:$E$43=""))+SUMPRODUCT(('Companies and trusts'!$D$79:$D$88&gt;0)*('Companies and trusts'!$C$79:$C$88="Property")*('Companies and trusts'!$E$79:$E$88=""))+SUMPRODUCT(('Companies and trusts'!$D$124:$D$133&gt;0)*('Companies and trusts'!$C$124:$C$133="Property")*('Companies and trusts'!$E$124:$E$133=""))+SUMPRODUCT(('Companies and trusts'!$D$169:$D$178&gt;0)*('Companies and trusts'!$C$169:$C$178="Property")*('Companies and trusts'!$E$169:$E$178=""))</f>
       </c>
     </row>
     <row r="34" ht="44" customHeight="1" spans="2:6" x14ac:dyDescent="0.25">
@@ -5198,7 +5293,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z70"/>
+  <dimension ref="A1:Z89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -5610,192 +5705,216 @@
       <c r="P19" s="14"/>
       <c r="Q19" s="11"/>
     </row>
-    <row r="21" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B21" s="4" t="s">
+    <row r="20" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B20" s="11"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="11"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="11"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B21" s="11"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="11"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="11"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B22" s="11"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="11"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="11"/>
+    </row>
+    <row r="23" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B23" s="11"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="11"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="11"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
-      <c r="K21" s="5"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="5"/>
-      <c r="N21" s="5"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
-      <c r="Q21" s="5"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B22" s="12" t="s">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+    </row>
+    <row r="26" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B26" s="12" t="s">
         <v>142</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="12"/>
-      <c r="N22" s="12"/>
-      <c r="O22" s="12"/>
-      <c r="P22" s="12"/>
-      <c r="Q22" s="12"/>
-    </row>
-    <row r="23" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+    </row>
+    <row r="27" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
         <v>71</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C27" t="s">
         <v>72</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D27" t="s">
         <v>107</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E27" t="s">
         <v>143</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F27" t="s">
         <v>144</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G27" t="s">
         <v>115</v>
       </c>
-      <c r="H23" t="s">
+      <c r="H27" t="s">
         <v>116</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I27" t="s">
         <v>117</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J27" t="s">
         <v>119</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K27" t="s">
         <v>77</v>
       </c>
-      <c r="Z23" t="s">
+      <c r="Z27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="13" t="s">
+    <row r="28" ht="30" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D28" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E28" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="F24" s="13" t="s">
+      <c r="F28" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G28" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="H24" s="13" t="s">
+      <c r="H28" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I28" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="J24" s="13" t="s">
+      <c r="J28" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="K28" s="13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="21" t="s">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="C25" s="21">
+      <c r="C29" s="21">
         <f>'Lists'!$A$2</f>
       </c>
-      <c r="D25" s="22">
+      <c r="D29" s="22">
         <v>520000</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E29" s="22">
         <v>180000</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F29" s="22">
         <v>9800</v>
       </c>
-      <c r="G25" s="21" t="s">
+      <c r="G29" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="H25" s="21" t="s">
+      <c r="H29" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="I25" s="21" t="s">
+      <c r="I29" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="J25" s="21" t="s">
+      <c r="J29" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="K25" s="21" t="s">
+      <c r="K29" s="21" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="11"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="11"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="11"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="11"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="11"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="11"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="11"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="23"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="11"/>
     </row>
     <row r="30" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="11"/>
@@ -5821,192 +5940,192 @@
       <c r="J31" s="14"/>
       <c r="K31" s="11"/>
     </row>
-    <row r="33" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B33" s="4" t="s">
+    <row r="32" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="11"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="11"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="11"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="11"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="11"/>
+    </row>
+    <row r="35" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="11"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="23"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="11"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5"/>
-      <c r="J33" s="5"/>
-      <c r="K33" s="5"/>
-      <c r="L33" s="5"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="5"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-    </row>
-    <row r="34" ht="26" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B34" s="12" t="s">
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+    </row>
+    <row r="38" ht="26" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B38" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="12"/>
-      <c r="J34" s="12"/>
-      <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
-      <c r="M34" s="12"/>
-      <c r="N34" s="12"/>
-      <c r="O34" s="12"/>
-      <c r="P34" s="12"/>
-      <c r="Q34" s="12"/>
-    </row>
-    <row r="35" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="12"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12"/>
+      <c r="P38" s="12"/>
+      <c r="Q38" s="12"/>
+    </row>
+    <row r="39" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>71</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C39" t="s">
         <v>72</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D39" t="s">
         <v>152</v>
       </c>
-      <c r="E35" t="s">
+      <c r="E39" t="s">
         <v>107</v>
       </c>
-      <c r="F35" t="s">
+      <c r="F39" t="s">
         <v>109</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G39" t="s">
         <v>110</v>
       </c>
-      <c r="H35" t="s">
+      <c r="H39" t="s">
         <v>115</v>
       </c>
-      <c r="I35" t="s">
+      <c r="I39" t="s">
         <v>116</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J39" t="s">
         <v>119</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K39" t="s">
         <v>77</v>
       </c>
-      <c r="Z35" t="s">
+      <c r="Z39" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="13" t="s">
+    <row r="40" ht="30" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C40" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D40" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E40" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F40" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G40" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="H36" s="13" t="s">
+      <c r="H40" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="I36" s="13" t="s">
+      <c r="I40" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J40" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="K36" s="13" t="s">
+      <c r="K40" s="13" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="21" t="s">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="C37" s="21">
+      <c r="C41" s="21">
         <f>'Lists'!$A$2</f>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D41" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E41" s="22">
         <v>85000</v>
       </c>
-      <c r="F37" s="22" t="s">
+      <c r="F41" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="G37" s="26" t="s">
+      <c r="G41" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="H37" s="21" t="s">
+      <c r="H41" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="I37" s="21" t="s">
+      <c r="I41" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="J37" s="21" t="s">
+      <c r="J41" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="K37" s="21" t="s">
+      <c r="K41" s="21" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="11"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="11"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="11"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="23"/>
-      <c r="F39" s="23"/>
-      <c r="G39" s="10"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="11"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B40" s="11"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="23"/>
-      <c r="F40" s="23"/>
-      <c r="G40" s="10"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="11"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="11"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="23"/>
-      <c r="F41" s="23"/>
-      <c r="G41" s="10"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="11"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="11"/>
     </row>
     <row r="42" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="11"/>
@@ -6140,267 +6259,495 @@
       <c r="J52" s="14"/>
       <c r="K52" s="11"/>
     </row>
-    <row r="54" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="5"/>
-      <c r="L54" s="5"/>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5"/>
-      <c r="O54" s="5"/>
-      <c r="P54" s="5"/>
-      <c r="Q54" s="5"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
-      <c r="B55" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="12"/>
-      <c r="J55" s="12"/>
-      <c r="K55" s="12"/>
-      <c r="L55" s="12"/>
-      <c r="M55" s="12"/>
-      <c r="N55" s="12"/>
-      <c r="O55" s="12"/>
-      <c r="P55" s="12"/>
-      <c r="Q55" s="12"/>
-    </row>
-    <row r="56" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B56" t="s">
-        <v>71</v>
-      </c>
-      <c r="C56" t="s">
-        <v>72</v>
-      </c>
-      <c r="D56" t="s">
-        <v>161</v>
-      </c>
-      <c r="E56" t="s">
-        <v>162</v>
-      </c>
-      <c r="F56" t="s">
-        <v>163</v>
-      </c>
-      <c r="G56" t="s">
-        <v>164</v>
-      </c>
-      <c r="H56" t="s">
-        <v>165</v>
-      </c>
-      <c r="I56" t="s">
-        <v>119</v>
-      </c>
-      <c r="J56" t="s">
-        <v>77</v>
-      </c>
-      <c r="Z56" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" ht="30" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B57" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="D57" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="G57" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="H57" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="I57" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="J57" s="13" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B58" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="C58" s="21">
-        <f>'Lists'!$A$2</f>
-      </c>
-      <c r="D58" s="21" t="s">
-        <v>173</v>
-      </c>
-      <c r="E58" s="22">
-        <v>25000</v>
-      </c>
-      <c r="F58" s="21">
-        <v>19.5</v>
-      </c>
-      <c r="G58" s="22">
-        <v>1500</v>
-      </c>
-      <c r="H58" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="I58" s="21" t="s">
-        <v>158</v>
-      </c>
-      <c r="J58" s="21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="53" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B53" s="11"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="14"/>
+      <c r="E53" s="23"/>
+      <c r="F53" s="23"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="14"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="11"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B54" s="11"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="14"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="11"/>
+    </row>
+    <row r="55" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B55" s="11"/>
+      <c r="C55" s="14"/>
+      <c r="D55" s="14"/>
+      <c r="E55" s="23"/>
+      <c r="F55" s="23"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="14"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="11"/>
+    </row>
+    <row r="56" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B56" s="11"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="10"/>
+      <c r="H56" s="14"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="11"/>
+    </row>
+    <row r="57" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B57" s="11"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14"/>
+      <c r="E57" s="23"/>
+      <c r="F57" s="23"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="11"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B58" s="11"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="23"/>
+      <c r="F58" s="23"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="11"/>
+    </row>
+    <row r="59" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="11"/>
       <c r="C59" s="14"/>
       <c r="D59" s="14"/>
       <c r="E59" s="23"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="23"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="10"/>
       <c r="H59" s="14"/>
-      <c r="I59" s="14"/>
-      <c r="J59" s="11"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I59" s="11"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="11"/>
+    </row>
+    <row r="60" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="11"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>
       <c r="E60" s="23"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="23"/>
+      <c r="F60" s="23"/>
+      <c r="G60" s="10"/>
       <c r="H60" s="14"/>
-      <c r="I60" s="14"/>
-      <c r="J60" s="11"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I60" s="11"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="11"/>
+    </row>
+    <row r="61" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="11"/>
       <c r="C61" s="14"/>
       <c r="D61" s="14"/>
       <c r="E61" s="23"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="23"/>
+      <c r="F61" s="23"/>
+      <c r="G61" s="10"/>
       <c r="H61" s="14"/>
-      <c r="I61" s="14"/>
-      <c r="J61" s="11"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I61" s="11"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="11"/>
+    </row>
+    <row r="62" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B62" s="11"/>
       <c r="C62" s="14"/>
       <c r="D62" s="14"/>
       <c r="E62" s="23"/>
-      <c r="F62" s="27"/>
-      <c r="G62" s="23"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="10"/>
       <c r="H62" s="14"/>
-      <c r="I62" s="14"/>
-      <c r="J62" s="11"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I62" s="11"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="11"/>
+    </row>
+    <row r="63" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B63" s="11"/>
       <c r="C63" s="14"/>
       <c r="D63" s="14"/>
       <c r="E63" s="23"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="23"/>
+      <c r="F63" s="23"/>
+      <c r="G63" s="10"/>
       <c r="H63" s="14"/>
-      <c r="I63" s="14"/>
-      <c r="J63" s="11"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I63" s="11"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="11"/>
+    </row>
+    <row r="64" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B64" s="11"/>
       <c r="C64" s="14"/>
       <c r="D64" s="14"/>
       <c r="E64" s="23"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="23"/>
+      <c r="F64" s="23"/>
+      <c r="G64" s="10"/>
       <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="11"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I64" s="11"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="11"/>
+    </row>
+    <row r="65" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B65" s="11"/>
       <c r="C65" s="14"/>
       <c r="D65" s="14"/>
       <c r="E65" s="23"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="23"/>
+      <c r="F65" s="23"/>
+      <c r="G65" s="10"/>
       <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="11"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I65" s="11"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="11"/>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B66" s="11"/>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
       <c r="E66" s="23"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="23"/>
+      <c r="F66" s="23"/>
+      <c r="G66" s="10"/>
       <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="11"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I66" s="11"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="11"/>
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B67" s="11"/>
       <c r="C67" s="14"/>
       <c r="D67" s="14"/>
       <c r="E67" s="23"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="23"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="10"/>
       <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="11"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I67" s="11"/>
+      <c r="J67" s="14"/>
+      <c r="K67" s="11"/>
+    </row>
+    <row r="68" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B68" s="11"/>
       <c r="C68" s="14"/>
       <c r="D68" s="14"/>
       <c r="E68" s="23"/>
-      <c r="F68" s="27"/>
-      <c r="G68" s="23"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="10"/>
       <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="11"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I68" s="11"/>
+      <c r="J68" s="14"/>
+      <c r="K68" s="11"/>
+    </row>
+    <row r="69" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B69" s="11"/>
       <c r="C69" s="14"/>
       <c r="D69" s="14"/>
       <c r="E69" s="23"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="23"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="10"/>
       <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="11"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="I69" s="11"/>
+      <c r="J69" s="14"/>
+      <c r="K69" s="11"/>
+    </row>
+    <row r="70" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B70" s="11"/>
       <c r="C70" s="14"/>
       <c r="D70" s="14"/>
       <c r="E70" s="23"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="23"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="10"/>
       <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="14"/>
+      <c r="K70" s="11"/>
+    </row>
+    <row r="71" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B71" s="11"/>
+      <c r="C71" s="14"/>
+      <c r="D71" s="14"/>
+      <c r="E71" s="23"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="10"/>
+      <c r="H71" s="14"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="14"/>
+      <c r="K71" s="11"/>
+    </row>
+    <row r="73" ht="18" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B73" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="5"/>
+    </row>
+    <row r="74" ht="15" customHeight="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="B74" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="12"/>
+      <c r="H74" s="12"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
+      <c r="M74" s="12"/>
+      <c r="N74" s="12"/>
+      <c r="O74" s="12"/>
+      <c r="P74" s="12"/>
+      <c r="Q74" s="12"/>
+    </row>
+    <row r="75" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
+      <c r="B75" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" t="s">
+        <v>72</v>
+      </c>
+      <c r="D75" t="s">
+        <v>161</v>
+      </c>
+      <c r="E75" t="s">
+        <v>162</v>
+      </c>
+      <c r="F75" t="s">
+        <v>163</v>
+      </c>
+      <c r="G75" t="s">
+        <v>164</v>
+      </c>
+      <c r="H75" t="s">
+        <v>165</v>
+      </c>
+      <c r="I75" t="s">
+        <v>119</v>
+      </c>
+      <c r="J75" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" ht="30" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B76" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C76" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E76" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="F76" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="G76" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="I76" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="J76" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B77" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="C77" s="21">
+        <f>'Lists'!$A$2</f>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" s="22">
+        <v>25000</v>
+      </c>
+      <c r="F77" s="21">
+        <v>19.5</v>
+      </c>
+      <c r="G77" s="22">
+        <v>1500</v>
+      </c>
+      <c r="H77" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="I77" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="J77" s="21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B78" s="11"/>
+      <c r="C78" s="14"/>
+      <c r="D78" s="14"/>
+      <c r="E78" s="23"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="23"/>
+      <c r="H78" s="14"/>
+      <c r="I78" s="14"/>
+      <c r="J78" s="11"/>
+    </row>
+    <row r="79" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B79" s="11"/>
+      <c r="C79" s="14"/>
+      <c r="D79" s="14"/>
+      <c r="E79" s="23"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="23"/>
+      <c r="H79" s="14"/>
+      <c r="I79" s="14"/>
+      <c r="J79" s="11"/>
+    </row>
+    <row r="80" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B80" s="11"/>
+      <c r="C80" s="14"/>
+      <c r="D80" s="14"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="23"/>
+      <c r="H80" s="14"/>
+      <c r="I80" s="14"/>
+      <c r="J80" s="11"/>
+    </row>
+    <row r="81" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B81" s="11"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="23"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="23"/>
+      <c r="H81" s="14"/>
+      <c r="I81" s="14"/>
+      <c r="J81" s="11"/>
+    </row>
+    <row r="82" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B82" s="11"/>
+      <c r="C82" s="14"/>
+      <c r="D82" s="14"/>
+      <c r="E82" s="23"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="23"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="11"/>
+    </row>
+    <row r="83" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B83" s="11"/>
+      <c r="C83" s="14"/>
+      <c r="D83" s="14"/>
+      <c r="E83" s="23"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="23"/>
+      <c r="H83" s="14"/>
+      <c r="I83" s="14"/>
+      <c r="J83" s="11"/>
+    </row>
+    <row r="84" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B84" s="11"/>
+      <c r="C84" s="14"/>
+      <c r="D84" s="14"/>
+      <c r="E84" s="23"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="23"/>
+      <c r="H84" s="14"/>
+      <c r="I84" s="14"/>
+      <c r="J84" s="11"/>
+    </row>
+    <row r="85" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B85" s="11"/>
+      <c r="C85" s="14"/>
+      <c r="D85" s="14"/>
+      <c r="E85" s="23"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="23"/>
+      <c r="H85" s="14"/>
+      <c r="I85" s="14"/>
+      <c r="J85" s="11"/>
+    </row>
+    <row r="86" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B86" s="11"/>
+      <c r="C86" s="14"/>
+      <c r="D86" s="14"/>
+      <c r="E86" s="23"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="23"/>
+      <c r="H86" s="14"/>
+      <c r="I86" s="14"/>
+      <c r="J86" s="11"/>
+    </row>
+    <row r="87" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B87" s="11"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="23"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="23"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="11"/>
+    </row>
+    <row r="88" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B88" s="11"/>
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="27"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="11"/>
+    </row>
+    <row r="89" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B89" s="11"/>
+      <c r="C89" s="14"/>
+      <c r="D89" s="14"/>
+      <c r="E89" s="23"/>
+      <c r="F89" s="27"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="14"/>
+      <c r="I89" s="14"/>
+      <c r="J89" s="11"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
@@ -6409,97 +6756,97 @@
     <mergeCell ref="B2:Q2"/>
     <mergeCell ref="B5:Q5"/>
     <mergeCell ref="B8:Q8"/>
-    <mergeCell ref="B22:Q22"/>
-    <mergeCell ref="B34:Q34"/>
-    <mergeCell ref="B55:Q55"/>
+    <mergeCell ref="B26:Q26"/>
+    <mergeCell ref="B38:Q38"/>
+    <mergeCell ref="B74:Q74"/>
   </mergeCells>
   <dataValidations count="28">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose a name" error="Please choose a name from the list (or Joint). The names come from the Client and family sheet." sqref="C12:C19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose a name" error="Please choose a name from the list (or Joint). The names come from the Client and family sheet." sqref="C12:C23">
       <formula1>'Lists'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose a name" error="Please choose a name from the list (or Joint). The names come from the Client and family sheet." sqref="C26:C31">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose a name" error="Please choose a name from the list (or Joint). The names come from the Client and family sheet." sqref="C30:C35">
       <formula1>'Lists'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose a name" error="Please choose a name from the list (or Joint). The names come from the Client and family sheet." sqref="C38:C52">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose a name" error="Please choose a name from the list (or Joint). The names come from the Client and family sheet." sqref="C42:C71">
       <formula1>'Lists'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose a name" error="Please choose a name from the list (or Joint). The names come from the Client and family sheet." sqref="C59:C70">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose a name" error="Please choose a name from the list (or Joint). The names come from the Client and family sheet." sqref="C78:C89">
       <formula1>'Lists'!$A$2:$A$4</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="D12:D19">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="D12:D23">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="D26:F31">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="D30:F35">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D38:D52">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D42:D71">
       <formula1>'Lists'!$N$2:$N$10</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D59:D70">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D78:D89">
       <formula1>'Lists'!$M$2:$M$10</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="E12:E19">
+    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="E12:E23">
       <formula1>7306</formula1>
       <formula2>73415</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="E38:F52">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="E42:F71">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="E59:E70">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="E78:E89">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="F12:F19">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="F12:F23">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Number" error="Please type a number." sqref="F59:F70">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Number" error="Please type a number." sqref="F78:F89">
       <formula1>0</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="G12:G19">
+    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="G12:G23">
       <formula1>7306</formula1>
       <formula2>73415</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="G26:G31">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="G30:G35">
       <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="G38:G52">
+    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="G42:G71">
       <formula1>7306</formula1>
       <formula2>73415</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="G59:G70">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="G78:G89">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="H12:J19">
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="H12:J23">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="H38:H52">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="H42:H71">
       <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="H59:H70">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="H78:H89">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="I26:I31">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="I30:I35">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="I59:I70">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="I78:I89">
       <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="J26:J31">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="J30:J35">
       <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="J38:J52">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="J42:J71">
       <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="K12:K19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="K12:K23">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="L12:L19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="L12:L23">
       <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="N12:O19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="N12:O23">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="P12:P19">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="P12:P23">
       <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
   </dataValidations>
@@ -6509,8 +6856,9 @@
   <headerFooter>
     <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Fact find&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="53" max="16838" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="36" max="16838" man="1"/>
+    <brk id="72" max="16838" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -9930,7 +10278,7 @@
   </mergeCells>
   <dataValidations count="33">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Item or amount" prompt="Pick one of your assets from the list, or type an item or an amount." sqref="B68:B73">
-      <formula1>'Lists'!$C$2:$C$34</formula1>
+      <formula1>'Lists'!$C$2:$C$53</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Name" prompt="Pick a family member from the list, or type any name." sqref="B79:B83">
       <formula1>'Lists'!$B$2:$B$10</formula1>

--- a/Duwalcoe_Fact_Find_Template.xlsx
+++ b/Duwalcoe_Fact_Find_Template.xlsx
@@ -324,7 +324,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="851" uniqueCount="561">
   <si>
     <t>Duwalcoe Financial Consultants CC</t>
   </si>
@@ -1808,7 +1808,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.4</t>
+    <t>1.5</t>
   </si>
   <si>
     <t>Ms.</t>
@@ -2004,6 +2004,9 @@
   </si>
   <si>
     <t>Household Contents</t>
+  </si>
+  <si>
+    <t>Clinton Hayes</t>
   </si>
 </sst>
 </file>
@@ -2280,7 +2283,20 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -4056,19 +4072,25 @@
       <c r="B19" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="18">
+        <f>TODAY()</f>
+      </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="11"/>
+      <c r="C20" s="17" t="s">
+        <v>560</v>
+      </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="18">
+        <f>TODAY()</f>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
@@ -4082,16 +4104,8 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B12:F12"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="1">
     <dataValidation sqref="C15"/>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C19">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C21">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.6" header="0.25" footer="0.3"/>
@@ -4651,7 +4665,7 @@
       <c r="E40" s="14"/>
       <c r="F40" s="14"/>
       <c r="G40" s="20">
-        <f>IF(AND(LEN(C40)&lt;&gt;13,D40=""),"",DATEDIF(IF(LEN(C40)=13,IFERROR(DATE(IF(VALUE(LEFT(C40,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C40,2)),VALUE(MID(C40,3,2)),VALUE(MID(C40,5,2))),D40),D40),TODAY(),"Y"))</f>
+        <f>IFERROR(IF(AND(LEN(C40)&lt;&gt;13,D40=""),"",DATEDIF(IF(LEN(C40)=13,IFERROR(DATE(IF(VALUE(LEFT(C40,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C40,2)),VALUE(MID(C40,3,2)),VALUE(MID(C40,5,2))),D40),D40),TODAY(),"Y")),"")</f>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -4661,7 +4675,7 @@
       <c r="E41" s="14"/>
       <c r="F41" s="14"/>
       <c r="G41" s="20">
-        <f>IF(AND(LEN(C41)&lt;&gt;13,D41=""),"",DATEDIF(IF(LEN(C41)=13,IFERROR(DATE(IF(VALUE(LEFT(C41,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C41,2)),VALUE(MID(C41,3,2)),VALUE(MID(C41,5,2))),D41),D41),TODAY(),"Y"))</f>
+        <f>IFERROR(IF(AND(LEN(C41)&lt;&gt;13,D41=""),"",DATEDIF(IF(LEN(C41)=13,IFERROR(DATE(IF(VALUE(LEFT(C41,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C41,2)),VALUE(MID(C41,3,2)),VALUE(MID(C41,5,2))),D41),D41),TODAY(),"Y")),"")</f>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -4671,7 +4685,7 @@
       <c r="E42" s="14"/>
       <c r="F42" s="14"/>
       <c r="G42" s="20">
-        <f>IF(AND(LEN(C42)&lt;&gt;13,D42=""),"",DATEDIF(IF(LEN(C42)=13,IFERROR(DATE(IF(VALUE(LEFT(C42,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C42,2)),VALUE(MID(C42,3,2)),VALUE(MID(C42,5,2))),D42),D42),TODAY(),"Y"))</f>
+        <f>IFERROR(IF(AND(LEN(C42)&lt;&gt;13,D42=""),"",DATEDIF(IF(LEN(C42)=13,IFERROR(DATE(IF(VALUE(LEFT(C42,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C42,2)),VALUE(MID(C42,3,2)),VALUE(MID(C42,5,2))),D42),D42),TODAY(),"Y")),"")</f>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -4681,7 +4695,7 @@
       <c r="E43" s="14"/>
       <c r="F43" s="14"/>
       <c r="G43" s="20">
-        <f>IF(AND(LEN(C43)&lt;&gt;13,D43=""),"",DATEDIF(IF(LEN(C43)=13,IFERROR(DATE(IF(VALUE(LEFT(C43,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C43,2)),VALUE(MID(C43,3,2)),VALUE(MID(C43,5,2))),D43),D43),TODAY(),"Y"))</f>
+        <f>IFERROR(IF(AND(LEN(C43)&lt;&gt;13,D43=""),"",DATEDIF(IF(LEN(C43)=13,IFERROR(DATE(IF(VALUE(LEFT(C43,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C43,2)),VALUE(MID(C43,3,2)),VALUE(MID(C43,5,2))),D43),D43),TODAY(),"Y")),"")</f>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -4691,7 +4705,7 @@
       <c r="E44" s="14"/>
       <c r="F44" s="14"/>
       <c r="G44" s="20">
-        <f>IF(AND(LEN(C44)&lt;&gt;13,D44=""),"",DATEDIF(IF(LEN(C44)=13,IFERROR(DATE(IF(VALUE(LEFT(C44,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C44,2)),VALUE(MID(C44,3,2)),VALUE(MID(C44,5,2))),D44),D44),TODAY(),"Y"))</f>
+        <f>IFERROR(IF(AND(LEN(C44)&lt;&gt;13,D44=""),"",DATEDIF(IF(LEN(C44)=13,IFERROR(DATE(IF(VALUE(LEFT(C44,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C44,2)),VALUE(MID(C44,3,2)),VALUE(MID(C44,5,2))),D44),D44),TODAY(),"Y")),"")</f>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -4701,7 +4715,7 @@
       <c r="E45" s="14"/>
       <c r="F45" s="14"/>
       <c r="G45" s="20">
-        <f>IF(AND(LEN(C45)&lt;&gt;13,D45=""),"",DATEDIF(IF(LEN(C45)=13,IFERROR(DATE(IF(VALUE(LEFT(C45,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C45,2)),VALUE(MID(C45,3,2)),VALUE(MID(C45,5,2))),D45),D45),TODAY(),"Y"))</f>
+        <f>IFERROR(IF(AND(LEN(C45)&lt;&gt;13,D45=""),"",DATEDIF(IF(LEN(C45)=13,IFERROR(DATE(IF(VALUE(LEFT(C45,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C45,2)),VALUE(MID(C45,3,2)),VALUE(MID(C45,5,2))),D45),D45),TODAY(),"Y")),"")</f>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -4711,7 +4725,7 @@
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
       <c r="G46" s="20">
-        <f>IF(AND(LEN(C46)&lt;&gt;13,D46=""),"",DATEDIF(IF(LEN(C46)=13,IFERROR(DATE(IF(VALUE(LEFT(C46,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C46,2)),VALUE(MID(C46,3,2)),VALUE(MID(C46,5,2))),D46),D46),TODAY(),"Y"))</f>
+        <f>IFERROR(IF(AND(LEN(C46)&lt;&gt;13,D46=""),"",DATEDIF(IF(LEN(C46)=13,IFERROR(DATE(IF(VALUE(LEFT(C46,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C46,2)),VALUE(MID(C46,3,2)),VALUE(MID(C46,5,2))),D46),D46),TODAY(),"Y")),"")</f>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -4721,7 +4735,7 @@
       <c r="E47" s="14"/>
       <c r="F47" s="14"/>
       <c r="G47" s="20">
-        <f>IF(AND(LEN(C47)&lt;&gt;13,D47=""),"",DATEDIF(IF(LEN(C47)=13,IFERROR(DATE(IF(VALUE(LEFT(C47,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C47,2)),VALUE(MID(C47,3,2)),VALUE(MID(C47,5,2))),D47),D47),TODAY(),"Y"))</f>
+        <f>IFERROR(IF(AND(LEN(C47)&lt;&gt;13,D47=""),"",DATEDIF(IF(LEN(C47)=13,IFERROR(DATE(IF(VALUE(LEFT(C47,2))&gt;MOD(YEAR(TODAY()),100),1900,2000)+VALUE(LEFT(C47,2)),VALUE(MID(C47,3,2)),VALUE(MID(C47,5,2))),D47),D47),TODAY(),"Y")),"")</f>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
@@ -4764,11 +4778,23 @@
     <mergeCell ref="B50:G50"/>
     <mergeCell ref="C51:G51"/>
   </mergeCells>
+  <conditionalFormatting sqref="C16:D16">
+    <cfRule type="expression" dxfId="0" priority="1000">
+      <formula>AND(C16&lt;&gt;"",NOT(ISNUMBER(C16)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C33">
+    <cfRule type="expression" dxfId="0" priority="1001">
+      <formula>AND(C33&lt;&gt;"",NOT(ISNUMBER(C33)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D40:D47">
+    <cfRule type="expression" dxfId="0" priority="1002">
+      <formula>AND(D40&lt;&gt;"",NOT(ISNUMBER(D40)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="12">
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C16:D16">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C16:D16"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C17">
       <formula1>'Lists'!$E$2:$E$3</formula1>
     </dataValidation>
@@ -4781,10 +4807,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C32">
       <formula1>'Lists'!$H$2:$H$9</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C33">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C33"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C34">
       <formula1>'Lists'!$G$2:$G$3</formula1>
     </dataValidation>
@@ -4794,10 +4817,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D28">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="D40:D47">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="D40:D47"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="E40:E47">
       <formula1>'Lists'!$J$2:$J$6</formula1>
     </dataValidation>
@@ -6760,6 +6780,21 @@
     <mergeCell ref="B38:Q38"/>
     <mergeCell ref="B74:Q74"/>
   </mergeCells>
+  <conditionalFormatting sqref="E12:E23">
+    <cfRule type="expression" dxfId="0" priority="1000">
+      <formula>AND(E12&lt;&gt;"",NOT(ISNUMBER(E12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:G23">
+    <cfRule type="expression" dxfId="0" priority="1001">
+      <formula>AND(G12&lt;&gt;"",NOT(ISNUMBER(G12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G42:G71">
+    <cfRule type="expression" dxfId="0" priority="1002">
+      <formula>AND(G42&lt;&gt;"",NOT(ISNUMBER(G42)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="28">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose a name" error="Please choose a name from the list (or Joint). The names come from the Client and family sheet." sqref="C12:C23">
       <formula1>'Lists'!$A$2:$A$4</formula1>
@@ -6785,10 +6820,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D78:D89">
       <formula1>'Lists'!$M$2:$M$10</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="E12:E23">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="E12:E23"/>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="E42:F71">
       <formula1>0</formula1>
     </dataValidation>
@@ -6802,17 +6834,11 @@
       <formula1>0</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="G12:G23">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="G12:G23"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="G30:G35">
       <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="G42:G71">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="G42:G71"/>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="G78:G89">
       <formula1>0</formula1>
     </dataValidation>
@@ -8350,6 +8376,46 @@
     <mergeCell ref="C155:E155"/>
     <mergeCell ref="B166:G166"/>
   </mergeCells>
+  <conditionalFormatting sqref="C104">
+    <cfRule type="expression" dxfId="0" priority="1000">
+      <formula>AND(C104&lt;&gt;"",NOT(ISNUMBER(C104)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C116:D116">
+    <cfRule type="expression" dxfId="0" priority="1001">
+      <formula>AND(C116&lt;&gt;"",NOT(ISNUMBER(C116)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C13">
+    <cfRule type="expression" dxfId="0" priority="1002">
+      <formula>AND(C13&lt;&gt;"",NOT(ISNUMBER(C13)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C149">
+    <cfRule type="expression" dxfId="0" priority="1003">
+      <formula>AND(C149&lt;&gt;"",NOT(ISNUMBER(C149)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C161:D161">
+    <cfRule type="expression" dxfId="0" priority="1004">
+      <formula>AND(C161&lt;&gt;"",NOT(ISNUMBER(C161)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C25:D25">
+    <cfRule type="expression" dxfId="0" priority="1005">
+      <formula>AND(C25&lt;&gt;"",NOT(ISNUMBER(C25)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C59">
+    <cfRule type="expression" dxfId="0" priority="1006">
+      <formula>AND(C59&lt;&gt;"",NOT(ISNUMBER(C59)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C71:D71">
+    <cfRule type="expression" dxfId="0" priority="1007">
+      <formula>AND(C71&lt;&gt;"",NOT(ISNUMBER(C71)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="68">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C10">
       <formula1>'Lists'!$Q$2:$Q$5</formula1>
@@ -8366,10 +8432,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C103">
       <formula1>'Lists'!$P$2:$P$4</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C104">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C104"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C105">
       <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
@@ -8392,10 +8455,7 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="C114:D115">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C116:D116">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C116:D116"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C117:D117">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
@@ -8408,10 +8468,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C124:C133">
       <formula1>'Lists'!$S$2:$S$5</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C13">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C13"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C14">
       <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
@@ -8427,10 +8484,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C148">
       <formula1>'Lists'!$P$2:$P$4</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C149">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C149"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C15">
       <formula1>'Lists'!$V$2:$V$4</formula1>
     </dataValidation>
@@ -8453,10 +8507,7 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="C159:D160">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C161:D161">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C161:D161"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C162:D162">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
@@ -8479,10 +8530,7 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="C23:D24">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C25:D25">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C25:D25"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C26:D26">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>
@@ -8504,10 +8552,7 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C58">
       <formula1>'Lists'!$P$2:$P$4</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C59">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C59"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C60">
       <formula1>'Lists'!$U$2:$U$5</formula1>
     </dataValidation>
@@ -8527,10 +8572,7 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="C69:D70">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="date" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Date" error="Please type a date like 2012-03-31. If you only know the year, type the 1st of January of that year and say so in Notes." sqref="C71:D71">
-      <formula1>7306</formula1>
-      <formula2>73415</formula2>
-    </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C71:D71"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C72:D72">
       <formula1>'Lists'!$F$2:$F$3</formula1>
     </dataValidation>

--- a/Duwalcoe_Fact_Find_Template.xlsx
+++ b/Duwalcoe_Fact_Find_Template.xlsx
@@ -5002,6 +5002,7 @@
       <c r="E95" s="14"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" formatRows="0"/>
   <mergeCells count="75">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>
@@ -8084,6 +8085,10 @@
   <headerFooter>
     <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Fact find&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
   </headerFooter>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="36" max="16838" man="1"/>
+    <brk id="72" max="16838" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -9814,6 +9819,11 @@
   <headerFooter>
     <oddFooter>&amp;L&amp;8&amp;"Arial"Duwalcoe Financial Consultants CC  ·  FSP 9978  ·  Fact find&amp;R&amp;8&amp;"Arial"&amp;A  ·  page &amp;P</oddFooter>
   </headerFooter>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="51" max="16838" man="1"/>
+    <brk id="96" max="16838" man="1"/>
+    <brk id="141" max="16838" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -10801,6 +10811,7 @@
       <c r="E90" s="14"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" formatRows="0"/>
   <mergeCells count="45">
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="B2:E2"/>

--- a/Duwalcoe_Fact_Find_Template.xlsx
+++ b/Duwalcoe_Fact_Find_Template.xlsx
@@ -325,6 +325,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Will extras'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'Summary'!$A1:$F35</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Summary'!$1:$2</definedName>
+    <definedName name="FF_S_SpouseTitle">'Client and family'!$D$9</definedName>
+    <definedName name="FF_S_SpouseCallingName">'Client and family'!$D$12</definedName>
+    <definedName name="FF_S_SpouseGender">'Client and family'!$D$17</definedName>
+    <definedName name="FF_S_SpouseSmoker">'Client and family'!$D$18</definedName>
+    <definedName name="FF_S_SpouseTelHome">'Client and family'!$D$21</definedName>
+    <definedName name="FF_S_SpouseTelWork">'Client and family'!$D$22</definedName>
+    <definedName name="FF_S_SpouseEmployer">'Client and family'!$D$26</definedName>
+    <definedName name="FF_S_SpouseEducation">'Client and family'!$D$30</definedName>
+    <definedName name="FF_S_SpouseQualification">'Client and family'!$D$31</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
@@ -3289,8 +3298,10 @@
       <c r="AW3" t="s">
         <v>485</v>
       </c>
-      <c r="AX3" t="s">
-        <v>486</v>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
     </row>
     <row r="4" spans="1:49" x14ac:dyDescent="0.25">
@@ -3516,8 +3527,10 @@
       <c r="AW7" t="s">
         <v>539</v>
       </c>
-      <c r="AX7" t="s">
-        <v>486</v>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>1.7</t>
+        </is>
       </c>
     </row>
     <row r="8" spans="2:50" x14ac:dyDescent="0.25">
@@ -5612,7 +5625,7 @@
         <v>28</v>
       </c>
       <c r="C9" s="15"/>
-      <c r="D9" s="9"/>
+      <c r="D9" s="15"/>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
@@ -5633,7 +5646,7 @@
         <v>31</v>
       </c>
       <c r="C12" s="14"/>
-      <c r="D12" s="9"/>
+      <c r="D12" s="14"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
@@ -5676,14 +5689,14 @@
         <v>36</v>
       </c>
       <c r="C17" s="15"/>
-      <c r="D17" s="9"/>
+      <c r="D17" s="15"/>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
         <v>37</v>
       </c>
       <c r="C18" s="15"/>
-      <c r="D18" s="9"/>
+      <c r="D18" s="15"/>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
@@ -5704,14 +5717,14 @@
         <v>40</v>
       </c>
       <c r="C21" s="16"/>
-      <c r="D21" s="9"/>
+      <c r="D21" s="16"/>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" s="7" t="s">
         <v>41</v>
       </c>
       <c r="C22" s="16"/>
-      <c r="D22" s="9"/>
+      <c r="D22" s="16"/>
     </row>
     <row r="23" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B23" s="7" t="s">
@@ -5739,7 +5752,7 @@
         <v>45</v>
       </c>
       <c r="C26" s="14"/>
-      <c r="D26" s="9"/>
+      <c r="D26" s="14"/>
     </row>
     <row r="27" ht="30" customHeight="1" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B27" s="7" t="s">
@@ -5771,14 +5784,14 @@
         <v>49</v>
       </c>
       <c r="C30" s="15"/>
-      <c r="D30" s="9"/>
+      <c r="D30" s="15"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B31" s="7" t="s">
         <v>50</v>
       </c>
       <c r="C31" s="14"/>
-      <c r="D31" s="9"/>
+      <c r="D31" s="14"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B32" s="7" t="s">
@@ -5996,7 +6009,7 @@
       <formula>AND(D40&lt;&gt;"",NOT(ISNUMBER(D40)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="12">
+  <dataValidations count="16">
     <dataValidation showInputMessage="1" promptTitle="Date" prompt="Type a date like 2026-10-17 or 17 Oct 2026. If the cell turns red, Excel did not read it as a date: retype it." sqref="C16:D16"/>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C17">
       <formula1>'Lists'!$E$2:$E$3</formula1>
@@ -6026,6 +6039,18 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="F40:F47">
       <formula1>'Lists'!$F$2:$F$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D9">
+      <formula1>'Lists'!$D$2:$D$9</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D17">
+      <formula1>'Lists'!$E$2:$E$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D18">
+      <formula1>'Lists'!$F$2:$F$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="D30">
+      <formula1>'Lists'!$I$2:$I$7</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>

--- a/Duwalcoe_Fact_Find_Template.xlsx
+++ b/Duwalcoe_Fact_Find_Template.xlsx
@@ -3300,7 +3300,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
     </row>
@@ -9864,14 +9864,14 @@
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="28" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+    <col min="8" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="28" customWidth="1"/>
     <col min="26" max="26" width="18" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21.75" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="1" ht="21.75" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9883,8 +9883,9 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
-    </row>
-    <row r="2" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -9896,13 +9897,14 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
     </row>
     <row r="4" ht="20" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" ht="18" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
         <v>216</v>
       </c>
@@ -9914,8 +9916,9 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
-    </row>
-    <row r="7" ht="26" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" ht="26" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="12" t="s">
         <v>217</v>
       </c>
@@ -9927,6 +9930,7 @@
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
       <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
     </row>
     <row r="8" hidden="1" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
@@ -9941,26 +9945,31 @@
       <c r="E8" t="s">
         <v>220</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>fromAge</t>
+        </is>
+      </c>
+      <c r="G8" t="s">
         <v>221</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>222</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>223</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>224</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>78</v>
       </c>
       <c r="Z8" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" ht="30" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
         <v>225</v>
       </c>
@@ -9973,23 +9982,28 @@
       <c r="E9" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="13" t="inlineStr">
+        <is>
+          <t>From age (retirement only)</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="H9" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="I9" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="J9" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="K9" s="13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="21" t="s">
         <v>232</v>
       </c>
@@ -10002,160 +10016,175 @@
       <c r="E10" s="22">
         <v>40000</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="21">
         <v>20</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="H10" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="I10" s="21" t="s">
         <v>138</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>98</v>
       </c>
       <c r="J10" s="21" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K10" s="21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="14"/>
       <c r="C11" s="15"/>
       <c r="D11" s="15"/>
       <c r="E11" s="23"/>
       <c r="F11" s="27"/>
       <c r="G11" s="27"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="14"/>
+      <c r="H11" s="27"/>
+      <c r="I11" s="15"/>
       <c r="J11" s="14"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K11" s="14"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="14"/>
       <c r="C12" s="15"/>
       <c r="D12" s="15"/>
       <c r="E12" s="23"/>
       <c r="F12" s="27"/>
       <c r="G12" s="27"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="14"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="15"/>
       <c r="J12" s="14"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="14"/>
+    </row>
+    <row r="13" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="14"/>
       <c r="C13" s="15"/>
       <c r="D13" s="15"/>
       <c r="E13" s="23"/>
       <c r="F13" s="27"/>
       <c r="G13" s="27"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="14"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="15"/>
       <c r="J13" s="14"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K13" s="14"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="14"/>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
       <c r="E14" s="23"/>
       <c r="F14" s="27"/>
       <c r="G14" s="27"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="14"/>
+      <c r="H14" s="27"/>
+      <c r="I14" s="15"/>
       <c r="J14" s="14"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K14" s="14"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="14"/>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
       <c r="E15" s="23"/>
       <c r="F15" s="27"/>
       <c r="G15" s="27"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="14"/>
+      <c r="H15" s="27"/>
+      <c r="I15" s="15"/>
       <c r="J15" s="14"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="14"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="14"/>
       <c r="C16" s="15"/>
       <c r="D16" s="15"/>
       <c r="E16" s="23"/>
       <c r="F16" s="27"/>
       <c r="G16" s="27"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="14"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="15"/>
       <c r="J16" s="14"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K16" s="14"/>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="14"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="23"/>
       <c r="F17" s="27"/>
       <c r="G17" s="27"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="14"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="15"/>
       <c r="J17" s="14"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K17" s="14"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="14"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
       <c r="E18" s="23"/>
       <c r="F18" s="27"/>
       <c r="G18" s="27"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="14"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="15"/>
       <c r="J18" s="14"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K18" s="14"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="14"/>
       <c r="C19" s="15"/>
       <c r="D19" s="15"/>
       <c r="E19" s="23"/>
       <c r="F19" s="27"/>
       <c r="G19" s="27"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="14"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="15"/>
       <c r="J19" s="14"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K19" s="14"/>
+    </row>
+    <row r="20" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="14"/>
       <c r="C20" s="15"/>
       <c r="D20" s="15"/>
       <c r="E20" s="23"/>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="14"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="15"/>
       <c r="J20" s="14"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K20" s="14"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="14"/>
       <c r="C21" s="15"/>
       <c r="D21" s="15"/>
       <c r="E21" s="23"/>
       <c r="F21" s="27"/>
       <c r="G21" s="27"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="14"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="15"/>
       <c r="J21" s="14"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" ht="15" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="14"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="23"/>
       <c r="F22" s="27"/>
       <c r="G22" s="27"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="14"/>
+      <c r="H22" s="27"/>
+      <c r="I22" s="15"/>
       <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" formatRows="0"/>
   <mergeCells count="3">
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="B2:J2"/>
-    <mergeCell ref="B7:J7"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B7:K7"/>
   </mergeCells>
   <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="C11:C22">
@@ -10167,11 +10196,11 @@
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Amount" error="Please type the amount in rand as a number, without R or spaces, e.g. 1250000." sqref="E11:E22">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Number" error="Please type a number." sqref="F11:G22">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Number" error="Please type a number." sqref="F11:H22">
       <formula1>0</formula1>
       <formula2>1000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="H11:H22">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Please choose from the list" error="Please choose one of the options in the list." sqref="I11:I22">
       <formula1>'Lists'!$Y$2:$Y$4</formula1>
     </dataValidation>
   </dataValidations>
